--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,6 +1553,1235 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124971034</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95434</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>540178</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6448461</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124972164</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30115</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>540191</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6448460</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124976998</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105029</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>540248</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6448393</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124977940</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105029</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>540095</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6448266</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124971516</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95436</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>540172</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6448475</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124972268</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95423</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>540161</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6448467</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124976354</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57995</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>540222</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6448401</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124978294</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>540048</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6448338</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124972706</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>540171</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6448423</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124979217</v>
+      </c>
+      <c r="B18" t="n">
+        <v>9398</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>540120</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6448309</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124971310</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95434</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>540177</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6448472</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124968982</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105029</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>540253</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6448511</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124971034</v>
+        <v>124972268</v>
       </c>
       <c r="B9" t="n">
-        <v>95434</v>
+        <v>95423</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540178</v>
+        <v>540161</v>
       </c>
       <c r="R9" t="n">
-        <v>6448461</v>
+        <v>6448467</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124972164</v>
+        <v>124971310</v>
       </c>
       <c r="B10" t="n">
-        <v>30115</v>
+        <v>95434</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540191</v>
+        <v>540177</v>
       </c>
       <c r="R10" t="n">
-        <v>6448460</v>
+        <v>6448472</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124976998</v>
+        <v>124972706</v>
       </c>
       <c r="B11" t="n">
-        <v>105029</v>
+        <v>100188</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540248</v>
+        <v>540171</v>
       </c>
       <c r="R11" t="n">
-        <v>6448393</v>
+        <v>6448423</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124977940</v>
+        <v>124979217</v>
       </c>
       <c r="B12" t="n">
-        <v>105029</v>
+        <v>9398</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>101246</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540095</v>
+        <v>540120</v>
       </c>
       <c r="R12" t="n">
-        <v>6448266</v>
+        <v>6448309</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1937,11 +1937,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124971516</v>
+        <v>124976354</v>
       </c>
       <c r="B13" t="n">
-        <v>95436</v>
+        <v>57995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,25 +1975,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2666</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540172</v>
+        <v>540222</v>
       </c>
       <c r="R13" t="n">
-        <v>6448475</v>
+        <v>6448401</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124972268</v>
+        <v>124971516</v>
       </c>
       <c r="B14" t="n">
-        <v>95423</v>
+        <v>95436</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,13 +2105,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540161</v>
+        <v>540172</v>
       </c>
       <c r="R14" t="n">
-        <v>6448467</v>
+        <v>6448475</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2172,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124976354</v>
+        <v>124972164</v>
       </c>
       <c r="B15" t="n">
-        <v>57995</v>
+        <v>30115</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,25 +2179,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>200985</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,13 +2207,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540222</v>
+        <v>540191</v>
       </c>
       <c r="R15" t="n">
-        <v>6448401</v>
+        <v>6448460</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124978294</v>
+        <v>124971034</v>
       </c>
       <c r="B16" t="n">
-        <v>91032</v>
+        <v>95434</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,25 +2281,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,13 +2309,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540048</v>
+        <v>540178</v>
       </c>
       <c r="R16" t="n">
-        <v>6448338</v>
+        <v>6448461</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124972706</v>
+        <v>124976998</v>
       </c>
       <c r="B17" t="n">
-        <v>100188</v>
+        <v>105029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,16 +2387,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540171</v>
+        <v>540248</v>
       </c>
       <c r="R17" t="n">
-        <v>6448423</v>
+        <v>6448393</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2478,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124979217</v>
+        <v>124978294</v>
       </c>
       <c r="B18" t="n">
-        <v>9398</v>
+        <v>91032</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,25 +2485,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101246</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,13 +2513,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540120</v>
+        <v>540048</v>
       </c>
       <c r="R18" t="n">
-        <v>6448309</v>
+        <v>6448338</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124971310</v>
+        <v>124977940</v>
       </c>
       <c r="B19" t="n">
-        <v>95434</v>
+        <v>105029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,21 +2591,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540177</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>6448472</v>
+        <v>6448266</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2656,6 +2651,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,6 +2782,108 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125009086</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>540056</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6448344</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124972706</v>
+        <v>124976354</v>
       </c>
       <c r="B11" t="n">
-        <v>100188</v>
+        <v>57995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540171</v>
+        <v>540222</v>
       </c>
       <c r="R11" t="n">
-        <v>6448423</v>
+        <v>6448401</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124979217</v>
+        <v>124972706</v>
       </c>
       <c r="B12" t="n">
-        <v>9398</v>
+        <v>100188</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101246</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540120</v>
+        <v>540171</v>
       </c>
       <c r="R12" t="n">
-        <v>6448309</v>
+        <v>6448423</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124976354</v>
+        <v>124976998</v>
       </c>
       <c r="B13" t="n">
-        <v>57995</v>
+        <v>105029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,25 +1975,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540222</v>
+        <v>540248</v>
       </c>
       <c r="R13" t="n">
-        <v>6448401</v>
+        <v>6448393</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124971516</v>
+        <v>124977940</v>
       </c>
       <c r="B14" t="n">
-        <v>95436</v>
+        <v>105029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2666</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540172</v>
+        <v>540095</v>
       </c>
       <c r="R14" t="n">
-        <v>6448475</v>
+        <v>6448266</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2141,6 +2141,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124972164</v>
+        <v>124968982</v>
       </c>
       <c r="B15" t="n">
-        <v>30115</v>
+        <v>105029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>200985</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540191</v>
+        <v>540253</v>
       </c>
       <c r="R15" t="n">
-        <v>6448460</v>
+        <v>6448511</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2371,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124976998</v>
+        <v>124978294</v>
       </c>
       <c r="B17" t="n">
-        <v>105029</v>
+        <v>91032</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,25 +2388,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,13 +2416,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540248</v>
+        <v>540048</v>
       </c>
       <c r="R17" t="n">
-        <v>6448393</v>
+        <v>6448338</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124978294</v>
+        <v>124979217</v>
       </c>
       <c r="B18" t="n">
-        <v>91032</v>
+        <v>9398</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,25 +2490,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>101246</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,13 +2518,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540048</v>
+        <v>540120</v>
       </c>
       <c r="R18" t="n">
-        <v>6448338</v>
+        <v>6448309</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124977940</v>
+        <v>124971516</v>
       </c>
       <c r="B19" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,21 +2596,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>540172</v>
       </c>
       <c r="R19" t="n">
-        <v>6448266</v>
+        <v>6448475</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2651,11 +2656,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124968982</v>
+        <v>124972164</v>
       </c>
       <c r="B20" t="n">
-        <v>105029</v>
+        <v>30115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221141</v>
+        <v>200985</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540253</v>
+        <v>540191</v>
       </c>
       <c r="R20" t="n">
-        <v>6448511</v>
+        <v>6448460</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124972268</v>
+        <v>124979217</v>
       </c>
       <c r="B9" t="n">
-        <v>95423</v>
+        <v>9398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>101246</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540161</v>
+        <v>540120</v>
       </c>
       <c r="R9" t="n">
-        <v>6448467</v>
+        <v>6448309</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124971310</v>
+        <v>124976354</v>
       </c>
       <c r="B10" t="n">
-        <v>95434</v>
+        <v>57995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,25 +1669,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R10" t="n">
-        <v>6448472</v>
+        <v>6448401</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124976354</v>
+        <v>124978294</v>
       </c>
       <c r="B11" t="n">
-        <v>57995</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540222</v>
+        <v>540048</v>
       </c>
       <c r="R11" t="n">
-        <v>6448401</v>
+        <v>6448338</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124972706</v>
+        <v>124972268</v>
       </c>
       <c r="B12" t="n">
-        <v>100188</v>
+        <v>95423</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540171</v>
+        <v>540161</v>
       </c>
       <c r="R12" t="n">
-        <v>6448423</v>
+        <v>6448467</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124976998</v>
+        <v>124968982</v>
       </c>
       <c r="B13" t="n">
         <v>105029</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540248</v>
+        <v>540253</v>
       </c>
       <c r="R13" t="n">
-        <v>6448393</v>
+        <v>6448511</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124977940</v>
+        <v>124972164</v>
       </c>
       <c r="B14" t="n">
-        <v>105029</v>
+        <v>30115</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>200985</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540095</v>
+        <v>540191</v>
       </c>
       <c r="R14" t="n">
-        <v>6448266</v>
+        <v>6448460</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2141,11 +2141,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124968982</v>
+        <v>124971516</v>
       </c>
       <c r="B15" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540253</v>
+        <v>540172</v>
       </c>
       <c r="R15" t="n">
-        <v>6448511</v>
+        <v>6448475</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2274,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124971034</v>
+        <v>124971310</v>
       </c>
       <c r="B16" t="n">
         <v>95434</v>
@@ -2314,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540178</v>
+        <v>540177</v>
       </c>
       <c r="R16" t="n">
-        <v>6448461</v>
+        <v>6448472</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124978294</v>
+        <v>124971034</v>
       </c>
       <c r="B17" t="n">
-        <v>91032</v>
+        <v>95434</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,13 +2411,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540048</v>
+        <v>540178</v>
       </c>
       <c r="R17" t="n">
-        <v>6448338</v>
+        <v>6448461</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124979217</v>
+        <v>124976998</v>
       </c>
       <c r="B18" t="n">
-        <v>9398</v>
+        <v>105029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2489,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101246</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540120</v>
+        <v>540248</v>
       </c>
       <c r="R18" t="n">
-        <v>6448309</v>
+        <v>6448393</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124971516</v>
+        <v>124977940</v>
       </c>
       <c r="B19" t="n">
-        <v>95436</v>
+        <v>105029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,21 +2591,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2666</v>
+        <v>221141</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540172</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>6448475</v>
+        <v>6448266</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2656,6 +2651,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124972164</v>
+        <v>124972706</v>
       </c>
       <c r="B20" t="n">
-        <v>30115</v>
+        <v>100188</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>200985</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540191</v>
+        <v>540171</v>
       </c>
       <c r="R20" t="n">
-        <v>6448460</v>
+        <v>6448423</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124979217</v>
+        <v>124972268</v>
       </c>
       <c r="B9" t="n">
-        <v>9398</v>
+        <v>95423</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101246</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540120</v>
+        <v>540161</v>
       </c>
       <c r="R9" t="n">
-        <v>6448309</v>
+        <v>6448467</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124978294</v>
+        <v>124979217</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>9398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>101246</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540048</v>
+        <v>540120</v>
       </c>
       <c r="R11" t="n">
-        <v>6448338</v>
+        <v>6448309</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124972268</v>
+        <v>124972706</v>
       </c>
       <c r="B12" t="n">
-        <v>95423</v>
+        <v>100188</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540161</v>
+        <v>540171</v>
       </c>
       <c r="R12" t="n">
-        <v>6448467</v>
+        <v>6448423</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124968982</v>
+        <v>124972164</v>
       </c>
       <c r="B13" t="n">
-        <v>105029</v>
+        <v>30115</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>200985</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540253</v>
+        <v>540191</v>
       </c>
       <c r="R13" t="n">
-        <v>6448511</v>
+        <v>6448460</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124972164</v>
+        <v>124968982</v>
       </c>
       <c r="B14" t="n">
-        <v>30115</v>
+        <v>105029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>200985</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540191</v>
+        <v>540253</v>
       </c>
       <c r="R14" t="n">
-        <v>6448460</v>
+        <v>6448511</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124971516</v>
+        <v>124978294</v>
       </c>
       <c r="B15" t="n">
-        <v>95436</v>
+        <v>91032</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,25 +2179,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2666</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540172</v>
+        <v>540048</v>
       </c>
       <c r="R15" t="n">
-        <v>6448475</v>
+        <v>6448338</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124971310</v>
+        <v>124977940</v>
       </c>
       <c r="B16" t="n">
-        <v>95434</v>
+        <v>105029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2285,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540177</v>
+        <v>540095</v>
       </c>
       <c r="R16" t="n">
-        <v>6448472</v>
+        <v>6448266</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2345,6 +2345,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,7 +2376,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124971034</v>
+        <v>124971310</v>
       </c>
       <c r="B17" t="n">
         <v>95434</v>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540178</v>
+        <v>540177</v>
       </c>
       <c r="R17" t="n">
-        <v>6448461</v>
+        <v>6448472</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2473,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124976998</v>
+        <v>124971034</v>
       </c>
       <c r="B18" t="n">
-        <v>105029</v>
+        <v>95434</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540248</v>
+        <v>540178</v>
       </c>
       <c r="R18" t="n">
-        <v>6448393</v>
+        <v>6448461</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2575,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124977940</v>
+        <v>124971516</v>
       </c>
       <c r="B19" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,21 +2596,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>540172</v>
       </c>
       <c r="R19" t="n">
-        <v>6448266</v>
+        <v>6448475</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2651,11 +2656,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124972706</v>
+        <v>124976998</v>
       </c>
       <c r="B20" t="n">
-        <v>100188</v>
+        <v>105029</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,16 +2698,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540171</v>
+        <v>540248</v>
       </c>
       <c r="R20" t="n">
-        <v>6448423</v>
+        <v>6448393</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2884,6 +2884,759 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125147960</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>540183</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6448467</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124975270</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>540143</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6448377</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125147970</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>540192</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6448454</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125148042</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95423</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>540179</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6448499</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125148007</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95228</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>540181</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6448506</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125148013</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95434</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>540181</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6448509</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125148071</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>540190</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6448516</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124972268</v>
+        <v>124972706</v>
       </c>
       <c r="B9" t="n">
-        <v>95423</v>
+        <v>100188</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540161</v>
+        <v>540171</v>
       </c>
       <c r="R9" t="n">
-        <v>6448467</v>
+        <v>6448423</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124976354</v>
+        <v>124977940</v>
       </c>
       <c r="B10" t="n">
-        <v>57995</v>
+        <v>105029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,25 +1669,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540222</v>
+        <v>540095</v>
       </c>
       <c r="R10" t="n">
-        <v>6448401</v>
+        <v>6448266</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,6 +1733,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1861,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124972706</v>
+        <v>124978294</v>
       </c>
       <c r="B12" t="n">
-        <v>100188</v>
+        <v>91032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,25 +1878,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1906,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540171</v>
+        <v>540048</v>
       </c>
       <c r="R12" t="n">
-        <v>6448423</v>
+        <v>6448338</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2065,7 +2070,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124968982</v>
+        <v>124976998</v>
       </c>
       <c r="B14" t="n">
         <v>105029</v>
@@ -2105,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540253</v>
+        <v>540248</v>
       </c>
       <c r="R14" t="n">
-        <v>6448511</v>
+        <v>6448393</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2167,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124978294</v>
+        <v>124972268</v>
       </c>
       <c r="B15" t="n">
-        <v>91032</v>
+        <v>95423</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,25 +2184,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540048</v>
+        <v>540161</v>
       </c>
       <c r="R15" t="n">
-        <v>6448338</v>
+        <v>6448467</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2269,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124977940</v>
+        <v>124971310</v>
       </c>
       <c r="B16" t="n">
-        <v>105029</v>
+        <v>95434</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540095</v>
+        <v>540177</v>
       </c>
       <c r="R16" t="n">
-        <v>6448266</v>
+        <v>6448472</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2345,11 +2350,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124971310</v>
+        <v>124976354</v>
       </c>
       <c r="B17" t="n">
-        <v>95434</v>
+        <v>57995</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>103018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,13 +2416,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R17" t="n">
-        <v>6448472</v>
+        <v>6448401</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124971034</v>
+        <v>124968982</v>
       </c>
       <c r="B18" t="n">
-        <v>95434</v>
+        <v>105029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540178</v>
+        <v>540253</v>
       </c>
       <c r="R18" t="n">
-        <v>6448461</v>
+        <v>6448511</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124971516</v>
+        <v>124971034</v>
       </c>
       <c r="B19" t="n">
-        <v>95436</v>
+        <v>95434</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,16 +2596,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540172</v>
+        <v>540178</v>
       </c>
       <c r="R19" t="n">
-        <v>6448475</v>
+        <v>6448461</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124976998</v>
+        <v>124971516</v>
       </c>
       <c r="B20" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540248</v>
+        <v>540172</v>
       </c>
       <c r="R20" t="n">
-        <v>6448393</v>
+        <v>6448475</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125147960</v>
+        <v>125148071</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,31 +2898,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540183</v>
+        <v>540190</v>
       </c>
       <c r="R22" t="n">
-        <v>6448467</v>
+        <v>6448516</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2968,17 +2968,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2997,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124975270</v>
+        <v>125148007</v>
       </c>
       <c r="B23" t="n">
-        <v>5361</v>
+        <v>95228</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3009,41 +3005,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101728</v>
+        <v>2779</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540143</v>
+        <v>540181</v>
       </c>
       <c r="R23" t="n">
-        <v>6448377</v>
+        <v>6448506</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3075,17 +3075,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3318,10 +3314,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125148007</v>
+        <v>125147960</v>
       </c>
       <c r="B26" t="n">
-        <v>95228</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3330,31 +3326,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2779</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3362,10 +3358,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540181</v>
+        <v>540183</v>
       </c>
       <c r="R26" t="n">
-        <v>6448506</v>
+        <v>6448467</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3400,13 +3396,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125148071</v>
+        <v>124975270</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>5361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3544,45 +3544,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540190</v>
+        <v>540143</v>
       </c>
       <c r="R28" t="n">
-        <v>6448516</v>
+        <v>6448377</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3614,13 +3610,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -2070,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124976998</v>
+        <v>124972268</v>
       </c>
       <c r="B14" t="n">
-        <v>105029</v>
+        <v>95423</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540248</v>
+        <v>540161</v>
       </c>
       <c r="R14" t="n">
-        <v>6448393</v>
+        <v>6448467</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124972268</v>
+        <v>124976998</v>
       </c>
       <c r="B15" t="n">
-        <v>95423</v>
+        <v>105029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2671</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540161</v>
+        <v>540248</v>
       </c>
       <c r="R15" t="n">
-        <v>6448467</v>
+        <v>6448393</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125148013</v>
+        <v>124975270</v>
       </c>
       <c r="B27" t="n">
-        <v>95434</v>
+        <v>5361</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3437,45 +3437,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>101728</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540181</v>
+        <v>540143</v>
       </c>
       <c r="R27" t="n">
-        <v>6448509</v>
+        <v>6448377</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3507,13 +3503,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124975270</v>
+        <v>125148013</v>
       </c>
       <c r="B28" t="n">
-        <v>5361</v>
+        <v>95434</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3544,41 +3544,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101728</v>
+        <v>2667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540143</v>
+        <v>540181</v>
       </c>
       <c r="R28" t="n">
-        <v>6448377</v>
+        <v>6448509</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3610,17 +3614,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -2274,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124971310</v>
+        <v>124976354</v>
       </c>
       <c r="B16" t="n">
-        <v>95434</v>
+        <v>57995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,25 +2286,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R16" t="n">
-        <v>6448472</v>
+        <v>6448401</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124976354</v>
+        <v>124971310</v>
       </c>
       <c r="B17" t="n">
-        <v>57995</v>
+        <v>95434</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,13 +2416,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540222</v>
+        <v>540177</v>
       </c>
       <c r="R17" t="n">
-        <v>6448401</v>
+        <v>6448472</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124972706</v>
+        <v>124979217</v>
       </c>
       <c r="B9" t="n">
-        <v>100188</v>
+        <v>9398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>101246</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540171</v>
+        <v>540120</v>
       </c>
       <c r="R9" t="n">
-        <v>6448423</v>
+        <v>6448309</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124977940</v>
+        <v>124968982</v>
       </c>
       <c r="B10" t="n">
         <v>105029</v>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540095</v>
+        <v>540253</v>
       </c>
       <c r="R10" t="n">
-        <v>6448266</v>
+        <v>6448511</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1733,11 +1733,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124979217</v>
+        <v>124976354</v>
       </c>
       <c r="B11" t="n">
-        <v>9398</v>
+        <v>57995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,25 +1771,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101246</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1804,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540120</v>
+        <v>540222</v>
       </c>
       <c r="R11" t="n">
-        <v>6448309</v>
+        <v>6448401</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124978294</v>
+        <v>124972706</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>100188</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,25 +1873,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1906,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540048</v>
+        <v>540171</v>
       </c>
       <c r="R12" t="n">
-        <v>6448338</v>
+        <v>6448423</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1968,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124972164</v>
+        <v>124971310</v>
       </c>
       <c r="B13" t="n">
-        <v>30115</v>
+        <v>95434</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540191</v>
+        <v>540177</v>
       </c>
       <c r="R13" t="n">
-        <v>6448460</v>
+        <v>6448472</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2070,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124972268</v>
+        <v>124976998</v>
       </c>
       <c r="B14" t="n">
-        <v>95423</v>
+        <v>105029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,13 +2105,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540161</v>
+        <v>540248</v>
       </c>
       <c r="R14" t="n">
-        <v>6448467</v>
+        <v>6448393</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2172,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124976998</v>
+        <v>124971034</v>
       </c>
       <c r="B15" t="n">
-        <v>105029</v>
+        <v>95434</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540248</v>
+        <v>540178</v>
       </c>
       <c r="R15" t="n">
-        <v>6448393</v>
+        <v>6448461</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2274,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124976354</v>
+        <v>124978294</v>
       </c>
       <c r="B16" t="n">
-        <v>57995</v>
+        <v>91032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,21 +2285,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,13 +2309,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540222</v>
+        <v>540048</v>
       </c>
       <c r="R16" t="n">
-        <v>6448401</v>
+        <v>6448338</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124971310</v>
+        <v>124977940</v>
       </c>
       <c r="B17" t="n">
-        <v>95434</v>
+        <v>105029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,21 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540177</v>
+        <v>540095</v>
       </c>
       <c r="R17" t="n">
-        <v>6448472</v>
+        <v>6448266</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2452,6 +2447,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124968982</v>
+        <v>124971516</v>
       </c>
       <c r="B18" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540253</v>
+        <v>540172</v>
       </c>
       <c r="R18" t="n">
-        <v>6448511</v>
+        <v>6448475</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124971034</v>
+        <v>124972268</v>
       </c>
       <c r="B19" t="n">
-        <v>95434</v>
+        <v>95423</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,21 +2596,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540178</v>
+        <v>540161</v>
       </c>
       <c r="R19" t="n">
-        <v>6448461</v>
+        <v>6448467</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124971516</v>
+        <v>124972164</v>
       </c>
       <c r="B20" t="n">
-        <v>95436</v>
+        <v>30115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>200985</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540172</v>
+        <v>540191</v>
       </c>
       <c r="R20" t="n">
-        <v>6448475</v>
+        <v>6448460</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125148007</v>
+        <v>125147960</v>
       </c>
       <c r="B23" t="n">
-        <v>95228</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,31 +3005,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2779</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540181</v>
+        <v>540183</v>
       </c>
       <c r="R23" t="n">
-        <v>6448506</v>
+        <v>6448467</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3075,13 +3075,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125147970</v>
+        <v>125148042</v>
       </c>
       <c r="B24" t="n">
-        <v>100188</v>
+        <v>95423</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,21 +3120,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540192</v>
+        <v>540179</v>
       </c>
       <c r="R24" t="n">
-        <v>6448454</v>
+        <v>6448499</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,10 +3211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125148042</v>
+        <v>125147970</v>
       </c>
       <c r="B25" t="n">
-        <v>95423</v>
+        <v>100188</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3223,21 +3227,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3251,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540179</v>
+        <v>540192</v>
       </c>
       <c r="R25" t="n">
-        <v>6448499</v>
+        <v>6448454</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3314,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125147960</v>
+        <v>125148013</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>95434</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,31 +3330,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3358,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540183</v>
+        <v>540181</v>
       </c>
       <c r="R26" t="n">
-        <v>6448467</v>
+        <v>6448509</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3396,17 +3400,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125148013</v>
+        <v>125148007</v>
       </c>
       <c r="B28" t="n">
-        <v>95434</v>
+        <v>95228</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
         <v>540181</v>
       </c>
       <c r="R28" t="n">
-        <v>6448509</v>
+        <v>6448506</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124979217</v>
+        <v>124976354</v>
       </c>
       <c r="B9" t="n">
-        <v>9398</v>
+        <v>57995</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101246</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540120</v>
+        <v>540222</v>
       </c>
       <c r="R9" t="n">
-        <v>6448309</v>
+        <v>6448401</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124968982</v>
+        <v>124971034</v>
       </c>
       <c r="B10" t="n">
-        <v>105029</v>
+        <v>95434</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540253</v>
+        <v>540178</v>
       </c>
       <c r="R10" t="n">
-        <v>6448511</v>
+        <v>6448461</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124976354</v>
+        <v>124978294</v>
       </c>
       <c r="B11" t="n">
-        <v>57995</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540222</v>
+        <v>540048</v>
       </c>
       <c r="R11" t="n">
-        <v>6448401</v>
+        <v>6448338</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124972706</v>
+        <v>124968982</v>
       </c>
       <c r="B12" t="n">
-        <v>100188</v>
+        <v>105029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540171</v>
+        <v>540253</v>
       </c>
       <c r="R12" t="n">
-        <v>6448423</v>
+        <v>6448511</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124976998</v>
+        <v>124971516</v>
       </c>
       <c r="B14" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540248</v>
+        <v>540172</v>
       </c>
       <c r="R14" t="n">
-        <v>6448393</v>
+        <v>6448475</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124971034</v>
+        <v>124972706</v>
       </c>
       <c r="B15" t="n">
-        <v>95434</v>
+        <v>100188</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540178</v>
+        <v>540171</v>
       </c>
       <c r="R15" t="n">
-        <v>6448461</v>
+        <v>6448423</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124978294</v>
+        <v>124976998</v>
       </c>
       <c r="B16" t="n">
-        <v>91032</v>
+        <v>105029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>221141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540048</v>
+        <v>540248</v>
       </c>
       <c r="R16" t="n">
-        <v>6448338</v>
+        <v>6448393</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124977940</v>
+        <v>124972268</v>
       </c>
       <c r="B17" t="n">
-        <v>105029</v>
+        <v>95423</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540095</v>
+        <v>540161</v>
       </c>
       <c r="R17" t="n">
-        <v>6448266</v>
+        <v>6448467</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,11 +2447,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124971516</v>
+        <v>124972164</v>
       </c>
       <c r="B18" t="n">
-        <v>95436</v>
+        <v>30115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2489,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2666</v>
+        <v>200985</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540172</v>
+        <v>540191</v>
       </c>
       <c r="R18" t="n">
-        <v>6448475</v>
+        <v>6448460</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124972268</v>
+        <v>124979217</v>
       </c>
       <c r="B19" t="n">
-        <v>95423</v>
+        <v>9398</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,21 +2591,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2671</v>
+        <v>101246</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,13 +2615,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540161</v>
+        <v>540120</v>
       </c>
       <c r="R19" t="n">
-        <v>6448467</v>
+        <v>6448309</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124972164</v>
+        <v>124977940</v>
       </c>
       <c r="B20" t="n">
-        <v>30115</v>
+        <v>105029</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,21 +2693,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>200985</v>
+        <v>221141</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540191</v>
+        <v>540095</v>
       </c>
       <c r="R20" t="n">
-        <v>6448460</v>
+        <v>6448266</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2758,6 +2753,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125148071</v>
+        <v>125148013</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540190</v>
+        <v>540181</v>
       </c>
       <c r="R22" t="n">
-        <v>6448516</v>
+        <v>6448509</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125147960</v>
+        <v>124975270</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>5361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3009,41 +3009,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540183</v>
+        <v>540143</v>
       </c>
       <c r="R23" t="n">
-        <v>6448467</v>
+        <v>6448377</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3077,7 +3073,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125148042</v>
+        <v>125147960</v>
       </c>
       <c r="B24" t="n">
-        <v>95423</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,31 +3112,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3148,10 +3144,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540179</v>
+        <v>540183</v>
       </c>
       <c r="R24" t="n">
-        <v>6448499</v>
+        <v>6448467</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3186,13 +3182,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125147970</v>
+        <v>125148007</v>
       </c>
       <c r="B25" t="n">
-        <v>100188</v>
+        <v>95228</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>2779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540192</v>
+        <v>540181</v>
       </c>
       <c r="R25" t="n">
-        <v>6448454</v>
+        <v>6448506</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125148013</v>
+        <v>125147970</v>
       </c>
       <c r="B26" t="n">
-        <v>95434</v>
+        <v>100188</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540181</v>
+        <v>540192</v>
       </c>
       <c r="R26" t="n">
-        <v>6448509</v>
+        <v>6448454</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124975270</v>
+        <v>125148042</v>
       </c>
       <c r="B27" t="n">
-        <v>5361</v>
+        <v>95423</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3437,41 +3437,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101728</v>
+        <v>2671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540143</v>
+        <v>540179</v>
       </c>
       <c r="R27" t="n">
-        <v>6448377</v>
+        <v>6448499</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3503,17 +3507,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125148007</v>
+        <v>125148071</v>
       </c>
       <c r="B28" t="n">
-        <v>95228</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540181</v>
+        <v>540190</v>
       </c>
       <c r="R28" t="n">
-        <v>6448506</v>
+        <v>6448516</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124976354</v>
+        <v>124971310</v>
       </c>
       <c r="B9" t="n">
-        <v>57995</v>
+        <v>95434</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540222</v>
+        <v>540177</v>
       </c>
       <c r="R9" t="n">
-        <v>6448401</v>
+        <v>6448472</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124971034</v>
+        <v>124972268</v>
       </c>
       <c r="B10" t="n">
-        <v>95434</v>
+        <v>95423</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540178</v>
+        <v>540161</v>
       </c>
       <c r="R10" t="n">
-        <v>6448461</v>
+        <v>6448467</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124978294</v>
+        <v>124979217</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>9398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>101246</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540048</v>
+        <v>540120</v>
       </c>
       <c r="R11" t="n">
-        <v>6448338</v>
+        <v>6448309</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124968982</v>
+        <v>124978294</v>
       </c>
       <c r="B12" t="n">
-        <v>105029</v>
+        <v>91032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,25 +1873,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540253</v>
+        <v>540048</v>
       </c>
       <c r="R12" t="n">
-        <v>6448511</v>
+        <v>6448338</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124971310</v>
+        <v>124976354</v>
       </c>
       <c r="B13" t="n">
-        <v>95434</v>
+        <v>57995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,25 +1975,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R13" t="n">
-        <v>6448472</v>
+        <v>6448401</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124971516</v>
+        <v>124976998</v>
       </c>
       <c r="B14" t="n">
-        <v>95436</v>
+        <v>105029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2666</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540172</v>
+        <v>540248</v>
       </c>
       <c r="R14" t="n">
-        <v>6448475</v>
+        <v>6448393</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124972706</v>
+        <v>124972164</v>
       </c>
       <c r="B15" t="n">
-        <v>100188</v>
+        <v>30115</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>200985</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540171</v>
+        <v>540191</v>
       </c>
       <c r="R15" t="n">
-        <v>6448423</v>
+        <v>6448460</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124976998</v>
+        <v>124971516</v>
       </c>
       <c r="B16" t="n">
-        <v>105029</v>
+        <v>95436</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2285,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540248</v>
+        <v>540172</v>
       </c>
       <c r="R16" t="n">
-        <v>6448393</v>
+        <v>6448475</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124972268</v>
+        <v>124971034</v>
       </c>
       <c r="B17" t="n">
-        <v>95423</v>
+        <v>95434</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540161</v>
+        <v>540178</v>
       </c>
       <c r="R17" t="n">
-        <v>6448467</v>
+        <v>6448461</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124972164</v>
+        <v>124968982</v>
       </c>
       <c r="B18" t="n">
-        <v>30115</v>
+        <v>105029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,21 +2489,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>200985</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540191</v>
+        <v>540253</v>
       </c>
       <c r="R18" t="n">
-        <v>6448460</v>
+        <v>6448511</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124979217</v>
+        <v>124977940</v>
       </c>
       <c r="B19" t="n">
-        <v>9398</v>
+        <v>105029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101246</v>
+        <v>221141</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540120</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>6448309</v>
+        <v>6448266</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2651,6 +2651,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124977940</v>
+        <v>124972706</v>
       </c>
       <c r="B20" t="n">
-        <v>105029</v>
+        <v>100188</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,16 +2698,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221141</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2717,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540095</v>
+        <v>540171</v>
       </c>
       <c r="R20" t="n">
-        <v>6448266</v>
+        <v>6448423</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2753,11 +2758,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125148013</v>
+        <v>124975270</v>
       </c>
       <c r="B22" t="n">
-        <v>95434</v>
+        <v>5361</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,45 +2898,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2667</v>
+        <v>101728</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540181</v>
+        <v>540143</v>
       </c>
       <c r="R22" t="n">
-        <v>6448509</v>
+        <v>6448377</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2968,13 +2964,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124975270</v>
+        <v>125148007</v>
       </c>
       <c r="B23" t="n">
-        <v>5361</v>
+        <v>95228</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,41 +3005,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101728</v>
+        <v>2779</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540143</v>
+        <v>540181</v>
       </c>
       <c r="R23" t="n">
-        <v>6448377</v>
+        <v>6448506</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,17 +3075,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125147960</v>
+        <v>125148013</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>95434</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3112,31 +3112,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540183</v>
+        <v>540181</v>
       </c>
       <c r="R24" t="n">
-        <v>6448467</v>
+        <v>6448509</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3182,17 +3182,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3211,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125148007</v>
+        <v>125147960</v>
       </c>
       <c r="B25" t="n">
-        <v>95228</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3223,31 +3219,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2779</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3255,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540181</v>
+        <v>540183</v>
       </c>
       <c r="R25" t="n">
-        <v>6448506</v>
+        <v>6448467</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3293,13 +3289,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125147970</v>
+        <v>125148042</v>
       </c>
       <c r="B26" t="n">
-        <v>100188</v>
+        <v>95423</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540192</v>
+        <v>540179</v>
       </c>
       <c r="R26" t="n">
-        <v>6448454</v>
+        <v>6448499</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125148042</v>
+        <v>125148071</v>
       </c>
       <c r="B27" t="n">
-        <v>95423</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540179</v>
+        <v>540190</v>
       </c>
       <c r="R27" t="n">
-        <v>6448499</v>
+        <v>6448516</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125148071</v>
+        <v>125147970</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>100188</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540190</v>
+        <v>540192</v>
       </c>
       <c r="R28" t="n">
-        <v>6448516</v>
+        <v>6448454</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,6 +3637,790 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125366402</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>540235</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6448561</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125366661</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>540315</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6448561</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125366597</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>540304</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6448563</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125366523</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>540310</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6448533</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125366296</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95434</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>540223</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6448441</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125366562</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Biberget, Biberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>540372</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6448589</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125366314</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95438</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>540203</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6448451</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124971310</v>
+        <v>124977940</v>
       </c>
       <c r="B9" t="n">
-        <v>95434</v>
+        <v>105029</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540177</v>
+        <v>540095</v>
       </c>
       <c r="R9" t="n">
-        <v>6448472</v>
+        <v>6448266</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1631,6 +1631,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124972268</v>
+        <v>124968982</v>
       </c>
       <c r="B10" t="n">
-        <v>95423</v>
+        <v>105029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,21 +1678,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1702,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540161</v>
+        <v>540253</v>
       </c>
       <c r="R10" t="n">
-        <v>6448467</v>
+        <v>6448511</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124979217</v>
+        <v>124972268</v>
       </c>
       <c r="B11" t="n">
-        <v>9398</v>
+        <v>95423</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,21 +1780,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101246</v>
+        <v>2671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540120</v>
+        <v>540161</v>
       </c>
       <c r="R11" t="n">
-        <v>6448309</v>
+        <v>6448467</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124978294</v>
+        <v>124971310</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>95434</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,25 +1878,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1906,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540048</v>
+        <v>540177</v>
       </c>
       <c r="R12" t="n">
-        <v>6448338</v>
+        <v>6448472</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,10 +1968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124976354</v>
+        <v>124976998</v>
       </c>
       <c r="B13" t="n">
-        <v>57995</v>
+        <v>105029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,25 +1980,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +2008,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540222</v>
+        <v>540248</v>
       </c>
       <c r="R13" t="n">
-        <v>6448401</v>
+        <v>6448393</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124976998</v>
+        <v>124972706</v>
       </c>
       <c r="B14" t="n">
-        <v>105029</v>
+        <v>100188</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,16 +2086,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2105,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540248</v>
+        <v>540171</v>
       </c>
       <c r="R14" t="n">
-        <v>6448393</v>
+        <v>6448423</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2167,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124972164</v>
+        <v>124971034</v>
       </c>
       <c r="B15" t="n">
-        <v>30115</v>
+        <v>95434</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540191</v>
+        <v>540178</v>
       </c>
       <c r="R15" t="n">
-        <v>6448460</v>
+        <v>6448461</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2269,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124971516</v>
+        <v>124972164</v>
       </c>
       <c r="B16" t="n">
-        <v>95436</v>
+        <v>30115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2666</v>
+        <v>200985</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540172</v>
+        <v>540191</v>
       </c>
       <c r="R16" t="n">
-        <v>6448475</v>
+        <v>6448460</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2371,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124971034</v>
+        <v>124971516</v>
       </c>
       <c r="B17" t="n">
-        <v>95434</v>
+        <v>95436</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,16 +2392,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540178</v>
+        <v>540172</v>
       </c>
       <c r="R17" t="n">
-        <v>6448461</v>
+        <v>6448475</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2473,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124968982</v>
+        <v>124978294</v>
       </c>
       <c r="B18" t="n">
-        <v>105029</v>
+        <v>91032</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,25 +2490,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,13 +2518,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540253</v>
+        <v>540048</v>
       </c>
       <c r="R18" t="n">
-        <v>6448511</v>
+        <v>6448338</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124977940</v>
+        <v>124979217</v>
       </c>
       <c r="B19" t="n">
-        <v>105029</v>
+        <v>9398</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,21 +2596,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221141</v>
+        <v>101246</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>540120</v>
       </c>
       <c r="R19" t="n">
-        <v>6448266</v>
+        <v>6448309</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2651,11 +2656,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124972706</v>
+        <v>124976354</v>
       </c>
       <c r="B20" t="n">
-        <v>100188</v>
+        <v>57995</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2694,25 +2694,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540171</v>
+        <v>540222</v>
       </c>
       <c r="R20" t="n">
-        <v>6448423</v>
+        <v>6448401</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124975270</v>
+        <v>125148042</v>
       </c>
       <c r="B22" t="n">
-        <v>5361</v>
+        <v>95423</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,41 +2898,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101728</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540143</v>
+        <v>540179</v>
       </c>
       <c r="R22" t="n">
-        <v>6448377</v>
+        <v>6448499</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2964,17 +2968,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125148007</v>
+        <v>124975270</v>
       </c>
       <c r="B23" t="n">
-        <v>95228</v>
+        <v>5361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,45 +3005,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2779</v>
+        <v>101728</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540181</v>
+        <v>540143</v>
       </c>
       <c r="R23" t="n">
-        <v>6448506</v>
+        <v>6448377</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3075,13 +3071,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125147960</v>
+        <v>125148071</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,31 +3219,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540183</v>
+        <v>540190</v>
       </c>
       <c r="R25" t="n">
-        <v>6448467</v>
+        <v>6448516</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3289,17 +3289,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3318,10 +3314,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125148042</v>
+        <v>125147970</v>
       </c>
       <c r="B26" t="n">
-        <v>95423</v>
+        <v>100188</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,21 +3330,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3358,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540179</v>
+        <v>540192</v>
       </c>
       <c r="R26" t="n">
-        <v>6448499</v>
+        <v>6448454</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3425,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125148071</v>
+        <v>125148007</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>95228</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3441,21 +3437,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3469,10 +3465,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540190</v>
+        <v>540181</v>
       </c>
       <c r="R27" t="n">
-        <v>6448516</v>
+        <v>6448506</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3532,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125147970</v>
+        <v>125147960</v>
       </c>
       <c r="B28" t="n">
-        <v>100188</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3544,31 +3540,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3576,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540192</v>
+        <v>540183</v>
       </c>
       <c r="R28" t="n">
-        <v>6448454</v>
+        <v>6448467</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3614,13 +3610,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125366402</v>
+        <v>125366562</v>
       </c>
       <c r="B29" t="n">
-        <v>100188</v>
+        <v>8436</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3655,37 +3655,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Biberget, Biberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540235</v>
+        <v>540372</v>
       </c>
       <c r="R29" t="n">
-        <v>6448561</v>
+        <v>6448589</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,22 +3739,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125366661</v>
+        <v>125366314</v>
       </c>
       <c r="B30" t="n">
-        <v>5361</v>
+        <v>95438</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101728</v>
+        <v>2668</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540315</v>
+        <v>540203</v>
       </c>
       <c r="R30" t="n">
-        <v>6448561</v>
+        <v>6448451</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3851,22 +3851,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125366597</v>
+        <v>125366523</v>
       </c>
       <c r="B31" t="n">
-        <v>100188</v>
+        <v>5361</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3875,25 +3875,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>101728</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540304</v>
+        <v>540310</v>
       </c>
       <c r="R31" t="n">
-        <v>6448563</v>
+        <v>6448533</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3975,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125366523</v>
+        <v>125366402</v>
       </c>
       <c r="B32" t="n">
-        <v>5361</v>
+        <v>100188</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3987,25 +3987,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101728</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540310</v>
+        <v>540235</v>
       </c>
       <c r="R32" t="n">
-        <v>6448533</v>
+        <v>6448561</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125366562</v>
+        <v>125366597</v>
       </c>
       <c r="B34" t="n">
-        <v>8436</v>
+        <v>100188</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4215,37 +4215,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Biberget, Biberget, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540372</v>
+        <v>540304</v>
       </c>
       <c r="R34" t="n">
-        <v>6448589</v>
+        <v>6448563</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4299,22 +4299,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125366314</v>
+        <v>125366661</v>
       </c>
       <c r="B35" t="n">
-        <v>95438</v>
+        <v>5361</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4323,25 +4323,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2668</v>
+        <v>101728</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540203</v>
+        <v>540315</v>
       </c>
       <c r="R35" t="n">
-        <v>6448451</v>
+        <v>6448561</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4411,12 +4411,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4421,6 +4421,122 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125364467</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>540168</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6448533</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124977940</v>
+        <v>124972164</v>
       </c>
       <c r="B9" t="n">
-        <v>105029</v>
+        <v>30115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>200985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540095</v>
+        <v>540191</v>
       </c>
       <c r="R9" t="n">
-        <v>6448266</v>
+        <v>6448460</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1631,11 +1631,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124968982</v>
+        <v>124972268</v>
       </c>
       <c r="B10" t="n">
-        <v>105029</v>
+        <v>95423</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,21 +1673,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1702,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540253</v>
+        <v>540161</v>
       </c>
       <c r="R10" t="n">
-        <v>6448511</v>
+        <v>6448467</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1764,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124972268</v>
+        <v>124971516</v>
       </c>
       <c r="B11" t="n">
-        <v>95423</v>
+        <v>95436</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,21 +1775,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1804,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540161</v>
+        <v>540172</v>
       </c>
       <c r="R11" t="n">
-        <v>6448467</v>
+        <v>6448475</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124971310</v>
+        <v>124968982</v>
       </c>
       <c r="B12" t="n">
-        <v>95434</v>
+        <v>105029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1906,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540177</v>
+        <v>540253</v>
       </c>
       <c r="R12" t="n">
-        <v>6448472</v>
+        <v>6448511</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1968,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124976998</v>
+        <v>124979217</v>
       </c>
       <c r="B13" t="n">
-        <v>105029</v>
+        <v>9398</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>101246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540248</v>
+        <v>540120</v>
       </c>
       <c r="R13" t="n">
-        <v>6448393</v>
+        <v>6448309</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2172,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124971034</v>
+        <v>124978294</v>
       </c>
       <c r="B15" t="n">
-        <v>95434</v>
+        <v>91032</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,25 +2179,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,13 +2207,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540178</v>
+        <v>540048</v>
       </c>
       <c r="R15" t="n">
-        <v>6448461</v>
+        <v>6448338</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124972164</v>
+        <v>124971310</v>
       </c>
       <c r="B16" t="n">
-        <v>30115</v>
+        <v>95434</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,21 +2285,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540191</v>
+        <v>540177</v>
       </c>
       <c r="R16" t="n">
-        <v>6448460</v>
+        <v>6448472</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124971516</v>
+        <v>124976998</v>
       </c>
       <c r="B17" t="n">
-        <v>95436</v>
+        <v>105029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,21 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2666</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540172</v>
+        <v>540248</v>
       </c>
       <c r="R17" t="n">
-        <v>6448475</v>
+        <v>6448393</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2478,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124978294</v>
+        <v>124971034</v>
       </c>
       <c r="B18" t="n">
-        <v>91032</v>
+        <v>95434</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,25 +2485,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,13 +2513,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540048</v>
+        <v>540178</v>
       </c>
       <c r="R18" t="n">
-        <v>6448338</v>
+        <v>6448461</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124979217</v>
+        <v>124976354</v>
       </c>
       <c r="B19" t="n">
-        <v>9398</v>
+        <v>57995</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,25 +2587,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101246</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,13 +2615,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540120</v>
+        <v>540222</v>
       </c>
       <c r="R19" t="n">
-        <v>6448309</v>
+        <v>6448401</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124976354</v>
+        <v>124977940</v>
       </c>
       <c r="B20" t="n">
-        <v>57995</v>
+        <v>105029</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2694,25 +2689,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>221141</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,13 +2717,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540222</v>
+        <v>540095</v>
       </c>
       <c r="R20" t="n">
-        <v>6448401</v>
+        <v>6448266</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2758,6 +2753,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125148042</v>
+        <v>125148007</v>
       </c>
       <c r="B22" t="n">
-        <v>95423</v>
+        <v>95228</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540179</v>
+        <v>540181</v>
       </c>
       <c r="R22" t="n">
-        <v>6448499</v>
+        <v>6448506</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124975270</v>
+        <v>125148042</v>
       </c>
       <c r="B23" t="n">
-        <v>5361</v>
+        <v>95423</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,41 +3005,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101728</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540143</v>
+        <v>540179</v>
       </c>
       <c r="R23" t="n">
-        <v>6448377</v>
+        <v>6448499</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,17 +3075,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125148013</v>
+        <v>125148071</v>
       </c>
       <c r="B24" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540181</v>
+        <v>540190</v>
       </c>
       <c r="R24" t="n">
-        <v>6448509</v>
+        <v>6448516</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125148071</v>
+        <v>125147970</v>
       </c>
       <c r="B25" t="n">
-        <v>100279</v>
+        <v>100188</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540190</v>
+        <v>540192</v>
       </c>
       <c r="R25" t="n">
-        <v>6448516</v>
+        <v>6448454</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125147970</v>
+        <v>125147960</v>
       </c>
       <c r="B26" t="n">
-        <v>100188</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,31 +3326,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540192</v>
+        <v>540183</v>
       </c>
       <c r="R26" t="n">
-        <v>6448454</v>
+        <v>6448467</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3396,13 +3396,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3421,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125148007</v>
+        <v>124975270</v>
       </c>
       <c r="B27" t="n">
-        <v>95228</v>
+        <v>5361</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,45 +3437,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2779</v>
+        <v>101728</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540181</v>
+        <v>540143</v>
       </c>
       <c r="R27" t="n">
-        <v>6448506</v>
+        <v>6448377</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3503,13 +3503,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3528,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125147960</v>
+        <v>125148013</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>95434</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,31 +3544,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3572,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540183</v>
+        <v>540181</v>
       </c>
       <c r="R28" t="n">
-        <v>6448467</v>
+        <v>6448509</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3610,17 +3614,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125366562</v>
+        <v>125366296</v>
       </c>
       <c r="B29" t="n">
-        <v>8436</v>
+        <v>95434</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3655,34 +3655,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>2667</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Biberget, Biberget, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540372</v>
+        <v>540223</v>
       </c>
       <c r="R29" t="n">
-        <v>6448589</v>
+        <v>6448441</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,22 +3739,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125366314</v>
+        <v>125366523</v>
       </c>
       <c r="B30" t="n">
-        <v>95438</v>
+        <v>5361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2668</v>
+        <v>101728</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540203</v>
+        <v>540310</v>
       </c>
       <c r="R30" t="n">
-        <v>6448451</v>
+        <v>6448533</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3851,19 +3851,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125366523</v>
+        <v>125366661</v>
       </c>
       <c r="B31" t="n">
         <v>5361</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540310</v>
+        <v>540315</v>
       </c>
       <c r="R31" t="n">
-        <v>6448533</v>
+        <v>6448561</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125366402</v>
+        <v>125366562</v>
       </c>
       <c r="B32" t="n">
-        <v>100188</v>
+        <v>8436</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,37 +3991,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Biberget, Biberget, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540235</v>
+        <v>540372</v>
       </c>
       <c r="R32" t="n">
-        <v>6448561</v>
+        <v>6448589</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,22 +4075,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125366296</v>
+        <v>125366402</v>
       </c>
       <c r="B33" t="n">
-        <v>95434</v>
+        <v>100188</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4103,21 +4103,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540223</v>
+        <v>540235</v>
       </c>
       <c r="R33" t="n">
-        <v>6448441</v>
+        <v>6448561</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,12 +4187,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125366661</v>
+        <v>125366314</v>
       </c>
       <c r="B35" t="n">
-        <v>5361</v>
+        <v>95438</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4323,25 +4323,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101728</v>
+        <v>2668</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540315</v>
+        <v>540203</v>
       </c>
       <c r="R35" t="n">
-        <v>6448561</v>
+        <v>6448451</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4411,12 +4411,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4537,6 +4537,108 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125499677</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57914</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>540224</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6448406</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124972164</v>
+        <v>124971034</v>
       </c>
       <c r="B9" t="n">
-        <v>30115</v>
+        <v>95602</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540191</v>
+        <v>540178</v>
       </c>
       <c r="R9" t="n">
-        <v>6448460</v>
+        <v>6448461</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124972268</v>
+        <v>124979217</v>
       </c>
       <c r="B10" t="n">
-        <v>95423</v>
+        <v>9398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>101246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540161</v>
+        <v>540120</v>
       </c>
       <c r="R10" t="n">
-        <v>6448467</v>
+        <v>6448309</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124971516</v>
+        <v>124978294</v>
       </c>
       <c r="B11" t="n">
-        <v>95436</v>
+        <v>91186</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2666</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540172</v>
+        <v>540048</v>
       </c>
       <c r="R11" t="n">
-        <v>6448475</v>
+        <v>6448338</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>124968982</v>
       </c>
       <c r="B12" t="n">
-        <v>105029</v>
+        <v>105205</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124979217</v>
+        <v>124972268</v>
       </c>
       <c r="B13" t="n">
-        <v>9398</v>
+        <v>95591</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101246</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540120</v>
+        <v>540161</v>
       </c>
       <c r="R13" t="n">
-        <v>6448309</v>
+        <v>6448467</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124972706</v>
+        <v>124976354</v>
       </c>
       <c r="B14" t="n">
-        <v>100188</v>
+        <v>58111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,25 +2077,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540171</v>
+        <v>540222</v>
       </c>
       <c r="R14" t="n">
-        <v>6448423</v>
+        <v>6448401</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124978294</v>
+        <v>124977940</v>
       </c>
       <c r="B15" t="n">
-        <v>91032</v>
+        <v>105205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,25 +2179,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540048</v>
+        <v>540095</v>
       </c>
       <c r="R15" t="n">
-        <v>6448338</v>
+        <v>6448266</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,6 +2243,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124971310</v>
+        <v>124972164</v>
       </c>
       <c r="B16" t="n">
-        <v>95434</v>
+        <v>30128</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>200985</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540177</v>
+        <v>540191</v>
       </c>
       <c r="R16" t="n">
-        <v>6448472</v>
+        <v>6448460</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2374,7 +2379,7 @@
         <v>124976998</v>
       </c>
       <c r="B17" t="n">
-        <v>105029</v>
+        <v>105205</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124971034</v>
+        <v>124972706</v>
       </c>
       <c r="B18" t="n">
-        <v>95434</v>
+        <v>100358</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540178</v>
+        <v>540171</v>
       </c>
       <c r="R18" t="n">
-        <v>6448461</v>
+        <v>6448423</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2575,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124976354</v>
+        <v>124971310</v>
       </c>
       <c r="B19" t="n">
-        <v>57995</v>
+        <v>95602</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,25 +2592,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>2667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,13 +2620,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540222</v>
+        <v>540177</v>
       </c>
       <c r="R19" t="n">
-        <v>6448401</v>
+        <v>6448472</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2677,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124977940</v>
+        <v>124971516</v>
       </c>
       <c r="B20" t="n">
-        <v>105029</v>
+        <v>95604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2717,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540095</v>
+        <v>540172</v>
       </c>
       <c r="R20" t="n">
-        <v>6448266</v>
+        <v>6448475</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2753,11 +2758,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,7 +2787,7 @@
         <v>125009086</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125148007</v>
+        <v>125148071</v>
       </c>
       <c r="B22" t="n">
-        <v>95228</v>
+        <v>100451</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540181</v>
+        <v>540190</v>
       </c>
       <c r="R22" t="n">
-        <v>6448506</v>
+        <v>6448516</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125148042</v>
+        <v>124975270</v>
       </c>
       <c r="B23" t="n">
-        <v>95423</v>
+        <v>5361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,45 +3005,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2671</v>
+        <v>101728</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540179</v>
+        <v>540143</v>
       </c>
       <c r="R23" t="n">
-        <v>6448499</v>
+        <v>6448377</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3075,13 +3071,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125148071</v>
+        <v>125148013</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
+        <v>95602</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540190</v>
+        <v>540181</v>
       </c>
       <c r="R24" t="n">
-        <v>6448516</v>
+        <v>6448509</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125147970</v>
+        <v>125147960</v>
       </c>
       <c r="B25" t="n">
-        <v>100188</v>
+        <v>57632</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,31 +3219,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540192</v>
+        <v>540183</v>
       </c>
       <c r="R25" t="n">
-        <v>6448454</v>
+        <v>6448467</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3289,13 +3289,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3314,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125147960</v>
+        <v>125147970</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>100358</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,31 +3330,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3358,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540183</v>
+        <v>540192</v>
       </c>
       <c r="R26" t="n">
-        <v>6448467</v>
+        <v>6448454</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3396,17 +3400,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124975270</v>
+        <v>125148007</v>
       </c>
       <c r="B27" t="n">
-        <v>5361</v>
+        <v>95396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3437,41 +3437,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101728</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540143</v>
+        <v>540181</v>
       </c>
       <c r="R27" t="n">
-        <v>6448377</v>
+        <v>6448506</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3503,17 +3507,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125148013</v>
+        <v>125148042</v>
       </c>
       <c r="B28" t="n">
-        <v>95434</v>
+        <v>95591</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540181</v>
+        <v>540179</v>
       </c>
       <c r="R28" t="n">
-        <v>6448509</v>
+        <v>6448499</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125366296</v>
+        <v>125366402</v>
       </c>
       <c r="B29" t="n">
-        <v>95434</v>
+        <v>100358</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540223</v>
+        <v>540235</v>
       </c>
       <c r="R29" t="n">
-        <v>6448441</v>
+        <v>6448561</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,22 +3739,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125366523</v>
+        <v>125366597</v>
       </c>
       <c r="B30" t="n">
-        <v>5361</v>
+        <v>100358</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101728</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540310</v>
+        <v>540304</v>
       </c>
       <c r="R30" t="n">
-        <v>6448533</v>
+        <v>6448563</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3975,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125366562</v>
+        <v>125366523</v>
       </c>
       <c r="B32" t="n">
-        <v>8436</v>
+        <v>5361</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3987,41 +3987,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>101728</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Biberget, Biberget, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540372</v>
+        <v>540310</v>
       </c>
       <c r="R32" t="n">
-        <v>6448589</v>
+        <v>6448533</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,22 +4075,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125366402</v>
+        <v>125366296</v>
       </c>
       <c r="B33" t="n">
-        <v>100188</v>
+        <v>95602</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4103,21 +4103,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540235</v>
+        <v>540223</v>
       </c>
       <c r="R33" t="n">
-        <v>6448561</v>
+        <v>6448441</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,22 +4187,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125366597</v>
+        <v>125366562</v>
       </c>
       <c r="B34" t="n">
-        <v>100188</v>
+        <v>8436</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4215,37 +4215,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Biberget, Biberget, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540304</v>
+        <v>540372</v>
       </c>
       <c r="R34" t="n">
-        <v>6448563</v>
+        <v>6448589</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4299,12 +4299,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4314,7 +4314,7 @@
         <v>125366314</v>
       </c>
       <c r="B35" t="n">
-        <v>95438</v>
+        <v>95606</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>125364467</v>
       </c>
       <c r="B36" t="n">
-        <v>100188</v>
+        <v>100358</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124968982</v>
+        <v>124972268</v>
       </c>
       <c r="B12" t="n">
-        <v>105205</v>
+        <v>95591</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540253</v>
+        <v>540161</v>
       </c>
       <c r="R12" t="n">
-        <v>6448511</v>
+        <v>6448467</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124972268</v>
+        <v>124968982</v>
       </c>
       <c r="B13" t="n">
-        <v>95591</v>
+        <v>105205</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540161</v>
+        <v>540253</v>
       </c>
       <c r="R13" t="n">
-        <v>6448467</v>
+        <v>6448511</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124971034</v>
+        <v>124979217</v>
       </c>
       <c r="B9" t="n">
-        <v>95602</v>
+        <v>9398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540178</v>
+        <v>540120</v>
       </c>
       <c r="R9" t="n">
-        <v>6448461</v>
+        <v>6448309</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124979217</v>
+        <v>124972268</v>
       </c>
       <c r="B10" t="n">
-        <v>9398</v>
+        <v>95591</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101246</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540120</v>
+        <v>540161</v>
       </c>
       <c r="R10" t="n">
-        <v>6448309</v>
+        <v>6448467</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124978294</v>
+        <v>124968982</v>
       </c>
       <c r="B11" t="n">
-        <v>91186</v>
+        <v>105205</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540048</v>
+        <v>540253</v>
       </c>
       <c r="R11" t="n">
-        <v>6448338</v>
+        <v>6448511</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124972268</v>
+        <v>124971310</v>
       </c>
       <c r="B12" t="n">
-        <v>95591</v>
+        <v>95602</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540161</v>
+        <v>540177</v>
       </c>
       <c r="R12" t="n">
-        <v>6448467</v>
+        <v>6448472</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124968982</v>
+        <v>124978294</v>
       </c>
       <c r="B13" t="n">
-        <v>105205</v>
+        <v>91186</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,25 +1975,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540253</v>
+        <v>540048</v>
       </c>
       <c r="R13" t="n">
-        <v>6448511</v>
+        <v>6448338</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124976354</v>
+        <v>124976998</v>
       </c>
       <c r="B14" t="n">
-        <v>58111</v>
+        <v>105205</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,25 +2077,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103018</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540222</v>
+        <v>540248</v>
       </c>
       <c r="R14" t="n">
-        <v>6448401</v>
+        <v>6448393</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124977940</v>
+        <v>124971516</v>
       </c>
       <c r="B15" t="n">
-        <v>105205</v>
+        <v>95604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>2666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540095</v>
+        <v>540172</v>
       </c>
       <c r="R15" t="n">
-        <v>6448266</v>
+        <v>6448475</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2243,11 +2243,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124972164</v>
+        <v>124972706</v>
       </c>
       <c r="B16" t="n">
-        <v>30128</v>
+        <v>100358</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,21 +2285,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200985</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540191</v>
+        <v>540171</v>
       </c>
       <c r="R16" t="n">
-        <v>6448460</v>
+        <v>6448423</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124976998</v>
+        <v>124971034</v>
       </c>
       <c r="B17" t="n">
-        <v>105205</v>
+        <v>95602</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,21 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540248</v>
+        <v>540178</v>
       </c>
       <c r="R17" t="n">
-        <v>6448393</v>
+        <v>6448461</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2478,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124972706</v>
+        <v>124976354</v>
       </c>
       <c r="B18" t="n">
-        <v>100358</v>
+        <v>58111</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,25 +2485,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,13 +2513,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540171</v>
+        <v>540222</v>
       </c>
       <c r="R18" t="n">
-        <v>6448423</v>
+        <v>6448401</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124971310</v>
+        <v>124977940</v>
       </c>
       <c r="B19" t="n">
-        <v>95602</v>
+        <v>105205</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,21 +2591,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>221141</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540177</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>6448472</v>
+        <v>6448266</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2656,6 +2651,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124971516</v>
+        <v>124972164</v>
       </c>
       <c r="B20" t="n">
-        <v>95604</v>
+        <v>30128</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>200985</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540172</v>
+        <v>540191</v>
       </c>
       <c r="R20" t="n">
-        <v>6448475</v>
+        <v>6448460</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125148071</v>
+        <v>124975270</v>
       </c>
       <c r="B22" t="n">
-        <v>100451</v>
+        <v>5361</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,45 +2898,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540190</v>
+        <v>540143</v>
       </c>
       <c r="R22" t="n">
-        <v>6448516</v>
+        <v>6448377</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2968,13 +2964,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124975270</v>
+        <v>125148007</v>
       </c>
       <c r="B23" t="n">
-        <v>5361</v>
+        <v>95396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,41 +3005,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101728</v>
+        <v>2779</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540143</v>
+        <v>540181</v>
       </c>
       <c r="R23" t="n">
-        <v>6448377</v>
+        <v>6448506</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,17 +3075,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125148013</v>
+        <v>125148071</v>
       </c>
       <c r="B24" t="n">
-        <v>95602</v>
+        <v>100451</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540181</v>
+        <v>540190</v>
       </c>
       <c r="R24" t="n">
-        <v>6448509</v>
+        <v>6448516</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125147960</v>
+        <v>125148042</v>
       </c>
       <c r="B25" t="n">
-        <v>57632</v>
+        <v>95591</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,31 +3219,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540183</v>
+        <v>540179</v>
       </c>
       <c r="R25" t="n">
-        <v>6448467</v>
+        <v>6448499</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3289,17 +3289,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3318,10 +3314,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125147970</v>
+        <v>125148013</v>
       </c>
       <c r="B26" t="n">
-        <v>100358</v>
+        <v>95602</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,21 +3330,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3358,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540192</v>
+        <v>540181</v>
       </c>
       <c r="R26" t="n">
-        <v>6448454</v>
+        <v>6448509</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3425,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125148007</v>
+        <v>125147960</v>
       </c>
       <c r="B27" t="n">
-        <v>95396</v>
+        <v>57632</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3437,31 +3433,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2779</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3469,10 +3465,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540181</v>
+        <v>540183</v>
       </c>
       <c r="R27" t="n">
-        <v>6448506</v>
+        <v>6448467</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3507,13 +3503,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125148042</v>
+        <v>125147970</v>
       </c>
       <c r="B28" t="n">
-        <v>95591</v>
+        <v>100358</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540179</v>
+        <v>540192</v>
       </c>
       <c r="R28" t="n">
-        <v>6448499</v>
+        <v>6448454</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125366402</v>
+        <v>125366597</v>
       </c>
       <c r="B29" t="n">
         <v>100358</v>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540235</v>
+        <v>540304</v>
       </c>
       <c r="R29" t="n">
-        <v>6448561</v>
+        <v>6448563</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125366597</v>
+        <v>125366661</v>
       </c>
       <c r="B30" t="n">
-        <v>100358</v>
+        <v>5361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>101728</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540304</v>
+        <v>540315</v>
       </c>
       <c r="R30" t="n">
-        <v>6448563</v>
+        <v>6448561</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125366661</v>
+        <v>125366314</v>
       </c>
       <c r="B31" t="n">
-        <v>5361</v>
+        <v>95606</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3875,25 +3875,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101728</v>
+        <v>2668</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540315</v>
+        <v>540203</v>
       </c>
       <c r="R31" t="n">
-        <v>6448561</v>
+        <v>6448451</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,12 +3963,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125366314</v>
+        <v>125366402</v>
       </c>
       <c r="B35" t="n">
-        <v>95606</v>
+        <v>100358</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4327,21 +4327,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540203</v>
+        <v>540235</v>
       </c>
       <c r="R35" t="n">
-        <v>6448451</v>
+        <v>6448561</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4411,12 +4411,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125147960</v>
+        <v>125147970</v>
       </c>
       <c r="B27" t="n">
-        <v>57632</v>
+        <v>100358</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,31 +3433,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540183</v>
+        <v>540192</v>
       </c>
       <c r="R27" t="n">
-        <v>6448467</v>
+        <v>6448454</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3503,17 +3503,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125147970</v>
+        <v>125147960</v>
       </c>
       <c r="B28" t="n">
-        <v>100358</v>
+        <v>57632</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3544,31 +3540,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3576,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540192</v>
+        <v>540183</v>
       </c>
       <c r="R28" t="n">
-        <v>6448454</v>
+        <v>6448467</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3614,13 +3610,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -1560,11 +1560,6 @@
       <c r="B9" t="n">
         <v>9398</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1657,15 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124972268</v>
+        <v>124968982</v>
       </c>
       <c r="B10" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,21 +1663,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,13 +1687,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540161</v>
+        <v>540253</v>
       </c>
       <c r="R10" t="n">
-        <v>6448467</v>
+        <v>6448511</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,16 +1749,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124968982</v>
+        <v>124976998</v>
       </c>
       <c r="B11" t="n">
         <v>105205</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1799,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540253</v>
+        <v>540248</v>
       </c>
       <c r="R11" t="n">
-        <v>6448511</v>
+        <v>6448393</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1866,11 +1851,6 @@
       <c r="B12" t="n">
         <v>95602</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1963,37 +1943,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124978294</v>
+        <v>124972706</v>
       </c>
       <c r="B13" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,13 +1978,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540048</v>
+        <v>540171</v>
       </c>
       <c r="R13" t="n">
-        <v>6448338</v>
+        <v>6448423</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,15 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124976998</v>
+        <v>124972268</v>
       </c>
       <c r="B14" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,21 +2051,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,13 +2075,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540248</v>
+        <v>540161</v>
       </c>
       <c r="R14" t="n">
-        <v>6448393</v>
+        <v>6448467</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2167,15 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124971516</v>
+        <v>124977940</v>
       </c>
       <c r="B15" t="n">
-        <v>95604</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105205</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2666</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540172</v>
+        <v>540095</v>
       </c>
       <c r="R15" t="n">
-        <v>6448475</v>
+        <v>6448266</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2243,6 +2208,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,15 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124972706</v>
+        <v>124971516</v>
       </c>
       <c r="B16" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95604</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,21 +2250,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>2666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540171</v>
+        <v>540172</v>
       </c>
       <c r="R16" t="n">
-        <v>6448423</v>
+        <v>6448475</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2376,11 +2341,6 @@
       <c r="B17" t="n">
         <v>95602</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>LC</t>
@@ -2473,37 +2433,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124976354</v>
+        <v>124972164</v>
       </c>
       <c r="B18" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>30128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>200985</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,13 +2468,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540222</v>
+        <v>540191</v>
       </c>
       <c r="R18" t="n">
-        <v>6448401</v>
+        <v>6448460</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,37 +2530,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124977940</v>
+        <v>124976354</v>
       </c>
       <c r="B19" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221141</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>540222</v>
       </c>
       <c r="R19" t="n">
-        <v>6448266</v>
+        <v>6448401</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2651,11 +2601,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,37 +2627,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124972164</v>
+        <v>124978294</v>
       </c>
       <c r="B20" t="n">
-        <v>30128</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>200985</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,13 +2662,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540191</v>
+        <v>540048</v>
       </c>
       <c r="R20" t="n">
-        <v>6448460</v>
+        <v>6448338</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,11 +2729,6 @@
       <c r="B21" t="n">
         <v>79565</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2886,53 +2821,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124975270</v>
+        <v>125148042</v>
       </c>
       <c r="B22" t="n">
-        <v>5361</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95645</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101728</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540143</v>
+        <v>540179</v>
       </c>
       <c r="R22" t="n">
-        <v>6448377</v>
+        <v>6448499</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2964,17 +2898,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,15 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125148007</v>
+        <v>125147970</v>
       </c>
       <c r="B23" t="n">
-        <v>95396</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,21 +2934,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3037,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540181</v>
+        <v>540192</v>
       </c>
       <c r="R23" t="n">
-        <v>6448506</v>
+        <v>6448454</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3100,15 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125148071</v>
+        <v>125148007</v>
       </c>
       <c r="B24" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,21 +3036,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540190</v>
+        <v>540181</v>
       </c>
       <c r="R24" t="n">
-        <v>6448516</v>
+        <v>6448506</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,15 +3127,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125148042</v>
+        <v>125148071</v>
       </c>
       <c r="B25" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3251,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540179</v>
+        <v>540190</v>
       </c>
       <c r="R25" t="n">
-        <v>6448499</v>
+        <v>6448516</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3314,57 +3229,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125148013</v>
+        <v>124975270</v>
       </c>
       <c r="B26" t="n">
-        <v>95602</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>101728</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Solbacken, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540181</v>
+        <v>540143</v>
       </c>
       <c r="R26" t="n">
-        <v>6448509</v>
+        <v>6448377</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3396,13 +3302,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3421,15 +3331,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125147970</v>
+        <v>125148013</v>
       </c>
       <c r="B27" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3437,21 +3342,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3465,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540192</v>
+        <v>540181</v>
       </c>
       <c r="R27" t="n">
-        <v>6448454</v>
+        <v>6448509</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3531,12 +3436,7 @@
         <v>125147960</v>
       </c>
       <c r="B28" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3639,15 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125366597</v>
+        <v>125366314</v>
       </c>
       <c r="B29" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3679,13 +3574,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540304</v>
+        <v>540203</v>
       </c>
       <c r="R29" t="n">
-        <v>6448563</v>
+        <v>6448451</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3714,7 +3609,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3619,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,28 +3634,23 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125366661</v>
+        <v>125366523</v>
       </c>
       <c r="B30" t="n">
         <v>5361</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3791,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540315</v>
+        <v>540310</v>
       </c>
       <c r="R30" t="n">
-        <v>6448561</v>
+        <v>6448533</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3826,7 +3716,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3836,7 +3726,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,15 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125366314</v>
+        <v>125366562</v>
       </c>
       <c r="B31" t="n">
-        <v>95606</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,34 +3764,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2668</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Biberget, Biberget, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540203</v>
+        <v>540372</v>
       </c>
       <c r="R31" t="n">
-        <v>6448451</v>
+        <v>6448589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,7 +3823,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3948,7 +3833,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,49 +3848,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125366523</v>
+        <v>125366296</v>
       </c>
       <c r="B32" t="n">
-        <v>5361</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101728</v>
+        <v>2667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4015,13 +3895,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540310</v>
+        <v>540223</v>
       </c>
       <c r="R32" t="n">
-        <v>6448533</v>
+        <v>6448441</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,49 +3955,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125366296</v>
+        <v>125366661</v>
       </c>
       <c r="B33" t="n">
-        <v>95602</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2667</v>
+        <v>101728</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4127,13 +4002,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540223</v>
+        <v>540315</v>
       </c>
       <c r="R33" t="n">
-        <v>6448441</v>
+        <v>6448561</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4162,7 +4037,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4172,7 +4047,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,27 +4062,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125366562</v>
+        <v>125366597</v>
       </c>
       <c r="B34" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,37 +4085,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Biberget, Biberget, Ög</t>
+          <t>Nyhagen, Nyhagen, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540372</v>
+        <v>540304</v>
       </c>
       <c r="R34" t="n">
-        <v>6448589</v>
+        <v>6448563</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4274,7 +4144,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4284,7 +4154,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4299,12 +4169,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4314,12 +4184,7 @@
         <v>125366402</v>
       </c>
       <c r="B35" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4426,12 +4291,7 @@
         <v>125364467</v>
       </c>
       <c r="B36" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,12 +4402,7 @@
         <v>125499677</v>
       </c>
       <c r="B37" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -2824,7 +2824,7 @@
         <v>125148042</v>
       </c>
       <c r="B22" t="n">
-        <v>95645</v>
+        <v>95652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125147970</v>
       </c>
       <c r="B23" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>125148007</v>
       </c>
       <c r="B24" t="n">
-        <v>95450</v>
+        <v>95457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>125148071</v>
       </c>
       <c r="B25" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>125148013</v>
       </c>
       <c r="B27" t="n">
-        <v>95656</v>
+        <v>95663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>125366314</v>
       </c>
       <c r="B29" t="n">
-        <v>95660</v>
+        <v>95667</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>125366296</v>
       </c>
       <c r="B32" t="n">
-        <v>95656</v>
+        <v>95663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>125366597</v>
       </c>
       <c r="B34" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>125366402</v>
       </c>
       <c r="B35" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>125364467</v>
       </c>
       <c r="B36" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -3542,7 +3542,7 @@
         <v>125366314</v>
       </c>
       <c r="B29" t="n">
-        <v>95667</v>
+        <v>95670</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>125366296</v>
       </c>
       <c r="B32" t="n">
-        <v>95663</v>
+        <v>95666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>125366597</v>
       </c>
       <c r="B34" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>125366402</v>
       </c>
       <c r="B35" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>125364467</v>
       </c>
       <c r="B36" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>125499677</v>
       </c>
       <c r="B37" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -3542,7 +3542,7 @@
         <v>125366314</v>
       </c>
       <c r="B29" t="n">
-        <v>95670</v>
+        <v>95674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>125366296</v>
       </c>
       <c r="B32" t="n">
-        <v>95666</v>
+        <v>95670</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>125366597</v>
       </c>
       <c r="B34" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>125366402</v>
       </c>
       <c r="B35" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>125364467</v>
       </c>
       <c r="B36" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -3542,7 +3542,7 @@
         <v>125366314</v>
       </c>
       <c r="B29" t="n">
-        <v>95674</v>
+        <v>95675</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>125366296</v>
       </c>
       <c r="B32" t="n">
-        <v>95670</v>
+        <v>95671</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>125366597</v>
       </c>
       <c r="B34" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>125366402</v>
       </c>
       <c r="B35" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>125364467</v>
       </c>
       <c r="B36" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4402,7 +4402,7 @@
         <v>125499677</v>
       </c>
       <c r="B37" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92447</v>
+        <v>92521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127081927</v>
+        <v>127081948</v>
       </c>
       <c r="B39" t="n">
-        <v>91265</v>
+        <v>95768</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540175</v>
+        <v>540060</v>
       </c>
       <c r="R39" t="n">
-        <v>6448411</v>
+        <v>6448311</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4690,32 +4690,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127081948</v>
+        <v>127081927</v>
       </c>
       <c r="B40" t="n">
-        <v>95693</v>
+        <v>91339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540060</v>
+        <v>540175</v>
       </c>
       <c r="R40" t="n">
-        <v>6448311</v>
+        <v>6448411</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4787,10 +4787,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127081969</v>
+        <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95487</v>
+        <v>95768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540121</v>
+        <v>540087</v>
       </c>
       <c r="R41" t="n">
-        <v>6448349</v>
+        <v>6448342</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127081956</v>
+        <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95693</v>
+        <v>95562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4895,21 +4895,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540087</v>
+        <v>540121</v>
       </c>
       <c r="R42" t="n">
-        <v>6448342</v>
+        <v>6448349</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4984,7 +4984,7 @@
         <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>79360</v>
+        <v>79391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>95810</v>
+        <v>95885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>127081916</v>
       </c>
       <c r="B45" t="n">
-        <v>91807</v>
+        <v>91881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081964</v>
       </c>
       <c r="B46" t="n">
-        <v>95487</v>
+        <v>95562</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B47" t="n">
-        <v>74998</v>
+        <v>95768</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R47" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081957</v>
+        <v>127081963</v>
       </c>
       <c r="B48" t="n">
-        <v>95487</v>
+        <v>95768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540098</v>
+        <v>540121</v>
       </c>
       <c r="R48" t="n">
-        <v>6448341</v>
+        <v>6448366</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081949</v>
+        <v>127081957</v>
       </c>
       <c r="B49" t="n">
-        <v>30129</v>
+        <v>95562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>200985</v>
+        <v>2779</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540052</v>
+        <v>540098</v>
       </c>
       <c r="R49" t="n">
-        <v>6448313</v>
+        <v>6448341</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,32 +5660,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081963</v>
+        <v>127081932</v>
       </c>
       <c r="B50" t="n">
-        <v>95693</v>
+        <v>75057</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540121</v>
+        <v>540159</v>
       </c>
       <c r="R50" t="n">
-        <v>6448366</v>
+        <v>6448374</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081921</v>
+        <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>95693</v>
+        <v>30129</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2667</v>
+        <v>200985</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540200</v>
+        <v>540052</v>
       </c>
       <c r="R51" t="n">
-        <v>6448453</v>
+        <v>6448313</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081959</v>
+        <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95487</v>
+        <v>95757</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540103</v>
+        <v>540074</v>
       </c>
       <c r="R52" t="n">
-        <v>6448344</v>
+        <v>6448313</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5951,10 +5951,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127081951</v>
+        <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95682</v>
+        <v>95562</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540074</v>
+        <v>540103</v>
       </c>
       <c r="R53" t="n">
-        <v>6448313</v>
+        <v>6448344</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6051,7 +6051,7 @@
         <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95693</v>
+        <v>95768</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>127081940</v>
       </c>
       <c r="B55" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>127081939</v>
       </c>
       <c r="B56" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>127081926</v>
       </c>
       <c r="B57" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95487</v>
+        <v>95562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127081950</v>
+        <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95682</v>
+        <v>95562</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6544,21 +6544,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540055</v>
+        <v>540086</v>
       </c>
       <c r="R59" t="n">
-        <v>6448309</v>
+        <v>6448340</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127081975</v>
+        <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95487</v>
+        <v>95757</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6641,21 +6641,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540086</v>
+        <v>540055</v>
       </c>
       <c r="R60" t="n">
-        <v>6448340</v>
+        <v>6448309</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>91807</v>
+        <v>91881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>95693</v>
+        <v>95768</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7018,32 +7018,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127081920</v>
+        <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>95682</v>
+        <v>92521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>2075</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540200</v>
+        <v>540128</v>
       </c>
       <c r="R64" t="n">
-        <v>6448453</v>
+        <v>6448358</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081967</v>
+        <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R65" t="n">
-        <v>6448358</v>
+        <v>6448453</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081952</v>
+        <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540073</v>
+        <v>540121</v>
       </c>
       <c r="R66" t="n">
-        <v>6448314</v>
+        <v>6448358</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,32 +7309,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081960</v>
+        <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>92447</v>
+        <v>95757</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540128</v>
+        <v>540073</v>
       </c>
       <c r="R67" t="n">
-        <v>6448358</v>
+        <v>6448314</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081968</v>
+        <v>127081941</v>
       </c>
       <c r="B68" t="n">
-        <v>95682</v>
+        <v>91881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540109</v>
+        <v>540160</v>
       </c>
       <c r="R68" t="n">
-        <v>6448358</v>
+        <v>6448357</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B69" t="n">
-        <v>91807</v>
+        <v>95757</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R69" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B70" t="n">
-        <v>91807</v>
+        <v>91881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R70" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081971</v>
+        <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>95682</v>
+        <v>91881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R71" t="n">
-        <v>6448345</v>
+        <v>6448293</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081928</v>
+        <v>127081974</v>
       </c>
       <c r="B72" t="n">
-        <v>95693</v>
+        <v>95562</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540172</v>
+        <v>540097</v>
       </c>
       <c r="R72" t="n">
-        <v>6448411</v>
+        <v>6448346</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081974</v>
+        <v>127081923</v>
       </c>
       <c r="B73" t="n">
-        <v>95487</v>
+        <v>95757</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540097</v>
+        <v>540198</v>
       </c>
       <c r="R73" t="n">
-        <v>6448346</v>
+        <v>6448437</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081945</v>
+        <v>127081928</v>
       </c>
       <c r="B74" t="n">
-        <v>91807</v>
+        <v>95768</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540092</v>
+        <v>540172</v>
       </c>
       <c r="R74" t="n">
-        <v>6448293</v>
+        <v>6448411</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081923</v>
+        <v>127081971</v>
       </c>
       <c r="B75" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540198</v>
+        <v>540096</v>
       </c>
       <c r="R75" t="n">
-        <v>6448437</v>
+        <v>6448345</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8185,7 +8185,7 @@
         <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>95693</v>
+        <v>95768</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92447</v>
+        <v>92521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081944</v>
+        <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>91807</v>
+        <v>95757</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R79" t="n">
-        <v>6448303</v>
+        <v>6448349</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081924</v>
+        <v>127081925</v>
       </c>
       <c r="B80" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540180</v>
+        <v>540175</v>
       </c>
       <c r="R80" t="n">
-        <v>6448428</v>
+        <v>6448426</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081925</v>
+        <v>127081944</v>
       </c>
       <c r="B81" t="n">
-        <v>95682</v>
+        <v>91881</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540175</v>
+        <v>540096</v>
       </c>
       <c r="R81" t="n">
-        <v>6448426</v>
+        <v>6448303</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081976</v>
+        <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540092</v>
+        <v>540180</v>
       </c>
       <c r="R82" t="n">
-        <v>6448349</v>
+        <v>6448428</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8880,6 +8880,6835 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127288040</v>
+      </c>
+      <c r="B83" t="n">
+        <v>105290</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>540165</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6448488</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127288064</v>
+      </c>
+      <c r="B84" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>540177</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6448499</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127288031</v>
+      </c>
+      <c r="B85" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>540180</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6448493</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127288089</v>
+      </c>
+      <c r="B86" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>540206</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6448439</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127288035</v>
+      </c>
+      <c r="B87" t="n">
+        <v>95789</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>540222</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6448525</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127288023</v>
+      </c>
+      <c r="B88" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>540237</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6448446</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127288100</v>
+      </c>
+      <c r="B89" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>540195</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6448342</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127288019</v>
+      </c>
+      <c r="B90" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>540163</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6448517</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127288060</v>
+      </c>
+      <c r="B91" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>540187</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6448488</v>
+      </c>
+      <c r="S91" t="n">
+        <v>15</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127288063</v>
+      </c>
+      <c r="B92" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>540162</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6448519</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127288025</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>540221</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6448522</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127288082</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>540219</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6448415</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127288108</v>
+      </c>
+      <c r="B95" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>540163</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6448463</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127288038</v>
+      </c>
+      <c r="B96" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>540274</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6448610</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127288011</v>
+      </c>
+      <c r="B97" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>540224</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6448404</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127288013</v>
+      </c>
+      <c r="B98" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>540189</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6448461</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127288027</v>
+      </c>
+      <c r="B99" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>540310</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6448579</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127288065</v>
+      </c>
+      <c r="B100" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>540174</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6448468</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127288074</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>540039</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6448303</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127288057</v>
+      </c>
+      <c r="B102" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>540076</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6448321</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127288101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>540333</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6448609</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>127288105</v>
+      </c>
+      <c r="B104" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>540171</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6448504</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127288028</v>
+      </c>
+      <c r="B105" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>540335</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6448550</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127288061</v>
+      </c>
+      <c r="B106" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>540180</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6448493</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127288094</v>
+      </c>
+      <c r="B107" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>540171</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6448441</v>
+      </c>
+      <c r="S107" t="n">
+        <v>15</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127288030</v>
+      </c>
+      <c r="B108" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>540192</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6448466</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127288086</v>
+      </c>
+      <c r="B109" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>540333</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6448609</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127288087</v>
+      </c>
+      <c r="B110" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>540335</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6448608</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127288014</v>
+      </c>
+      <c r="B111" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>540187</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6448463</v>
+      </c>
+      <c r="S111" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127288093</v>
+      </c>
+      <c r="B112" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>540165</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6448484</v>
+      </c>
+      <c r="S112" t="n">
+        <v>15</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127288022</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91339</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>540171</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6448436</v>
+      </c>
+      <c r="S113" t="n">
+        <v>15</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127288016</v>
+      </c>
+      <c r="B114" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>540187</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6448494</v>
+      </c>
+      <c r="S114" t="n">
+        <v>15</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127288039</v>
+      </c>
+      <c r="B115" t="n">
+        <v>105290</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>540178</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6448431</v>
+      </c>
+      <c r="S115" t="n">
+        <v>15</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127288037</v>
+      </c>
+      <c r="B116" t="n">
+        <v>95789</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>540213</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6448463</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127288059</v>
+      </c>
+      <c r="B117" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>540182</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6448496</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127288075</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>540145</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6448348</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127288084</v>
+      </c>
+      <c r="B119" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>540075</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6448321</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127288012</v>
+      </c>
+      <c r="B120" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>540210</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6448417</v>
+      </c>
+      <c r="S120" t="n">
+        <v>15</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127288076</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>540155</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6448348</v>
+      </c>
+      <c r="S121" t="n">
+        <v>15</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127288091</v>
+      </c>
+      <c r="B122" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>540169</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6448494</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127288088</v>
+      </c>
+      <c r="B123" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>540338</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6448617</v>
+      </c>
+      <c r="S123" t="n">
+        <v>15</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>127288062</v>
+      </c>
+      <c r="B124" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>540177</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6448495</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127288110</v>
+      </c>
+      <c r="B125" t="n">
+        <v>91279</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>540237</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6448446</v>
+      </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>127288069</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79391</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>540332</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6448609</v>
+      </c>
+      <c r="S126" t="n">
+        <v>15</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>127288033</v>
+      </c>
+      <c r="B127" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>540170</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6448516</v>
+      </c>
+      <c r="S127" t="n">
+        <v>15</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127288078</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>540193</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6448342</v>
+      </c>
+      <c r="S128" t="n">
+        <v>15</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127288017</v>
+      </c>
+      <c r="B129" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>540172</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6448507</v>
+      </c>
+      <c r="S129" t="n">
+        <v>15</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>127288103</v>
+      </c>
+      <c r="B130" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>540182</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6448495</v>
+      </c>
+      <c r="S130" t="n">
+        <v>15</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>127288085</v>
+      </c>
+      <c r="B131" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>540251</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6448599</v>
+      </c>
+      <c r="S131" t="n">
+        <v>15</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127288058</v>
+      </c>
+      <c r="B132" t="n">
+        <v>95768</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>540182</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6448466</v>
+      </c>
+      <c r="S132" t="n">
+        <v>15</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>127288029</v>
+      </c>
+      <c r="B133" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>540217</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6448454</v>
+      </c>
+      <c r="S133" t="n">
+        <v>15</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>127288021</v>
+      </c>
+      <c r="B134" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>540167</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6448497</v>
+      </c>
+      <c r="S134" t="n">
+        <v>15</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>127288077</v>
+      </c>
+      <c r="B135" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>540152</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6448350</v>
+      </c>
+      <c r="S135" t="n">
+        <v>15</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>127288107</v>
+      </c>
+      <c r="B136" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>540174</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6448493</v>
+      </c>
+      <c r="S136" t="n">
+        <v>15</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127288026</v>
+      </c>
+      <c r="B137" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>540319</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6448616</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127288092</v>
+      </c>
+      <c r="B138" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>540169</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6448494</v>
+      </c>
+      <c r="S138" t="n">
+        <v>15</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>127288034</v>
+      </c>
+      <c r="B139" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>540169</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6448432</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>127288090</v>
+      </c>
+      <c r="B140" t="n">
+        <v>95562</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>540163</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6448518</v>
+      </c>
+      <c r="S140" t="n">
+        <v>15</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>127288079</v>
+      </c>
+      <c r="B141" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>540310</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6448579</v>
+      </c>
+      <c r="S141" t="n">
+        <v>15</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>127288104</v>
+      </c>
+      <c r="B142" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>540169</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6448515</v>
+      </c>
+      <c r="S142" t="n">
+        <v>15</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>127288036</v>
+      </c>
+      <c r="B143" t="n">
+        <v>95789</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>540336</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6448578</v>
+      </c>
+      <c r="S143" t="n">
+        <v>15</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>127288068</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79391</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>540274</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6448603</v>
+      </c>
+      <c r="S144" t="n">
+        <v>15</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>127288018</v>
+      </c>
+      <c r="B145" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>540167</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6448513</v>
+      </c>
+      <c r="S145" t="n">
+        <v>15</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>127288024</v>
+      </c>
+      <c r="B146" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>540221</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6448466</v>
+      </c>
+      <c r="S146" t="n">
+        <v>15</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>127288080</v>
+      </c>
+      <c r="B147" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>540251</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6448423</v>
+      </c>
+      <c r="S147" t="n">
+        <v>15</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>127288015</v>
+      </c>
+      <c r="B148" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>540180</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6448493</v>
+      </c>
+      <c r="S148" t="n">
+        <v>15</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>127288032</v>
+      </c>
+      <c r="B149" t="n">
+        <v>100525</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>540179</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6448506</v>
+      </c>
+      <c r="S149" t="n">
+        <v>15</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>127288081</v>
+      </c>
+      <c r="B150" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>540243</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6448421</v>
+      </c>
+      <c r="S150" t="n">
+        <v>15</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>127288020</v>
+      </c>
+      <c r="B151" t="n">
+        <v>95772</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>540165</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6448511</v>
+      </c>
+      <c r="S151" t="n">
+        <v>15</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>127288102</v>
+      </c>
+      <c r="B152" t="n">
+        <v>95757</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>540208</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6448415</v>
+      </c>
+      <c r="S152" t="n">
+        <v>15</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92521</v>
+        <v>92527</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127081948</v>
+        <v>127081927</v>
       </c>
       <c r="B39" t="n">
-        <v>95768</v>
+        <v>91345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540060</v>
+        <v>540175</v>
       </c>
       <c r="R39" t="n">
-        <v>6448311</v>
+        <v>6448411</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4690,32 +4690,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127081927</v>
+        <v>127081948</v>
       </c>
       <c r="B40" t="n">
-        <v>91339</v>
+        <v>95774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540175</v>
+        <v>540060</v>
       </c>
       <c r="R40" t="n">
-        <v>6448411</v>
+        <v>6448311</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>79391</v>
+        <v>79394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>95885</v>
+        <v>95891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>127081916</v>
       </c>
       <c r="B45" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081964</v>
       </c>
       <c r="B46" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081921</v>
+        <v>127081932</v>
       </c>
       <c r="B47" t="n">
-        <v>95768</v>
+        <v>75060</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540200</v>
+        <v>540159</v>
       </c>
       <c r="R47" t="n">
-        <v>6448453</v>
+        <v>6448374</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081963</v>
+        <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R48" t="n">
-        <v>6448366</v>
+        <v>6448453</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081957</v>
+        <v>127081963</v>
       </c>
       <c r="B49" t="n">
-        <v>95562</v>
+        <v>95774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540098</v>
+        <v>540121</v>
       </c>
       <c r="R49" t="n">
-        <v>6448341</v>
+        <v>6448366</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,32 +5660,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081932</v>
+        <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>75057</v>
+        <v>95568</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1460</v>
+        <v>2779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540159</v>
+        <v>540098</v>
       </c>
       <c r="R50" t="n">
-        <v>6448374</v>
+        <v>6448341</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5857,7 +5857,7 @@
         <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081940</v>
+        <v>127081926</v>
       </c>
       <c r="B55" t="n">
-        <v>100525</v>
+        <v>91345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222771</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540164</v>
+        <v>540175</v>
       </c>
       <c r="R55" t="n">
-        <v>6448364</v>
+        <v>6448412</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6245,7 +6245,7 @@
         <v>127081939</v>
       </c>
       <c r="B56" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6339,32 +6339,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127081926</v>
+        <v>127081940</v>
       </c>
       <c r="B57" t="n">
-        <v>91339</v>
+        <v>100531</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>222771</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540175</v>
+        <v>540164</v>
       </c>
       <c r="R57" t="n">
-        <v>6448412</v>
+        <v>6448364</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>92521</v>
+        <v>92527</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>127081941</v>
       </c>
       <c r="B68" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081968</v>
+        <v>127081958</v>
       </c>
       <c r="B69" t="n">
-        <v>95757</v>
+        <v>91887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540109</v>
+        <v>540100</v>
       </c>
       <c r="R69" t="n">
-        <v>6448358</v>
+        <v>6448331</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B70" t="n">
-        <v>91881</v>
+        <v>95763</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R70" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7700,7 +7700,7 @@
         <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081974</v>
+        <v>127081971</v>
       </c>
       <c r="B72" t="n">
-        <v>95562</v>
+        <v>95763</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540097</v>
+        <v>540096</v>
       </c>
       <c r="R72" t="n">
-        <v>6448346</v>
+        <v>6448345</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081923</v>
+        <v>127081974</v>
       </c>
       <c r="B73" t="n">
-        <v>95757</v>
+        <v>95568</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540198</v>
+        <v>540097</v>
       </c>
       <c r="R73" t="n">
-        <v>6448437</v>
+        <v>6448346</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081928</v>
+        <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95768</v>
+        <v>95763</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540172</v>
+        <v>540198</v>
       </c>
       <c r="R74" t="n">
-        <v>6448411</v>
+        <v>6448437</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081971</v>
+        <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>95757</v>
+        <v>95774</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540096</v>
+        <v>540172</v>
       </c>
       <c r="R75" t="n">
-        <v>6448345</v>
+        <v>6448411</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B76" t="n">
-        <v>95768</v>
+        <v>9398</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,34 +8193,55 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R76" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8261,6 +8282,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8279,10 +8301,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B77" t="n">
-        <v>9398</v>
+        <v>95774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8290,55 +8312,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R77" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8379,7 +8380,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92521</v>
+        <v>92527</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>127081925</v>
       </c>
       <c r="B80" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081944</v>
+        <v>127081924</v>
       </c>
       <c r="B81" t="n">
-        <v>91881</v>
+        <v>95763</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540096</v>
+        <v>540180</v>
       </c>
       <c r="R81" t="n">
-        <v>6448303</v>
+        <v>6448428</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081924</v>
+        <v>127081944</v>
       </c>
       <c r="B82" t="n">
-        <v>95757</v>
+        <v>91887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540180</v>
+        <v>540096</v>
       </c>
       <c r="R82" t="n">
-        <v>6448428</v>
+        <v>6448303</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288040</v>
+        <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>105290</v>
+        <v>95774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221101</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540165</v>
+        <v>540177</v>
       </c>
       <c r="R83" t="n">
-        <v>6448488</v>
+        <v>6448499</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8962,7 +8962,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8981,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288064</v>
+        <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95768</v>
+        <v>95568</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8992,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9016,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540177</v>
+        <v>540206</v>
       </c>
       <c r="R84" t="n">
-        <v>6448499</v>
+        <v>6448439</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9078,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288031</v>
+        <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>100525</v>
+        <v>95795</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9089,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9113,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540180</v>
+        <v>540222</v>
       </c>
       <c r="R85" t="n">
-        <v>6448493</v>
+        <v>6448525</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9175,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288089</v>
+        <v>127288040</v>
       </c>
       <c r="B86" t="n">
-        <v>95562</v>
+        <v>105296</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9186,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2779</v>
+        <v>221101</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9210,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540206</v>
+        <v>540165</v>
       </c>
       <c r="R86" t="n">
-        <v>6448439</v>
+        <v>6448488</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9254,6 +9253,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9272,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288035</v>
+        <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>95789</v>
+        <v>100531</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,21 +9283,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2818</v>
+        <v>222771</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540222</v>
+        <v>540180</v>
       </c>
       <c r="R87" t="n">
-        <v>6448525</v>
+        <v>6448493</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288023</v>
+        <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>100525</v>
+        <v>95763</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540237</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>6448446</v>
+        <v>6448342</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288100</v>
+        <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95757</v>
+        <v>95778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540195</v>
+        <v>540163</v>
       </c>
       <c r="R89" t="n">
-        <v>6448342</v>
+        <v>6448517</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288019</v>
+        <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95772</v>
+        <v>95774</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540163</v>
+        <v>540187</v>
       </c>
       <c r="R90" t="n">
-        <v>6448517</v>
+        <v>6448488</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288060</v>
+        <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>95768</v>
+        <v>100531</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540187</v>
+        <v>540237</v>
       </c>
       <c r="R91" t="n">
-        <v>6448488</v>
+        <v>6448446</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127288025</v>
+        <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>100525</v>
+        <v>91887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,21 +9865,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540221</v>
+        <v>540219</v>
       </c>
       <c r="R93" t="n">
-        <v>6448522</v>
+        <v>6448415</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127288082</v>
+        <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>91881</v>
+        <v>100531</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9962,21 +9962,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540219</v>
+        <v>540221</v>
       </c>
       <c r="R94" t="n">
-        <v>6448415</v>
+        <v>6448522</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10051,7 +10051,7 @@
         <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10145,32 +10145,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288038</v>
+        <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>106031</v>
+        <v>95778</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10180,10 +10180,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540274</v>
+        <v>540224</v>
       </c>
       <c r="R96" t="n">
-        <v>6448610</v>
+        <v>6448404</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10218,18 +10218,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10248,32 +10242,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288011</v>
+        <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>95772</v>
+        <v>106037</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2668</v>
+        <v>220785</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10283,10 +10277,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540224</v>
+        <v>540274</v>
       </c>
       <c r="R97" t="n">
-        <v>6448404</v>
+        <v>6448610</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10321,12 +10315,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288013</v>
+        <v>127288074</v>
       </c>
       <c r="B98" t="n">
-        <v>95772</v>
+        <v>91887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540189</v>
+        <v>540039</v>
       </c>
       <c r="R98" t="n">
-        <v>6448461</v>
+        <v>6448303</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288027</v>
+        <v>127288013</v>
       </c>
       <c r="B99" t="n">
-        <v>100525</v>
+        <v>95778</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540310</v>
+        <v>540189</v>
       </c>
       <c r="R99" t="n">
-        <v>6448579</v>
+        <v>6448461</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10542,7 +10542,7 @@
         <v>127288065</v>
       </c>
       <c r="B100" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288074</v>
+        <v>127288057</v>
       </c>
       <c r="B101" t="n">
-        <v>91881</v>
+        <v>95774</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540039</v>
+        <v>540076</v>
       </c>
       <c r="R101" t="n">
-        <v>6448303</v>
+        <v>6448321</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288057</v>
+        <v>127288027</v>
       </c>
       <c r="B102" t="n">
-        <v>95768</v>
+        <v>100531</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540076</v>
+        <v>540310</v>
       </c>
       <c r="R102" t="n">
-        <v>6448321</v>
+        <v>6448579</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288101</v>
+        <v>127288028</v>
       </c>
       <c r="B103" t="n">
-        <v>95757</v>
+        <v>100531</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540333</v>
+        <v>540335</v>
       </c>
       <c r="R103" t="n">
-        <v>6448609</v>
+        <v>6448550</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10927,10 +10927,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288105</v>
+        <v>127288101</v>
       </c>
       <c r="B104" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R104" t="n">
-        <v>6448504</v>
+        <v>6448609</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288028</v>
+        <v>127288105</v>
       </c>
       <c r="B105" t="n">
-        <v>100525</v>
+        <v>95763</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540335</v>
+        <v>540171</v>
       </c>
       <c r="R105" t="n">
-        <v>6448550</v>
+        <v>6448504</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11124,7 +11124,7 @@
         <v>127288061</v>
       </c>
       <c r="B106" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>127288094</v>
       </c>
       <c r="B107" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288086</v>
+        <v>127288022</v>
       </c>
       <c r="B109" t="n">
-        <v>95562</v>
+        <v>91345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R109" t="n">
-        <v>6448609</v>
+        <v>6448436</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,10 +11525,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288087</v>
+        <v>127288086</v>
       </c>
       <c r="B110" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R110" t="n">
-        <v>6448608</v>
+        <v>6448609</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288014</v>
+        <v>127288087</v>
       </c>
       <c r="B111" t="n">
-        <v>95772</v>
+        <v>95568</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540187</v>
+        <v>540335</v>
       </c>
       <c r="R111" t="n">
-        <v>6448463</v>
+        <v>6448608</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288093</v>
+        <v>127288014</v>
       </c>
       <c r="B112" t="n">
-        <v>95757</v>
+        <v>95778</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540165</v>
+        <v>540187</v>
       </c>
       <c r="R112" t="n">
-        <v>6448484</v>
+        <v>6448463</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,24 +11798,8 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11832,32 +11816,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288022</v>
+        <v>127288093</v>
       </c>
       <c r="B113" t="n">
-        <v>91339</v>
+        <v>95763</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11851,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540171</v>
+        <v>540165</v>
       </c>
       <c r="R113" t="n">
-        <v>6448436</v>
+        <v>6448484</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11911,8 +11895,24 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11932,7 +11932,7 @@
         <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>95772</v>
+        <v>95778</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288039</v>
+        <v>127288075</v>
       </c>
       <c r="B115" t="n">
-        <v>105290</v>
+        <v>91887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221101</v>
+        <v>3884</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540178</v>
+        <v>540145</v>
       </c>
       <c r="R115" t="n">
-        <v>6448431</v>
+        <v>6448348</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12126,7 +12126,7 @@
         <v>127288037</v>
       </c>
       <c r="B116" t="n">
-        <v>95789</v>
+        <v>95795</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>127288059</v>
       </c>
       <c r="B117" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288075</v>
+        <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>91881</v>
+        <v>95568</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540145</v>
+        <v>540075</v>
       </c>
       <c r="R118" t="n">
-        <v>6448348</v>
+        <v>6448321</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288084</v>
+        <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>95562</v>
+        <v>95778</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540075</v>
+        <v>540210</v>
       </c>
       <c r="R119" t="n">
-        <v>6448321</v>
+        <v>6448417</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288012</v>
+        <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>95772</v>
+        <v>105296</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2668</v>
+        <v>221101</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540210</v>
+        <v>540178</v>
       </c>
       <c r="R120" t="n">
-        <v>6448417</v>
+        <v>6448431</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12611,7 +12611,7 @@
         <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288091</v>
+        <v>127288088</v>
       </c>
       <c r="B122" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540169</v>
+        <v>540338</v>
       </c>
       <c r="R122" t="n">
-        <v>6448494</v>
+        <v>6448617</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288088</v>
+        <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540338</v>
+        <v>540169</v>
       </c>
       <c r="R123" t="n">
-        <v>6448617</v>
+        <v>6448494</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>91279</v>
+        <v>91285</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>127288069</v>
       </c>
       <c r="B126" t="n">
-        <v>79391</v>
+        <v>79394</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95772</v>
+        <v>95778</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>95772</v>
+        <v>95778</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288026</v>
+        <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>100525</v>
+        <v>95776</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222771</v>
+        <v>2666</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540319</v>
+        <v>540169</v>
       </c>
       <c r="R137" t="n">
-        <v>6448616</v>
+        <v>6448494</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288092</v>
+        <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>95770</v>
+        <v>100531</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2666</v>
+        <v>222771</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540169</v>
+        <v>540319</v>
       </c>
       <c r="R138" t="n">
-        <v>6448494</v>
+        <v>6448616</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288034</v>
+        <v>127288079</v>
       </c>
       <c r="B139" t="n">
-        <v>100525</v>
+        <v>91887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540310</v>
       </c>
       <c r="R139" t="n">
-        <v>6448432</v>
+        <v>6448579</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288090</v>
+        <v>127288068</v>
       </c>
       <c r="B140" t="n">
-        <v>95562</v>
+        <v>79394</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540163</v>
+        <v>540274</v>
       </c>
       <c r="R140" t="n">
-        <v>6448518</v>
+        <v>6448603</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288079</v>
+        <v>127288034</v>
       </c>
       <c r="B141" t="n">
-        <v>91881</v>
+        <v>100531</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540310</v>
+        <v>540169</v>
       </c>
       <c r="R141" t="n">
-        <v>6448579</v>
+        <v>6448432</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288104</v>
+        <v>127288090</v>
       </c>
       <c r="B142" t="n">
-        <v>95757</v>
+        <v>95568</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R142" t="n">
-        <v>6448515</v>
+        <v>6448518</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288036</v>
+        <v>127288104</v>
       </c>
       <c r="B143" t="n">
-        <v>95789</v>
+        <v>95763</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R143" t="n">
-        <v>6448578</v>
+        <v>6448515</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288036</v>
       </c>
       <c r="B144" t="n">
-        <v>79391</v>
+        <v>95795</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>2818</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540336</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448578</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B145" t="n">
-        <v>95772</v>
+        <v>91887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R145" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288024</v>
+        <v>127288018</v>
       </c>
       <c r="B146" t="n">
-        <v>100525</v>
+        <v>95778</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540221</v>
+        <v>540167</v>
       </c>
       <c r="R146" t="n">
-        <v>6448466</v>
+        <v>6448513</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288080</v>
+        <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>91881</v>
+        <v>95778</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540251</v>
+        <v>540180</v>
       </c>
       <c r="R147" t="n">
-        <v>6448423</v>
+        <v>6448493</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,10 +15227,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288015</v>
+        <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>95772</v>
+        <v>100531</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15238,21 +15238,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540180</v>
+        <v>540221</v>
       </c>
       <c r="R148" t="n">
-        <v>6448493</v>
+        <v>6448466</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>127288081</v>
       </c>
       <c r="B150" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>127288020</v>
       </c>
       <c r="B151" t="n">
-        <v>95772</v>
+        <v>95778</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>127288102</v>
       </c>
       <c r="B152" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B43" t="n">
-        <v>79394</v>
+        <v>95891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R43" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B44" t="n">
-        <v>95891</v>
+        <v>79394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R44" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B47" t="n">
-        <v>75060</v>
+        <v>95774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R47" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081921</v>
+        <v>127081957</v>
       </c>
       <c r="B48" t="n">
-        <v>95774</v>
+        <v>95568</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540200</v>
+        <v>540098</v>
       </c>
       <c r="R48" t="n">
-        <v>6448453</v>
+        <v>6448341</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081963</v>
+        <v>127081932</v>
       </c>
       <c r="B49" t="n">
-        <v>95774</v>
+        <v>75060</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540121</v>
+        <v>540159</v>
       </c>
       <c r="R49" t="n">
-        <v>6448366</v>
+        <v>6448374</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081957</v>
+        <v>127081963</v>
       </c>
       <c r="B50" t="n">
-        <v>95568</v>
+        <v>95774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540098</v>
+        <v>540121</v>
       </c>
       <c r="R50" t="n">
-        <v>6448341</v>
+        <v>6448366</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081951</v>
+        <v>127081918</v>
       </c>
       <c r="B52" t="n">
-        <v>95763</v>
+        <v>95774</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540074</v>
+        <v>540208</v>
       </c>
       <c r="R52" t="n">
-        <v>6448313</v>
+        <v>6448378</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127081918</v>
+        <v>127081951</v>
       </c>
       <c r="B54" t="n">
-        <v>95774</v>
+        <v>95763</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540208</v>
+        <v>540074</v>
       </c>
       <c r="R54" t="n">
-        <v>6448378</v>
+        <v>6448313</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081926</v>
+        <v>127081940</v>
       </c>
       <c r="B55" t="n">
-        <v>91345</v>
+        <v>100531</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>222771</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540175</v>
+        <v>540164</v>
       </c>
       <c r="R55" t="n">
-        <v>6448412</v>
+        <v>6448364</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127081939</v>
+        <v>127081926</v>
       </c>
       <c r="B56" t="n">
-        <v>95763</v>
+        <v>91345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540134</v>
+        <v>540175</v>
       </c>
       <c r="R56" t="n">
-        <v>6448373</v>
+        <v>6448412</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6339,10 +6339,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127081940</v>
+        <v>127081939</v>
       </c>
       <c r="B57" t="n">
-        <v>100531</v>
+        <v>95763</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6350,21 +6350,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540164</v>
+        <v>540134</v>
       </c>
       <c r="R57" t="n">
-        <v>6448364</v>
+        <v>6448373</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081920</v>
+        <v>127081952</v>
       </c>
       <c r="B65" t="n">
         <v>95763</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540200</v>
+        <v>540073</v>
       </c>
       <c r="R65" t="n">
-        <v>6448453</v>
+        <v>6448314</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081967</v>
+        <v>127081920</v>
       </c>
       <c r="B66" t="n">
         <v>95763</v>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R66" t="n">
-        <v>6448358</v>
+        <v>6448453</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,7 +7309,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081952</v>
+        <v>127081967</v>
       </c>
       <c r="B67" t="n">
         <v>95763</v>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540073</v>
+        <v>540121</v>
       </c>
       <c r="R67" t="n">
-        <v>6448314</v>
+        <v>6448358</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081941</v>
+        <v>127081968</v>
       </c>
       <c r="B68" t="n">
-        <v>91887</v>
+        <v>95763</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540160</v>
+        <v>540109</v>
       </c>
       <c r="R68" t="n">
-        <v>6448357</v>
+        <v>6448358</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081958</v>
+        <v>127081941</v>
       </c>
       <c r="B69" t="n">
         <v>91887</v>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540100</v>
+        <v>540160</v>
       </c>
       <c r="R69" t="n">
-        <v>6448331</v>
+        <v>6448357</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081968</v>
+        <v>127081958</v>
       </c>
       <c r="B70" t="n">
-        <v>95763</v>
+        <v>91887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540109</v>
+        <v>540100</v>
       </c>
       <c r="R70" t="n">
-        <v>6448358</v>
+        <v>6448331</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081945</v>
+        <v>127081974</v>
       </c>
       <c r="B71" t="n">
-        <v>91887</v>
+        <v>95568</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540092</v>
+        <v>540097</v>
       </c>
       <c r="R71" t="n">
-        <v>6448293</v>
+        <v>6448346</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081974</v>
+        <v>127081923</v>
       </c>
       <c r="B73" t="n">
-        <v>95568</v>
+        <v>95763</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540097</v>
+        <v>540198</v>
       </c>
       <c r="R73" t="n">
-        <v>6448346</v>
+        <v>6448437</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081923</v>
+        <v>127081928</v>
       </c>
       <c r="B74" t="n">
-        <v>95763</v>
+        <v>95774</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540198</v>
+        <v>540172</v>
       </c>
       <c r="R74" t="n">
-        <v>6448437</v>
+        <v>6448411</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081928</v>
+        <v>127081945</v>
       </c>
       <c r="B75" t="n">
-        <v>95774</v>
+        <v>91887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540172</v>
+        <v>540092</v>
       </c>
       <c r="R75" t="n">
-        <v>6448411</v>
+        <v>6448293</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>9398</v>
+        <v>95774</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,55 +8193,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R76" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8282,7 +8261,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8301,10 +8279,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B77" t="n">
-        <v>95774</v>
+        <v>9398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8312,34 +8290,55 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R77" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8380,6 +8379,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8495,7 +8495,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081976</v>
+        <v>127081925</v>
       </c>
       <c r="B79" t="n">
         <v>95763</v>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540092</v>
+        <v>540175</v>
       </c>
       <c r="R79" t="n">
-        <v>6448349</v>
+        <v>6448426</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081925</v>
+        <v>127081924</v>
       </c>
       <c r="B80" t="n">
         <v>95763</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540175</v>
+        <v>540180</v>
       </c>
       <c r="R80" t="n">
-        <v>6448426</v>
+        <v>6448428</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081924</v>
+        <v>127081976</v>
       </c>
       <c r="B81" t="n">
         <v>95763</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540180</v>
+        <v>540092</v>
       </c>
       <c r="R81" t="n">
-        <v>6448428</v>
+        <v>6448349</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288100</v>
+        <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>95763</v>
+        <v>100531</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540237</v>
       </c>
       <c r="R88" t="n">
-        <v>6448342</v>
+        <v>6448446</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288019</v>
+        <v>127288100</v>
       </c>
       <c r="B89" t="n">
-        <v>95778</v>
+        <v>95763</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540163</v>
+        <v>540195</v>
       </c>
       <c r="R89" t="n">
-        <v>6448517</v>
+        <v>6448342</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288060</v>
+        <v>127288019</v>
       </c>
       <c r="B90" t="n">
-        <v>95774</v>
+        <v>95778</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540187</v>
+        <v>540163</v>
       </c>
       <c r="R90" t="n">
-        <v>6448488</v>
+        <v>6448517</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288023</v>
+        <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>100531</v>
+        <v>95774</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540237</v>
+        <v>540187</v>
       </c>
       <c r="R91" t="n">
-        <v>6448446</v>
+        <v>6448488</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127288082</v>
+        <v>127288025</v>
       </c>
       <c r="B93" t="n">
-        <v>91887</v>
+        <v>100531</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,21 +9865,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540219</v>
+        <v>540221</v>
       </c>
       <c r="R93" t="n">
-        <v>6448415</v>
+        <v>6448522</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127288025</v>
+        <v>127288082</v>
       </c>
       <c r="B94" t="n">
-        <v>100531</v>
+        <v>91887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9962,21 +9962,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540221</v>
+        <v>540219</v>
       </c>
       <c r="R94" t="n">
-        <v>6448522</v>
+        <v>6448415</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288074</v>
+        <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>91887</v>
+        <v>95778</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540039</v>
+        <v>540189</v>
       </c>
       <c r="R98" t="n">
-        <v>6448303</v>
+        <v>6448461</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288013</v>
+        <v>127288065</v>
       </c>
       <c r="B99" t="n">
-        <v>95778</v>
+        <v>95774</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540189</v>
+        <v>540174</v>
       </c>
       <c r="R99" t="n">
-        <v>6448461</v>
+        <v>6448468</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>95774</v>
+        <v>91887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R100" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288028</v>
+        <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>100531</v>
+        <v>95763</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R103" t="n">
-        <v>6448550</v>
+        <v>6448609</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10927,7 +10927,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288101</v>
+        <v>127288105</v>
       </c>
       <c r="B104" t="n">
         <v>95763</v>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R104" t="n">
-        <v>6448609</v>
+        <v>6448504</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95763</v>
+        <v>95774</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R105" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288061</v>
+        <v>127288094</v>
       </c>
       <c r="B106" t="n">
-        <v>95774</v>
+        <v>95763</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R106" t="n">
-        <v>6448493</v>
+        <v>6448441</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,8 +11200,24 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11218,10 +11234,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288094</v>
+        <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>95763</v>
+        <v>100531</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11229,21 +11245,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11253,10 +11269,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540171</v>
+        <v>540335</v>
       </c>
       <c r="R107" t="n">
-        <v>6448441</v>
+        <v>6448550</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11297,24 +11313,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288022</v>
+        <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>91345</v>
+        <v>95568</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R109" t="n">
-        <v>6448436</v>
+        <v>6448609</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,7 +11525,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288086</v>
+        <v>127288087</v>
       </c>
       <c r="B110" t="n">
         <v>95568</v>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540333</v>
+        <v>540335</v>
       </c>
       <c r="R110" t="n">
-        <v>6448609</v>
+        <v>6448608</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288087</v>
+        <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95568</v>
+        <v>95778</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540335</v>
+        <v>540187</v>
       </c>
       <c r="R111" t="n">
-        <v>6448608</v>
+        <v>6448463</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288014</v>
+        <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95778</v>
+        <v>95763</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540187</v>
+        <v>540165</v>
       </c>
       <c r="R112" t="n">
-        <v>6448463</v>
+        <v>6448484</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,8 +11798,24 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11816,10 +11832,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288093</v>
+        <v>127288016</v>
       </c>
       <c r="B113" t="n">
-        <v>95763</v>
+        <v>95778</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11827,16 +11843,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11851,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540165</v>
+        <v>540187</v>
       </c>
       <c r="R113" t="n">
-        <v>6448484</v>
+        <v>6448494</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11895,24 +11911,8 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B114" t="n">
-        <v>95778</v>
+        <v>91345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R114" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288075</v>
+        <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>91887</v>
+        <v>95795</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3884</v>
+        <v>2818</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540145</v>
+        <v>540213</v>
       </c>
       <c r="R115" t="n">
-        <v>6448348</v>
+        <v>6448463</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288037</v>
+        <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95795</v>
+        <v>95774</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540213</v>
+        <v>540182</v>
       </c>
       <c r="R116" t="n">
-        <v>6448463</v>
+        <v>6448496</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288059</v>
+        <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>95774</v>
+        <v>91887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540182</v>
+        <v>540145</v>
       </c>
       <c r="R117" t="n">
-        <v>6448496</v>
+        <v>6448348</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B125" t="n">
-        <v>91285</v>
+        <v>79394</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R125" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B126" t="n">
-        <v>79394</v>
+        <v>91285</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R126" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288079</v>
+        <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>91887</v>
+        <v>95568</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540310</v>
+        <v>540163</v>
       </c>
       <c r="R139" t="n">
-        <v>6448579</v>
+        <v>6448518</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288068</v>
+        <v>127288079</v>
       </c>
       <c r="B140" t="n">
-        <v>79394</v>
+        <v>91887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540274</v>
+        <v>540310</v>
       </c>
       <c r="R140" t="n">
-        <v>6448603</v>
+        <v>6448579</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288034</v>
+        <v>127288104</v>
       </c>
       <c r="B141" t="n">
-        <v>100531</v>
+        <v>95763</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
         <v>540169</v>
       </c>
       <c r="R141" t="n">
-        <v>6448432</v>
+        <v>6448515</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288090</v>
+        <v>127288036</v>
       </c>
       <c r="B142" t="n">
-        <v>95568</v>
+        <v>95795</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540163</v>
+        <v>540336</v>
       </c>
       <c r="R142" t="n">
-        <v>6448518</v>
+        <v>6448578</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288104</v>
+        <v>127288068</v>
       </c>
       <c r="B143" t="n">
-        <v>95763</v>
+        <v>79394</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2671</v>
+        <v>6431</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R143" t="n">
-        <v>6448515</v>
+        <v>6448603</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288036</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>95795</v>
+        <v>100531</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2818</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448578</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288080</v>
+        <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>91887</v>
+        <v>95778</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540251</v>
+        <v>540167</v>
       </c>
       <c r="R145" t="n">
-        <v>6448423</v>
+        <v>6448513</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>95778</v>
+        <v>91887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R146" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288081</v>
+        <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>91887</v>
+        <v>95778</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540243</v>
+        <v>540165</v>
       </c>
       <c r="R150" t="n">
-        <v>6448421</v>
+        <v>6448511</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288020</v>
+        <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95778</v>
+        <v>95763</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,16 +15529,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540165</v>
+        <v>540208</v>
       </c>
       <c r="R151" t="n">
-        <v>6448511</v>
+        <v>6448415</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288102</v>
+        <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>95763</v>
+        <v>91887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540208</v>
+        <v>540243</v>
       </c>
       <c r="R152" t="n">
-        <v>6448415</v>
+        <v>6448421</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081974</v>
+        <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>95568</v>
+        <v>91887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540097</v>
+        <v>540092</v>
       </c>
       <c r="R71" t="n">
-        <v>6448346</v>
+        <v>6448293</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081971</v>
+        <v>127081974</v>
       </c>
       <c r="B72" t="n">
-        <v>95763</v>
+        <v>95568</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540096</v>
+        <v>540097</v>
       </c>
       <c r="R72" t="n">
-        <v>6448345</v>
+        <v>6448346</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,7 +7891,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081923</v>
+        <v>127081971</v>
       </c>
       <c r="B73" t="n">
         <v>95763</v>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540198</v>
+        <v>540096</v>
       </c>
       <c r="R73" t="n">
-        <v>6448437</v>
+        <v>6448345</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081928</v>
+        <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95774</v>
+        <v>95763</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540172</v>
+        <v>540198</v>
       </c>
       <c r="R74" t="n">
-        <v>6448411</v>
+        <v>6448437</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081945</v>
+        <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>91887</v>
+        <v>95774</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540092</v>
+        <v>540172</v>
       </c>
       <c r="R75" t="n">
-        <v>6448293</v>
+        <v>6448411</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288037</v>
+        <v>127288039</v>
       </c>
       <c r="B115" t="n">
-        <v>95795</v>
+        <v>105296</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>221101</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540213</v>
+        <v>540178</v>
       </c>
       <c r="R115" t="n">
-        <v>6448463</v>
+        <v>6448431</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288059</v>
+        <v>127288037</v>
       </c>
       <c r="B116" t="n">
-        <v>95774</v>
+        <v>95795</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540182</v>
+        <v>540213</v>
       </c>
       <c r="R116" t="n">
-        <v>6448496</v>
+        <v>6448463</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288075</v>
+        <v>127288059</v>
       </c>
       <c r="B117" t="n">
-        <v>91887</v>
+        <v>95774</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540145</v>
+        <v>540182</v>
       </c>
       <c r="R117" t="n">
-        <v>6448348</v>
+        <v>6448496</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288084</v>
+        <v>127288075</v>
       </c>
       <c r="B118" t="n">
-        <v>95568</v>
+        <v>91887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540075</v>
+        <v>540145</v>
       </c>
       <c r="R118" t="n">
-        <v>6448321</v>
+        <v>6448348</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288012</v>
+        <v>127288084</v>
       </c>
       <c r="B119" t="n">
-        <v>95778</v>
+        <v>95568</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540210</v>
+        <v>540075</v>
       </c>
       <c r="R119" t="n">
-        <v>6448417</v>
+        <v>6448321</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288039</v>
+        <v>127288012</v>
       </c>
       <c r="B120" t="n">
-        <v>105296</v>
+        <v>95778</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221101</v>
+        <v>2668</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540178</v>
+        <v>540210</v>
       </c>
       <c r="R120" t="n">
-        <v>6448431</v>
+        <v>6448417</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288090</v>
+        <v>127288034</v>
       </c>
       <c r="B139" t="n">
-        <v>95568</v>
+        <v>100531</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448518</v>
+        <v>6448432</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288079</v>
+        <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>91887</v>
+        <v>95568</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540310</v>
+        <v>540163</v>
       </c>
       <c r="R140" t="n">
-        <v>6448579</v>
+        <v>6448518</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288104</v>
+        <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>95763</v>
+        <v>91887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540169</v>
+        <v>540310</v>
       </c>
       <c r="R141" t="n">
-        <v>6448515</v>
+        <v>6448579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288036</v>
+        <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95795</v>
+        <v>95763</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448578</v>
+        <v>6448515</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288068</v>
+        <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>79394</v>
+        <v>95795</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6431</v>
+        <v>2818</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540274</v>
+        <v>540336</v>
       </c>
       <c r="R143" t="n">
-        <v>6448603</v>
+        <v>6448578</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>100531</v>
+        <v>79394</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127081927</v>
       </c>
       <c r="B39" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>127081948</v>
       </c>
       <c r="B40" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>95891</v>
+        <v>79394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R43" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>79394</v>
+        <v>95892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R44" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>127081916</v>
       </c>
       <c r="B45" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081964</v>
       </c>
       <c r="B46" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081921</v>
+        <v>127081949</v>
       </c>
       <c r="B47" t="n">
-        <v>95774</v>
+        <v>30129</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5380,21 +5380,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2667</v>
+        <v>200985</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540200</v>
+        <v>540052</v>
       </c>
       <c r="R47" t="n">
-        <v>6448453</v>
+        <v>6448313</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081957</v>
+        <v>127081932</v>
       </c>
       <c r="B48" t="n">
-        <v>95568</v>
+        <v>75060</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2779</v>
+        <v>1460</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540098</v>
+        <v>540159</v>
       </c>
       <c r="R48" t="n">
-        <v>6448341</v>
+        <v>6448374</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B49" t="n">
-        <v>75060</v>
+        <v>95775</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R49" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5663,7 +5663,7 @@
         <v>127081963</v>
       </c>
       <c r="B50" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081949</v>
+        <v>127081957</v>
       </c>
       <c r="B51" t="n">
-        <v>30129</v>
+        <v>95569</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>200985</v>
+        <v>2779</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540052</v>
+        <v>540098</v>
       </c>
       <c r="R51" t="n">
-        <v>6448313</v>
+        <v>6448341</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081918</v>
+        <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95774</v>
+        <v>95764</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540208</v>
+        <v>540074</v>
       </c>
       <c r="R52" t="n">
-        <v>6448378</v>
+        <v>6448313</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127081951</v>
+        <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95763</v>
+        <v>95775</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540074</v>
+        <v>540208</v>
       </c>
       <c r="R54" t="n">
-        <v>6448313</v>
+        <v>6448378</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081940</v>
+        <v>127081926</v>
       </c>
       <c r="B55" t="n">
-        <v>100531</v>
+        <v>91346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222771</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540164</v>
+        <v>540175</v>
       </c>
       <c r="R55" t="n">
-        <v>6448364</v>
+        <v>6448412</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127081926</v>
+        <v>127081939</v>
       </c>
       <c r="B56" t="n">
-        <v>91345</v>
+        <v>95764</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540175</v>
+        <v>540134</v>
       </c>
       <c r="R56" t="n">
-        <v>6448412</v>
+        <v>6448373</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6339,10 +6339,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127081939</v>
+        <v>127081940</v>
       </c>
       <c r="B57" t="n">
-        <v>95763</v>
+        <v>100532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6350,21 +6350,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540134</v>
+        <v>540164</v>
       </c>
       <c r="R57" t="n">
-        <v>6448373</v>
+        <v>6448364</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081952</v>
+        <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540073</v>
+        <v>540200</v>
       </c>
       <c r="R65" t="n">
-        <v>6448314</v>
+        <v>6448453</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081920</v>
+        <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R66" t="n">
-        <v>6448453</v>
+        <v>6448358</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081967</v>
+        <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540121</v>
+        <v>540073</v>
       </c>
       <c r="R67" t="n">
-        <v>6448358</v>
+        <v>6448314</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081968</v>
+        <v>127081941</v>
       </c>
       <c r="B68" t="n">
-        <v>95763</v>
+        <v>91888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540109</v>
+        <v>540160</v>
       </c>
       <c r="R68" t="n">
-        <v>6448358</v>
+        <v>6448357</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B69" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R69" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B70" t="n">
-        <v>91887</v>
+        <v>95764</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R70" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7700,7 +7700,7 @@
         <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081974</v>
+        <v>127081971</v>
       </c>
       <c r="B72" t="n">
-        <v>95568</v>
+        <v>95764</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540097</v>
+        <v>540096</v>
       </c>
       <c r="R72" t="n">
-        <v>6448346</v>
+        <v>6448345</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081971</v>
+        <v>127081974</v>
       </c>
       <c r="B73" t="n">
-        <v>95763</v>
+        <v>95569</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540096</v>
+        <v>540097</v>
       </c>
       <c r="R73" t="n">
-        <v>6448345</v>
+        <v>6448346</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081925</v>
+        <v>127081944</v>
       </c>
       <c r="B79" t="n">
-        <v>95763</v>
+        <v>91888</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540175</v>
+        <v>540096</v>
       </c>
       <c r="R79" t="n">
-        <v>6448426</v>
+        <v>6448303</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081924</v>
+        <v>127081976</v>
       </c>
       <c r="B80" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540180</v>
+        <v>540092</v>
       </c>
       <c r="R80" t="n">
-        <v>6448428</v>
+        <v>6448349</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081976</v>
+        <v>127081925</v>
       </c>
       <c r="B81" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540092</v>
+        <v>540175</v>
       </c>
       <c r="R81" t="n">
-        <v>6448349</v>
+        <v>6448426</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081944</v>
+        <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>91887</v>
+        <v>95764</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540096</v>
+        <v>540180</v>
       </c>
       <c r="R82" t="n">
-        <v>6448303</v>
+        <v>6448428</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8886,7 +8886,7 @@
         <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95795</v>
+        <v>95796</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288040</v>
+        <v>127288031</v>
       </c>
       <c r="B86" t="n">
-        <v>105296</v>
+        <v>100532</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,16 +9185,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540165</v>
+        <v>540180</v>
       </c>
       <c r="R86" t="n">
-        <v>6448488</v>
+        <v>6448493</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,7 +9253,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9272,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>100531</v>
+        <v>105297</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,16 +9282,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R87" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9351,6 +9350,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288023</v>
+        <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>100531</v>
+        <v>95764</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540237</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>6448446</v>
+        <v>6448342</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288100</v>
+        <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95763</v>
+        <v>95779</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540195</v>
+        <v>540163</v>
       </c>
       <c r="R89" t="n">
-        <v>6448342</v>
+        <v>6448517</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288019</v>
+        <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95778</v>
+        <v>95775</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540163</v>
+        <v>540187</v>
       </c>
       <c r="R90" t="n">
-        <v>6448517</v>
+        <v>6448488</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288060</v>
+        <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>95774</v>
+        <v>100532</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540187</v>
+        <v>540237</v>
       </c>
       <c r="R91" t="n">
-        <v>6448488</v>
+        <v>6448446</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288025</v>
       </c>
       <c r="B93" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288082</v>
       </c>
       <c r="B94" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288013</v>
+        <v>127288027</v>
       </c>
       <c r="B98" t="n">
-        <v>95778</v>
+        <v>100532</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540189</v>
+        <v>540310</v>
       </c>
       <c r="R98" t="n">
-        <v>6448461</v>
+        <v>6448579</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288065</v>
+        <v>127288013</v>
       </c>
       <c r="B99" t="n">
-        <v>95774</v>
+        <v>95779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540174</v>
+        <v>540189</v>
       </c>
       <c r="R99" t="n">
-        <v>6448468</v>
+        <v>6448461</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288074</v>
+        <v>127288065</v>
       </c>
       <c r="B100" t="n">
-        <v>91887</v>
+        <v>95775</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540039</v>
+        <v>540174</v>
       </c>
       <c r="R100" t="n">
-        <v>6448303</v>
+        <v>6448468</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288057</v>
+        <v>127288074</v>
       </c>
       <c r="B101" t="n">
-        <v>95774</v>
+        <v>91888</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540076</v>
+        <v>540039</v>
       </c>
       <c r="R101" t="n">
-        <v>6448321</v>
+        <v>6448303</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288027</v>
+        <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>100531</v>
+        <v>95775</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540310</v>
+        <v>540076</v>
       </c>
       <c r="R102" t="n">
-        <v>6448579</v>
+        <v>6448321</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10833,7 +10833,7 @@
         <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>127288094</v>
       </c>
       <c r="B106" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11832,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>95778</v>
+        <v>91346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R113" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288022</v>
+        <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>91345</v>
+        <v>95779</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>2668</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540171</v>
+        <v>540187</v>
       </c>
       <c r="R114" t="n">
-        <v>6448436</v>
+        <v>6448494</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288039</v>
+        <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>105296</v>
+        <v>95796</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221101</v>
+        <v>2818</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540178</v>
+        <v>540213</v>
       </c>
       <c r="R115" t="n">
-        <v>6448431</v>
+        <v>6448463</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288037</v>
+        <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95795</v>
+        <v>95775</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540213</v>
+        <v>540182</v>
       </c>
       <c r="R116" t="n">
-        <v>6448463</v>
+        <v>6448496</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288059</v>
+        <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>95774</v>
+        <v>91888</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540182</v>
+        <v>540145</v>
       </c>
       <c r="R117" t="n">
-        <v>6448496</v>
+        <v>6448348</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288075</v>
+        <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>91887</v>
+        <v>95569</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540145</v>
+        <v>540075</v>
       </c>
       <c r="R118" t="n">
-        <v>6448348</v>
+        <v>6448321</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288084</v>
+        <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>95568</v>
+        <v>95779</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540075</v>
+        <v>540210</v>
       </c>
       <c r="R119" t="n">
-        <v>6448321</v>
+        <v>6448417</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288012</v>
+        <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>95778</v>
+        <v>105297</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2668</v>
+        <v>221101</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540210</v>
+        <v>540178</v>
       </c>
       <c r="R120" t="n">
-        <v>6448417</v>
+        <v>6448431</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12611,7 +12611,7 @@
         <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>127288088</v>
       </c>
       <c r="B122" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>127288110</v>
       </c>
       <c r="B126" t="n">
-        <v>91285</v>
+        <v>91286</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95568</v>
+        <v>95569</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95774</v>
+        <v>95775</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95776</v>
+        <v>95777</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288034</v>
+        <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>100531</v>
+        <v>95569</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222771</v>
+        <v>2779</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R139" t="n">
-        <v>6448432</v>
+        <v>6448518</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288090</v>
+        <v>127288079</v>
       </c>
       <c r="B140" t="n">
-        <v>95568</v>
+        <v>91888</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540163</v>
+        <v>540310</v>
       </c>
       <c r="R140" t="n">
-        <v>6448518</v>
+        <v>6448579</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288079</v>
+        <v>127288104</v>
       </c>
       <c r="B141" t="n">
-        <v>91887</v>
+        <v>95764</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540310</v>
+        <v>540169</v>
       </c>
       <c r="R141" t="n">
-        <v>6448579</v>
+        <v>6448515</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288104</v>
+        <v>127288036</v>
       </c>
       <c r="B142" t="n">
-        <v>95763</v>
+        <v>95796</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>2818</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540169</v>
+        <v>540336</v>
       </c>
       <c r="R142" t="n">
-        <v>6448515</v>
+        <v>6448578</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288036</v>
+        <v>127288068</v>
       </c>
       <c r="B143" t="n">
-        <v>95795</v>
+        <v>79394</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2818</v>
+        <v>6431</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540336</v>
+        <v>540274</v>
       </c>
       <c r="R143" t="n">
-        <v>6448578</v>
+        <v>6448603</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>79394</v>
+        <v>100532</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14939,7 +14939,7 @@
         <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>95778</v>
+        <v>95779</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>91887</v>
+        <v>91888</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -6824,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127081942</v>
+        <v>127081954</v>
       </c>
       <c r="B62" t="n">
-        <v>91888</v>
+        <v>95775</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540102</v>
+        <v>540093</v>
       </c>
       <c r="R62" t="n">
-        <v>6448315</v>
+        <v>6448328</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127081954</v>
+        <v>127081942</v>
       </c>
       <c r="B63" t="n">
-        <v>95775</v>
+        <v>91888</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540093</v>
+        <v>540102</v>
       </c>
       <c r="R63" t="n">
-        <v>6448328</v>
+        <v>6448315</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081944</v>
+        <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>91888</v>
+        <v>95764</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R79" t="n">
-        <v>6448303</v>
+        <v>6448349</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081976</v>
+        <v>127081925</v>
       </c>
       <c r="B80" t="n">
         <v>95764</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540092</v>
+        <v>540175</v>
       </c>
       <c r="R80" t="n">
-        <v>6448349</v>
+        <v>6448426</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081925</v>
+        <v>127081924</v>
       </c>
       <c r="B81" t="n">
         <v>95764</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540175</v>
+        <v>540180</v>
       </c>
       <c r="R81" t="n">
-        <v>6448426</v>
+        <v>6448428</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081924</v>
+        <v>127081944</v>
       </c>
       <c r="B82" t="n">
-        <v>95764</v>
+        <v>91888</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540180</v>
+        <v>540096</v>
       </c>
       <c r="R82" t="n">
-        <v>6448428</v>
+        <v>6448303</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288064</v>
+        <v>127288040</v>
       </c>
       <c r="B83" t="n">
-        <v>95775</v>
+        <v>105297</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>221101</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540177</v>
+        <v>540165</v>
       </c>
       <c r="R83" t="n">
-        <v>6448499</v>
+        <v>6448488</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8962,6 +8962,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8980,10 +8981,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288089</v>
+        <v>127288064</v>
       </c>
       <c r="B84" t="n">
-        <v>95569</v>
+        <v>95775</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8992,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9016,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540206</v>
+        <v>540177</v>
       </c>
       <c r="R84" t="n">
-        <v>6448439</v>
+        <v>6448499</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9078,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B85" t="n">
-        <v>95796</v>
+        <v>95569</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9089,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R85" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9175,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288031</v>
+        <v>127288035</v>
       </c>
       <c r="B86" t="n">
-        <v>100532</v>
+        <v>95796</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9186,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9210,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540180</v>
+        <v>540222</v>
       </c>
       <c r="R86" t="n">
-        <v>6448493</v>
+        <v>6448525</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288040</v>
+        <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>105297</v>
+        <v>100532</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,16 +9283,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540165</v>
+        <v>540180</v>
       </c>
       <c r="R87" t="n">
-        <v>6448488</v>
+        <v>6448493</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9350,7 +9351,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127288025</v>
+        <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>100532</v>
+        <v>91888</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,21 +9865,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540221</v>
+        <v>540219</v>
       </c>
       <c r="R93" t="n">
-        <v>6448522</v>
+        <v>6448415</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127288082</v>
+        <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>91888</v>
+        <v>100532</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9962,21 +9962,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540219</v>
+        <v>540221</v>
       </c>
       <c r="R94" t="n">
-        <v>6448415</v>
+        <v>6448522</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288108</v>
+        <v>127288038</v>
       </c>
       <c r="B95" t="n">
-        <v>95764</v>
+        <v>106038</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2671</v>
+        <v>220785</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540163</v>
+        <v>540274</v>
       </c>
       <c r="R95" t="n">
-        <v>6448463</v>
+        <v>6448610</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,12 +10121,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10145,10 +10151,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288011</v>
+        <v>127288108</v>
       </c>
       <c r="B96" t="n">
-        <v>95779</v>
+        <v>95764</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10156,16 +10162,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10180,10 +10186,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540224</v>
+        <v>540163</v>
       </c>
       <c r="R96" t="n">
-        <v>6448404</v>
+        <v>6448463</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10242,32 +10248,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288038</v>
+        <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>106038</v>
+        <v>95779</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10277,10 +10283,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540274</v>
+        <v>540224</v>
       </c>
       <c r="R97" t="n">
-        <v>6448610</v>
+        <v>6448404</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10315,18 +10321,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B143" t="n">
-        <v>79394</v>
+        <v>100532</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R143" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>100532</v>
+        <v>79394</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4593,32 +4593,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127081927</v>
+        <v>127081948</v>
       </c>
       <c r="B39" t="n">
-        <v>91346</v>
+        <v>95775</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540175</v>
+        <v>540060</v>
       </c>
       <c r="R39" t="n">
-        <v>6448411</v>
+        <v>6448311</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4690,32 +4690,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127081948</v>
+        <v>127081927</v>
       </c>
       <c r="B40" t="n">
-        <v>95775</v>
+        <v>91346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540060</v>
+        <v>540175</v>
       </c>
       <c r="R40" t="n">
-        <v>6448311</v>
+        <v>6448411</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B43" t="n">
-        <v>79394</v>
+        <v>95892</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R43" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B44" t="n">
-        <v>95892</v>
+        <v>79394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R44" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127081916</v>
+        <v>127081964</v>
       </c>
       <c r="B45" t="n">
-        <v>91888</v>
+        <v>95569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,21 +5186,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540227</v>
+        <v>540121</v>
       </c>
       <c r="R45" t="n">
-        <v>6448359</v>
+        <v>6448366</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5272,10 +5272,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127081964</v>
+        <v>127081916</v>
       </c>
       <c r="B46" t="n">
-        <v>95569</v>
+        <v>91888</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5283,21 +5283,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540121</v>
+        <v>540227</v>
       </c>
       <c r="R46" t="n">
-        <v>6448366</v>
+        <v>6448359</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081949</v>
+        <v>127081932</v>
       </c>
       <c r="B47" t="n">
-        <v>30129</v>
+        <v>75060</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>200985</v>
+        <v>1460</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540052</v>
+        <v>540159</v>
       </c>
       <c r="R47" t="n">
-        <v>6448313</v>
+        <v>6448374</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>75060</v>
+        <v>95775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R48" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081921</v>
+        <v>127081963</v>
       </c>
       <c r="B49" t="n">
         <v>95775</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R49" t="n">
-        <v>6448453</v>
+        <v>6448366</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081963</v>
+        <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>95775</v>
+        <v>95569</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540121</v>
+        <v>540098</v>
       </c>
       <c r="R50" t="n">
-        <v>6448366</v>
+        <v>6448341</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081957</v>
+        <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>95569</v>
+        <v>30129</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2779</v>
+        <v>200985</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540098</v>
+        <v>540052</v>
       </c>
       <c r="R51" t="n">
-        <v>6448341</v>
+        <v>6448313</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081951</v>
+        <v>127081959</v>
       </c>
       <c r="B52" t="n">
-        <v>95764</v>
+        <v>95569</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540074</v>
+        <v>540103</v>
       </c>
       <c r="R52" t="n">
-        <v>6448313</v>
+        <v>6448344</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5951,10 +5951,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127081959</v>
+        <v>127081918</v>
       </c>
       <c r="B53" t="n">
-        <v>95569</v>
+        <v>95775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540103</v>
+        <v>540208</v>
       </c>
       <c r="R53" t="n">
-        <v>6448344</v>
+        <v>6448378</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127081918</v>
+        <v>127081951</v>
       </c>
       <c r="B54" t="n">
-        <v>95775</v>
+        <v>95764</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540208</v>
+        <v>540074</v>
       </c>
       <c r="R54" t="n">
-        <v>6448378</v>
+        <v>6448313</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081926</v>
+        <v>127081939</v>
       </c>
       <c r="B55" t="n">
-        <v>91346</v>
+        <v>95764</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540175</v>
+        <v>540134</v>
       </c>
       <c r="R55" t="n">
-        <v>6448412</v>
+        <v>6448373</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127081939</v>
+        <v>127081926</v>
       </c>
       <c r="B56" t="n">
-        <v>95764</v>
+        <v>91346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540134</v>
+        <v>540175</v>
       </c>
       <c r="R56" t="n">
-        <v>6448373</v>
+        <v>6448412</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6824,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127081954</v>
+        <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>95775</v>
+        <v>91888</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540093</v>
+        <v>540102</v>
       </c>
       <c r="R62" t="n">
-        <v>6448328</v>
+        <v>6448315</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127081942</v>
+        <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>91888</v>
+        <v>95775</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540102</v>
+        <v>540093</v>
       </c>
       <c r="R63" t="n">
-        <v>6448315</v>
+        <v>6448328</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B69" t="n">
-        <v>91888</v>
+        <v>95764</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R69" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081968</v>
+        <v>127081958</v>
       </c>
       <c r="B70" t="n">
-        <v>95764</v>
+        <v>91888</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540109</v>
+        <v>540100</v>
       </c>
       <c r="R70" t="n">
-        <v>6448358</v>
+        <v>6448331</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081945</v>
+        <v>127081923</v>
       </c>
       <c r="B71" t="n">
-        <v>91888</v>
+        <v>95764</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540092</v>
+        <v>540198</v>
       </c>
       <c r="R71" t="n">
-        <v>6448293</v>
+        <v>6448437</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081971</v>
+        <v>127081928</v>
       </c>
       <c r="B72" t="n">
-        <v>95764</v>
+        <v>95775</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540096</v>
+        <v>540172</v>
       </c>
       <c r="R72" t="n">
-        <v>6448345</v>
+        <v>6448411</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081974</v>
+        <v>127081945</v>
       </c>
       <c r="B73" t="n">
-        <v>95569</v>
+        <v>91888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540097</v>
+        <v>540092</v>
       </c>
       <c r="R73" t="n">
-        <v>6448346</v>
+        <v>6448293</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,7 +7988,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081923</v>
+        <v>127081971</v>
       </c>
       <c r="B74" t="n">
         <v>95764</v>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540198</v>
+        <v>540096</v>
       </c>
       <c r="R74" t="n">
-        <v>6448437</v>
+        <v>6448345</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081928</v>
+        <v>127081974</v>
       </c>
       <c r="B75" t="n">
-        <v>95775</v>
+        <v>95569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540172</v>
+        <v>540097</v>
       </c>
       <c r="R75" t="n">
-        <v>6448411</v>
+        <v>6448346</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081976</v>
+        <v>127081944</v>
       </c>
       <c r="B79" t="n">
-        <v>95764</v>
+        <v>91888</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R79" t="n">
-        <v>6448349</v>
+        <v>6448303</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081925</v>
+        <v>127081976</v>
       </c>
       <c r="B80" t="n">
         <v>95764</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540175</v>
+        <v>540092</v>
       </c>
       <c r="R80" t="n">
-        <v>6448426</v>
+        <v>6448349</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081924</v>
+        <v>127081925</v>
       </c>
       <c r="B81" t="n">
         <v>95764</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540180</v>
+        <v>540175</v>
       </c>
       <c r="R81" t="n">
-        <v>6448428</v>
+        <v>6448426</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081944</v>
+        <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>91888</v>
+        <v>95764</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540096</v>
+        <v>540180</v>
       </c>
       <c r="R82" t="n">
-        <v>6448303</v>
+        <v>6448428</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288040</v>
+        <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>105297</v>
+        <v>95775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221101</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540165</v>
+        <v>540177</v>
       </c>
       <c r="R83" t="n">
-        <v>6448488</v>
+        <v>6448499</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8962,7 +8962,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8981,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288064</v>
+        <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95775</v>
+        <v>95569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8992,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9016,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540177</v>
+        <v>540206</v>
       </c>
       <c r="R84" t="n">
-        <v>6448499</v>
+        <v>6448439</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9078,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288089</v>
+        <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95569</v>
+        <v>95796</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9089,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9113,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540206</v>
+        <v>540222</v>
       </c>
       <c r="R85" t="n">
-        <v>6448439</v>
+        <v>6448525</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9175,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288035</v>
+        <v>127288031</v>
       </c>
       <c r="B86" t="n">
-        <v>95796</v>
+        <v>100532</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9186,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2818</v>
+        <v>222771</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9210,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540222</v>
+        <v>540180</v>
       </c>
       <c r="R86" t="n">
-        <v>6448525</v>
+        <v>6448493</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9272,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>100532</v>
+        <v>105297</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,16 +9282,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R87" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9351,6 +9350,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288038</v>
+        <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>106038</v>
+        <v>95764</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R95" t="n">
-        <v>6448610</v>
+        <v>6448463</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,18 +10121,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10151,10 +10145,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288108</v>
+        <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95764</v>
+        <v>95779</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10162,16 +10156,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10186,10 +10180,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540163</v>
+        <v>540224</v>
       </c>
       <c r="R96" t="n">
-        <v>6448463</v>
+        <v>6448404</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10248,32 +10242,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288011</v>
+        <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>95779</v>
+        <v>106038</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2668</v>
+        <v>220785</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10283,10 +10277,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540224</v>
+        <v>540274</v>
       </c>
       <c r="R97" t="n">
-        <v>6448404</v>
+        <v>6448610</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10321,12 +10315,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288027</v>
+        <v>127288074</v>
       </c>
       <c r="B98" t="n">
-        <v>100532</v>
+        <v>91888</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540310</v>
+        <v>540039</v>
       </c>
       <c r="R98" t="n">
-        <v>6448579</v>
+        <v>6448303</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288074</v>
+        <v>127288057</v>
       </c>
       <c r="B101" t="n">
-        <v>91888</v>
+        <v>95775</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540039</v>
+        <v>540076</v>
       </c>
       <c r="R101" t="n">
-        <v>6448303</v>
+        <v>6448321</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288057</v>
+        <v>127288027</v>
       </c>
       <c r="B102" t="n">
-        <v>95775</v>
+        <v>100532</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540076</v>
+        <v>540310</v>
       </c>
       <c r="R102" t="n">
-        <v>6448321</v>
+        <v>6448579</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288101</v>
+        <v>127288028</v>
       </c>
       <c r="B103" t="n">
-        <v>95764</v>
+        <v>100532</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540333</v>
+        <v>540335</v>
       </c>
       <c r="R103" t="n">
-        <v>6448609</v>
+        <v>6448550</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10927,7 +10927,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288105</v>
+        <v>127288101</v>
       </c>
       <c r="B104" t="n">
         <v>95764</v>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R104" t="n">
-        <v>6448504</v>
+        <v>6448609</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B105" t="n">
-        <v>95775</v>
+        <v>95764</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R105" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288094</v>
+        <v>127288061</v>
       </c>
       <c r="B106" t="n">
-        <v>95764</v>
+        <v>95775</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R106" t="n">
-        <v>6448441</v>
+        <v>6448493</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,24 +11200,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11234,10 +11218,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288028</v>
+        <v>127288094</v>
       </c>
       <c r="B107" t="n">
-        <v>100532</v>
+        <v>95764</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11245,21 +11229,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11269,10 +11253,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540335</v>
+        <v>540171</v>
       </c>
       <c r="R107" t="n">
-        <v>6448550</v>
+        <v>6448441</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11313,8 +11297,24 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288086</v>
+        <v>127288022</v>
       </c>
       <c r="B109" t="n">
-        <v>95569</v>
+        <v>91346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R109" t="n">
-        <v>6448609</v>
+        <v>6448436</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,7 +11525,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288087</v>
+        <v>127288086</v>
       </c>
       <c r="B110" t="n">
         <v>95569</v>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R110" t="n">
-        <v>6448608</v>
+        <v>6448609</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288014</v>
+        <v>127288087</v>
       </c>
       <c r="B111" t="n">
-        <v>95779</v>
+        <v>95569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540187</v>
+        <v>540335</v>
       </c>
       <c r="R111" t="n">
-        <v>6448463</v>
+        <v>6448608</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288093</v>
+        <v>127288014</v>
       </c>
       <c r="B112" t="n">
-        <v>95764</v>
+        <v>95779</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540165</v>
+        <v>540187</v>
       </c>
       <c r="R112" t="n">
-        <v>6448484</v>
+        <v>6448463</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,24 +11798,8 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11832,32 +11816,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288022</v>
+        <v>127288093</v>
       </c>
       <c r="B113" t="n">
-        <v>91346</v>
+        <v>95764</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11851,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540171</v>
+        <v>540165</v>
       </c>
       <c r="R113" t="n">
-        <v>6448436</v>
+        <v>6448484</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11911,8 +11895,24 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288075</v>
+        <v>127288084</v>
       </c>
       <c r="B117" t="n">
-        <v>91888</v>
+        <v>95569</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540145</v>
+        <v>540075</v>
       </c>
       <c r="R117" t="n">
-        <v>6448348</v>
+        <v>6448321</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288084</v>
+        <v>127288012</v>
       </c>
       <c r="B118" t="n">
-        <v>95569</v>
+        <v>95779</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540075</v>
+        <v>540210</v>
       </c>
       <c r="R118" t="n">
-        <v>6448321</v>
+        <v>6448417</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288012</v>
+        <v>127288075</v>
       </c>
       <c r="B119" t="n">
-        <v>95779</v>
+        <v>91888</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540210</v>
+        <v>540145</v>
       </c>
       <c r="R119" t="n">
-        <v>6448417</v>
+        <v>6448348</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>79394</v>
+        <v>91286</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R125" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B126" t="n">
-        <v>91286</v>
+        <v>79394</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R126" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288078</v>
+        <v>127288017</v>
       </c>
       <c r="B128" t="n">
-        <v>91888</v>
+        <v>95779</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540193</v>
+        <v>540172</v>
       </c>
       <c r="R128" t="n">
-        <v>6448342</v>
+        <v>6448507</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288017</v>
+        <v>127288103</v>
       </c>
       <c r="B129" t="n">
-        <v>95779</v>
+        <v>95764</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,16 +13395,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540172</v>
+        <v>540182</v>
       </c>
       <c r="R129" t="n">
-        <v>6448507</v>
+        <v>6448495</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127288103</v>
+        <v>127288085</v>
       </c>
       <c r="B130" t="n">
-        <v>95764</v>
+        <v>95569</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540182</v>
+        <v>540251</v>
       </c>
       <c r="R130" t="n">
-        <v>6448495</v>
+        <v>6448599</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288085</v>
+        <v>127288058</v>
       </c>
       <c r="B131" t="n">
-        <v>95569</v>
+        <v>95775</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540251</v>
+        <v>540182</v>
       </c>
       <c r="R131" t="n">
-        <v>6448599</v>
+        <v>6448466</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127288058</v>
+        <v>127288078</v>
       </c>
       <c r="B132" t="n">
-        <v>95775</v>
+        <v>91888</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540182</v>
+        <v>540193</v>
       </c>
       <c r="R132" t="n">
-        <v>6448466</v>
+        <v>6448342</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>100532</v>
+        <v>95779</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R133" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>95779</v>
+        <v>100532</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R134" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288090</v>
+        <v>127288079</v>
       </c>
       <c r="B139" t="n">
-        <v>95569</v>
+        <v>91888</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540163</v>
+        <v>540310</v>
       </c>
       <c r="R139" t="n">
-        <v>6448518</v>
+        <v>6448579</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288079</v>
+        <v>127288068</v>
       </c>
       <c r="B140" t="n">
-        <v>91888</v>
+        <v>79394</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540310</v>
+        <v>540274</v>
       </c>
       <c r="R140" t="n">
-        <v>6448579</v>
+        <v>6448603</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288104</v>
+        <v>127288090</v>
       </c>
       <c r="B141" t="n">
-        <v>95764</v>
+        <v>95569</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R141" t="n">
-        <v>6448515</v>
+        <v>6448518</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288036</v>
+        <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95796</v>
+        <v>95764</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448578</v>
+        <v>6448515</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288034</v>
+        <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>100532</v>
+        <v>95796</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540169</v>
+        <v>540336</v>
       </c>
       <c r="R143" t="n">
-        <v>6448432</v>
+        <v>6448578</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>79394</v>
+        <v>100532</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B145" t="n">
-        <v>95779</v>
+        <v>91888</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R145" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288080</v>
+        <v>127288018</v>
       </c>
       <c r="B146" t="n">
-        <v>91888</v>
+        <v>95779</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540251</v>
+        <v>540167</v>
       </c>
       <c r="R146" t="n">
-        <v>6448423</v>
+        <v>6448513</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288020</v>
+        <v>127288081</v>
       </c>
       <c r="B150" t="n">
-        <v>95779</v>
+        <v>91888</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540165</v>
+        <v>540243</v>
       </c>
       <c r="R150" t="n">
-        <v>6448511</v>
+        <v>6448421</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288102</v>
+        <v>127288020</v>
       </c>
       <c r="B151" t="n">
-        <v>95764</v>
+        <v>95779</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,16 +15529,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540208</v>
+        <v>540165</v>
       </c>
       <c r="R151" t="n">
-        <v>6448415</v>
+        <v>6448511</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288081</v>
+        <v>127288102</v>
       </c>
       <c r="B152" t="n">
-        <v>91888</v>
+        <v>95764</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540243</v>
+        <v>540208</v>
       </c>
       <c r="R152" t="n">
-        <v>6448421</v>
+        <v>6448415</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>95892</v>
+        <v>79394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R43" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>79394</v>
+        <v>95892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R44" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081959</v>
+        <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95569</v>
+        <v>95764</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540103</v>
+        <v>540074</v>
       </c>
       <c r="R52" t="n">
-        <v>6448344</v>
+        <v>6448313</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5951,10 +5951,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127081918</v>
+        <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95775</v>
+        <v>95569</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540208</v>
+        <v>540103</v>
       </c>
       <c r="R53" t="n">
-        <v>6448378</v>
+        <v>6448344</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127081951</v>
+        <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95764</v>
+        <v>95775</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540074</v>
+        <v>540208</v>
       </c>
       <c r="R54" t="n">
-        <v>6448313</v>
+        <v>6448378</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288108</v>
+        <v>127288038</v>
       </c>
       <c r="B95" t="n">
-        <v>95764</v>
+        <v>106038</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2671</v>
+        <v>220785</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540163</v>
+        <v>540274</v>
       </c>
       <c r="R95" t="n">
-        <v>6448463</v>
+        <v>6448610</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,12 +10121,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10145,10 +10151,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288011</v>
+        <v>127288108</v>
       </c>
       <c r="B96" t="n">
-        <v>95779</v>
+        <v>95764</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10156,16 +10162,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10180,10 +10186,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540224</v>
+        <v>540163</v>
       </c>
       <c r="R96" t="n">
-        <v>6448404</v>
+        <v>6448463</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10242,32 +10248,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288038</v>
+        <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>106038</v>
+        <v>95779</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10277,10 +10283,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540274</v>
+        <v>540224</v>
       </c>
       <c r="R97" t="n">
-        <v>6448610</v>
+        <v>6448404</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10315,18 +10321,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288037</v>
+        <v>127288039</v>
       </c>
       <c r="B115" t="n">
-        <v>95796</v>
+        <v>105297</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>221101</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540213</v>
+        <v>540178</v>
       </c>
       <c r="R115" t="n">
-        <v>6448463</v>
+        <v>6448431</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288059</v>
+        <v>127288075</v>
       </c>
       <c r="B116" t="n">
-        <v>95775</v>
+        <v>91888</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540182</v>
+        <v>540145</v>
       </c>
       <c r="R116" t="n">
-        <v>6448496</v>
+        <v>6448348</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288084</v>
+        <v>127288037</v>
       </c>
       <c r="B117" t="n">
-        <v>95569</v>
+        <v>95796</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540075</v>
+        <v>540213</v>
       </c>
       <c r="R117" t="n">
-        <v>6448321</v>
+        <v>6448463</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288012</v>
+        <v>127288059</v>
       </c>
       <c r="B118" t="n">
-        <v>95779</v>
+        <v>95775</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540210</v>
+        <v>540182</v>
       </c>
       <c r="R118" t="n">
-        <v>6448417</v>
+        <v>6448496</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288075</v>
+        <v>127288084</v>
       </c>
       <c r="B119" t="n">
-        <v>91888</v>
+        <v>95569</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540145</v>
+        <v>540075</v>
       </c>
       <c r="R119" t="n">
-        <v>6448348</v>
+        <v>6448321</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288039</v>
+        <v>127288012</v>
       </c>
       <c r="B120" t="n">
-        <v>105297</v>
+        <v>95779</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221101</v>
+        <v>2668</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540178</v>
+        <v>540210</v>
       </c>
       <c r="R120" t="n">
-        <v>6448431</v>
+        <v>6448417</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>95779</v>
+        <v>100532</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R133" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>100532</v>
+        <v>95779</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R134" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288080</v>
+        <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>91888</v>
+        <v>95779</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540251</v>
+        <v>540167</v>
       </c>
       <c r="R145" t="n">
-        <v>6448423</v>
+        <v>6448513</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,7 +15033,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288018</v>
+        <v>127288015</v>
       </c>
       <c r="B146" t="n">
         <v>95779</v>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540167</v>
+        <v>540180</v>
       </c>
       <c r="R146" t="n">
-        <v>6448513</v>
+        <v>6448493</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288015</v>
+        <v>127288024</v>
       </c>
       <c r="B147" t="n">
-        <v>95779</v>
+        <v>100532</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540180</v>
+        <v>540221</v>
       </c>
       <c r="R147" t="n">
-        <v>6448493</v>
+        <v>6448466</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,7 +15227,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288024</v>
+        <v>127288032</v>
       </c>
       <c r="B148" t="n">
         <v>100532</v>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540221</v>
+        <v>540179</v>
       </c>
       <c r="R148" t="n">
-        <v>6448466</v>
+        <v>6448506</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15324,10 +15324,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127288032</v>
+        <v>127288080</v>
       </c>
       <c r="B149" t="n">
-        <v>100532</v>
+        <v>91888</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>540179</v>
+        <v>540251</v>
       </c>
       <c r="R149" t="n">
-        <v>6448506</v>
+        <v>6448423</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081932</v>
+        <v>127081949</v>
       </c>
       <c r="B47" t="n">
-        <v>75060</v>
+        <v>30129</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1460</v>
+        <v>200985</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540159</v>
+        <v>540052</v>
       </c>
       <c r="R47" t="n">
-        <v>6448374</v>
+        <v>6448313</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081921</v>
+        <v>127081932</v>
       </c>
       <c r="B48" t="n">
-        <v>95775</v>
+        <v>75060</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540200</v>
+        <v>540159</v>
       </c>
       <c r="R48" t="n">
-        <v>6448453</v>
+        <v>6448374</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081963</v>
+        <v>127081921</v>
       </c>
       <c r="B49" t="n">
         <v>95775</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R49" t="n">
-        <v>6448366</v>
+        <v>6448453</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081957</v>
+        <v>127081963</v>
       </c>
       <c r="B50" t="n">
-        <v>95569</v>
+        <v>95775</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540098</v>
+        <v>540121</v>
       </c>
       <c r="R50" t="n">
-        <v>6448341</v>
+        <v>6448366</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081949</v>
+        <v>127081957</v>
       </c>
       <c r="B51" t="n">
-        <v>30129</v>
+        <v>95569</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>200985</v>
+        <v>2779</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540052</v>
+        <v>540098</v>
       </c>
       <c r="R51" t="n">
-        <v>6448313</v>
+        <v>6448341</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081968</v>
+        <v>127081958</v>
       </c>
       <c r="B69" t="n">
-        <v>95764</v>
+        <v>91888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540109</v>
+        <v>540100</v>
       </c>
       <c r="R69" t="n">
-        <v>6448358</v>
+        <v>6448331</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B70" t="n">
-        <v>91888</v>
+        <v>95764</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R70" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B76" t="n">
-        <v>95775</v>
+        <v>9398</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,34 +8193,55 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R76" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8261,6 +8282,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8279,10 +8301,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B77" t="n">
-        <v>9398</v>
+        <v>95775</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8290,55 +8312,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R77" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8379,7 +8380,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288017</v>
+        <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>95779</v>
+        <v>91888</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540172</v>
+        <v>540193</v>
       </c>
       <c r="R128" t="n">
-        <v>6448507</v>
+        <v>6448342</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288103</v>
+        <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95764</v>
+        <v>95779</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,16 +13395,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540182</v>
+        <v>540172</v>
       </c>
       <c r="R129" t="n">
-        <v>6448495</v>
+        <v>6448507</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127288085</v>
+        <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95569</v>
+        <v>95764</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540251</v>
+        <v>540182</v>
       </c>
       <c r="R130" t="n">
-        <v>6448599</v>
+        <v>6448495</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288058</v>
+        <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95775</v>
+        <v>95569</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540182</v>
+        <v>540251</v>
       </c>
       <c r="R131" t="n">
-        <v>6448466</v>
+        <v>6448599</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127288078</v>
+        <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>91888</v>
+        <v>95775</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540193</v>
+        <v>540182</v>
       </c>
       <c r="R132" t="n">
-        <v>6448342</v>
+        <v>6448466</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B145" t="n">
-        <v>95779</v>
+        <v>91888</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R145" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,7 +15033,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288015</v>
+        <v>127288018</v>
       </c>
       <c r="B146" t="n">
         <v>95779</v>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540180</v>
+        <v>540167</v>
       </c>
       <c r="R146" t="n">
-        <v>6448493</v>
+        <v>6448513</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288024</v>
+        <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>100532</v>
+        <v>95779</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540221</v>
+        <v>540180</v>
       </c>
       <c r="R147" t="n">
-        <v>6448466</v>
+        <v>6448493</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,7 +15227,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288032</v>
+        <v>127288024</v>
       </c>
       <c r="B148" t="n">
         <v>100532</v>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540179</v>
+        <v>540221</v>
       </c>
       <c r="R148" t="n">
-        <v>6448506</v>
+        <v>6448466</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15324,10 +15324,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127288080</v>
+        <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>91888</v>
+        <v>100532</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>540251</v>
+        <v>540179</v>
       </c>
       <c r="R149" t="n">
-        <v>6448423</v>
+        <v>6448506</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127081948</v>
       </c>
       <c r="B39" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>127081927</v>
       </c>
       <c r="B40" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B43" t="n">
-        <v>79394</v>
+        <v>95896</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R43" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B44" t="n">
-        <v>95892</v>
+        <v>79398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R44" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>127081964</v>
       </c>
       <c r="B45" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081916</v>
       </c>
       <c r="B46" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081949</v>
+        <v>127081921</v>
       </c>
       <c r="B47" t="n">
-        <v>30129</v>
+        <v>95779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5380,21 +5380,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540052</v>
+        <v>540200</v>
       </c>
       <c r="R47" t="n">
-        <v>6448313</v>
+        <v>6448453</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081932</v>
+        <v>127081957</v>
       </c>
       <c r="B48" t="n">
-        <v>75060</v>
+        <v>95573</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1460</v>
+        <v>2779</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540159</v>
+        <v>540098</v>
       </c>
       <c r="R48" t="n">
-        <v>6448374</v>
+        <v>6448341</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081921</v>
+        <v>127081963</v>
       </c>
       <c r="B49" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R49" t="n">
-        <v>6448453</v>
+        <v>6448366</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081963</v>
+        <v>127081949</v>
       </c>
       <c r="B50" t="n">
-        <v>95775</v>
+        <v>30133</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>200985</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540121</v>
+        <v>540052</v>
       </c>
       <c r="R50" t="n">
-        <v>6448366</v>
+        <v>6448313</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,32 +5757,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081957</v>
+        <v>127081932</v>
       </c>
       <c r="B51" t="n">
-        <v>95569</v>
+        <v>75064</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2779</v>
+        <v>1460</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540098</v>
+        <v>540159</v>
       </c>
       <c r="R51" t="n">
-        <v>6448341</v>
+        <v>6448374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081951</v>
+        <v>127081918</v>
       </c>
       <c r="B52" t="n">
-        <v>95764</v>
+        <v>95779</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540074</v>
+        <v>540208</v>
       </c>
       <c r="R52" t="n">
-        <v>6448313</v>
+        <v>6448378</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127081918</v>
+        <v>127081951</v>
       </c>
       <c r="B54" t="n">
-        <v>95775</v>
+        <v>95768</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540208</v>
+        <v>540074</v>
       </c>
       <c r="R54" t="n">
-        <v>6448378</v>
+        <v>6448313</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6148,7 +6148,7 @@
         <v>127081939</v>
       </c>
       <c r="B55" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>127081926</v>
       </c>
       <c r="B56" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>127081940</v>
       </c>
       <c r="B57" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7018,32 +7018,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127081960</v>
+        <v>127081952</v>
       </c>
       <c r="B64" t="n">
-        <v>92528</v>
+        <v>95768</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2075</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540128</v>
+        <v>540073</v>
       </c>
       <c r="R64" t="n">
-        <v>6448358</v>
+        <v>6448314</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7118,7 +7118,7 @@
         <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7309,32 +7309,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081952</v>
+        <v>127081960</v>
       </c>
       <c r="B67" t="n">
-        <v>95764</v>
+        <v>92532</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>2075</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540073</v>
+        <v>540128</v>
       </c>
       <c r="R67" t="n">
-        <v>6448314</v>
+        <v>6448358</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081941</v>
+        <v>127081968</v>
       </c>
       <c r="B68" t="n">
-        <v>91888</v>
+        <v>95768</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540160</v>
+        <v>540109</v>
       </c>
       <c r="R68" t="n">
-        <v>6448357</v>
+        <v>6448358</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7506,7 +7506,7 @@
         <v>127081958</v>
       </c>
       <c r="B69" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081968</v>
+        <v>127081941</v>
       </c>
       <c r="B70" t="n">
-        <v>95764</v>
+        <v>91892</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540109</v>
+        <v>540160</v>
       </c>
       <c r="R70" t="n">
-        <v>6448358</v>
+        <v>6448357</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081923</v>
+        <v>127081974</v>
       </c>
       <c r="B71" t="n">
-        <v>95764</v>
+        <v>95573</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540198</v>
+        <v>540097</v>
       </c>
       <c r="R71" t="n">
-        <v>6448437</v>
+        <v>6448346</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081928</v>
+        <v>127081971</v>
       </c>
       <c r="B72" t="n">
-        <v>95775</v>
+        <v>95768</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540172</v>
+        <v>540096</v>
       </c>
       <c r="R72" t="n">
-        <v>6448411</v>
+        <v>6448345</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081945</v>
+        <v>127081923</v>
       </c>
       <c r="B73" t="n">
-        <v>91888</v>
+        <v>95768</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540092</v>
+        <v>540198</v>
       </c>
       <c r="R73" t="n">
-        <v>6448293</v>
+        <v>6448437</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081971</v>
+        <v>127081945</v>
       </c>
       <c r="B74" t="n">
-        <v>95764</v>
+        <v>91892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R74" t="n">
-        <v>6448345</v>
+        <v>6448293</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081974</v>
+        <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>95569</v>
+        <v>95779</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540097</v>
+        <v>540172</v>
       </c>
       <c r="R75" t="n">
-        <v>6448346</v>
+        <v>6448411</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>9398</v>
+        <v>95779</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,55 +8193,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R76" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8282,7 +8261,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8301,10 +8279,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B77" t="n">
-        <v>95775</v>
+        <v>9401</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8312,34 +8290,55 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R77" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8380,6 +8379,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081944</v>
+        <v>127081925</v>
       </c>
       <c r="B79" t="n">
-        <v>91888</v>
+        <v>95768</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540096</v>
+        <v>540175</v>
       </c>
       <c r="R79" t="n">
-        <v>6448303</v>
+        <v>6448426</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081976</v>
+        <v>127081944</v>
       </c>
       <c r="B80" t="n">
-        <v>95764</v>
+        <v>91892</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8603,21 +8603,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R80" t="n">
-        <v>6448349</v>
+        <v>6448303</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081925</v>
+        <v>127081924</v>
       </c>
       <c r="B81" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540175</v>
+        <v>540180</v>
       </c>
       <c r="R81" t="n">
-        <v>6448426</v>
+        <v>6448428</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081924</v>
+        <v>127081976</v>
       </c>
       <c r="B82" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540180</v>
+        <v>540092</v>
       </c>
       <c r="R82" t="n">
-        <v>6448428</v>
+        <v>6448349</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8886,7 +8886,7 @@
         <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B86" t="n">
-        <v>100532</v>
+        <v>105303</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,16 +9185,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R86" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,6 +9253,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288040</v>
+        <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>105297</v>
+        <v>100536</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,16 +9283,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540165</v>
+        <v>540180</v>
       </c>
       <c r="R87" t="n">
-        <v>6448488</v>
+        <v>6448493</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9350,7 +9351,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95779</v>
+        <v>95783</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288038</v>
+        <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>106038</v>
+        <v>95768</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R95" t="n">
-        <v>6448610</v>
+        <v>6448463</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,18 +10121,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10151,10 +10145,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288108</v>
+        <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95764</v>
+        <v>95783</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10162,16 +10156,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10186,10 +10180,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540163</v>
+        <v>540224</v>
       </c>
       <c r="R96" t="n">
-        <v>6448463</v>
+        <v>6448404</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10248,32 +10242,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288011</v>
+        <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>95779</v>
+        <v>106044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2668</v>
+        <v>220785</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10283,10 +10277,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540224</v>
+        <v>540274</v>
       </c>
       <c r="R97" t="n">
-        <v>6448404</v>
+        <v>6448610</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10321,12 +10315,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288074</v>
+        <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>91888</v>
+        <v>95783</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540039</v>
+        <v>540189</v>
       </c>
       <c r="R98" t="n">
-        <v>6448303</v>
+        <v>6448461</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,7 +10442,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288013</v>
+        <v>127288065</v>
       </c>
       <c r="B99" t="n">
         <v>95779</v>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540189</v>
+        <v>540174</v>
       </c>
       <c r="R99" t="n">
-        <v>6448461</v>
+        <v>6448468</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>95775</v>
+        <v>91892</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R100" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10639,7 +10639,7 @@
         <v>127288057</v>
       </c>
       <c r="B101" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>127288027</v>
       </c>
       <c r="B102" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288028</v>
+        <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>100532</v>
+        <v>95768</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R103" t="n">
-        <v>6448550</v>
+        <v>6448609</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10927,10 +10927,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288101</v>
+        <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R104" t="n">
-        <v>6448609</v>
+        <v>6448504</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95764</v>
+        <v>95779</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R105" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288061</v>
+        <v>127288094</v>
       </c>
       <c r="B106" t="n">
-        <v>95775</v>
+        <v>95768</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R106" t="n">
-        <v>6448493</v>
+        <v>6448441</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,8 +11200,24 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11218,10 +11234,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288094</v>
+        <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>95764</v>
+        <v>100536</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11229,21 +11245,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11253,10 +11269,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540171</v>
+        <v>540335</v>
       </c>
       <c r="R107" t="n">
-        <v>6448441</v>
+        <v>6448550</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11297,24 +11313,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288022</v>
+        <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>91346</v>
+        <v>95573</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R109" t="n">
-        <v>6448436</v>
+        <v>6448609</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,10 +11525,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288086</v>
+        <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540333</v>
+        <v>540335</v>
       </c>
       <c r="R110" t="n">
-        <v>6448609</v>
+        <v>6448608</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288087</v>
+        <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95569</v>
+        <v>95783</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540335</v>
+        <v>540187</v>
       </c>
       <c r="R111" t="n">
-        <v>6448608</v>
+        <v>6448463</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288014</v>
+        <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540187</v>
+        <v>540165</v>
       </c>
       <c r="R112" t="n">
-        <v>6448463</v>
+        <v>6448484</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,8 +11798,24 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11816,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288093</v>
+        <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>95764</v>
+        <v>91350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11851,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540165</v>
+        <v>540171</v>
       </c>
       <c r="R113" t="n">
-        <v>6448484</v>
+        <v>6448436</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11895,24 +11911,8 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11932,7 +11932,7 @@
         <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>95779</v>
+        <v>95783</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288039</v>
+        <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>105297</v>
+        <v>95800</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221101</v>
+        <v>2818</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540178</v>
+        <v>540213</v>
       </c>
       <c r="R115" t="n">
-        <v>6448431</v>
+        <v>6448463</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288075</v>
+        <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>91888</v>
+        <v>95779</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540145</v>
+        <v>540182</v>
       </c>
       <c r="R116" t="n">
-        <v>6448348</v>
+        <v>6448496</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288037</v>
+        <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>95796</v>
+        <v>91892</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2818</v>
+        <v>3884</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540213</v>
+        <v>540145</v>
       </c>
       <c r="R117" t="n">
-        <v>6448463</v>
+        <v>6448348</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288059</v>
+        <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>95775</v>
+        <v>95573</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540182</v>
+        <v>540075</v>
       </c>
       <c r="R118" t="n">
-        <v>6448496</v>
+        <v>6448321</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288084</v>
+        <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>95569</v>
+        <v>95783</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540075</v>
+        <v>540210</v>
       </c>
       <c r="R119" t="n">
-        <v>6448321</v>
+        <v>6448417</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288012</v>
+        <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>95779</v>
+        <v>105303</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2668</v>
+        <v>221101</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540210</v>
+        <v>540178</v>
       </c>
       <c r="R120" t="n">
-        <v>6448417</v>
+        <v>6448431</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12611,7 +12611,7 @@
         <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>127288088</v>
       </c>
       <c r="B122" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B125" t="n">
-        <v>91286</v>
+        <v>79398</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R125" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B126" t="n">
-        <v>79394</v>
+        <v>91290</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R126" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95779</v>
+        <v>95783</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95569</v>
+        <v>95573</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95775</v>
+        <v>95779</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>95779</v>
+        <v>95783</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288077</v>
+        <v>127288026</v>
       </c>
       <c r="B135" t="n">
-        <v>91888</v>
+        <v>100536</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540152</v>
+        <v>540319</v>
       </c>
       <c r="R135" t="n">
-        <v>6448350</v>
+        <v>6448616</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288107</v>
+        <v>127288077</v>
       </c>
       <c r="B136" t="n">
-        <v>95764</v>
+        <v>91892</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540174</v>
+        <v>540152</v>
       </c>
       <c r="R136" t="n">
-        <v>6448493</v>
+        <v>6448350</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288092</v>
+        <v>127288107</v>
       </c>
       <c r="B137" t="n">
-        <v>95777</v>
+        <v>95768</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2666</v>
+        <v>2671</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540169</v>
+        <v>540174</v>
       </c>
       <c r="R137" t="n">
-        <v>6448494</v>
+        <v>6448493</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288026</v>
+        <v>127288092</v>
       </c>
       <c r="B138" t="n">
-        <v>100532</v>
+        <v>95781</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222771</v>
+        <v>2666</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540319</v>
+        <v>540169</v>
       </c>
       <c r="R138" t="n">
-        <v>6448616</v>
+        <v>6448494</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288079</v>
+        <v>127288068</v>
       </c>
       <c r="B139" t="n">
-        <v>91888</v>
+        <v>79398</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540310</v>
+        <v>540274</v>
       </c>
       <c r="R139" t="n">
-        <v>6448579</v>
+        <v>6448603</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288068</v>
+        <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>79394</v>
+        <v>95573</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R140" t="n">
-        <v>6448603</v>
+        <v>6448518</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288090</v>
+        <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>95569</v>
+        <v>91892</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540163</v>
+        <v>540310</v>
       </c>
       <c r="R141" t="n">
-        <v>6448518</v>
+        <v>6448579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14648,7 +14648,7 @@
         <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95764</v>
+        <v>95768</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288080</v>
+        <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>91888</v>
+        <v>95783</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540251</v>
+        <v>540167</v>
       </c>
       <c r="R145" t="n">
-        <v>6448423</v>
+        <v>6448513</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>95779</v>
+        <v>91892</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R146" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15133,7 +15133,7 @@
         <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>95779</v>
+        <v>95783</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288081</v>
+        <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>91888</v>
+        <v>95783</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540243</v>
+        <v>540165</v>
       </c>
       <c r="R150" t="n">
-        <v>6448421</v>
+        <v>6448511</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288020</v>
+        <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,16 +15529,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540165</v>
+        <v>540208</v>
       </c>
       <c r="R151" t="n">
-        <v>6448511</v>
+        <v>6448415</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288102</v>
+        <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>95764</v>
+        <v>91892</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540208</v>
+        <v>540243</v>
       </c>
       <c r="R152" t="n">
-        <v>6448415</v>
+        <v>6448421</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -5563,32 +5563,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081963</v>
+        <v>127081932</v>
       </c>
       <c r="B49" t="n">
-        <v>95779</v>
+        <v>75064</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540121</v>
+        <v>540159</v>
       </c>
       <c r="R49" t="n">
-        <v>6448366</v>
+        <v>6448374</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081949</v>
+        <v>127081963</v>
       </c>
       <c r="B50" t="n">
-        <v>30133</v>
+        <v>95779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>200985</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540052</v>
+        <v>540121</v>
       </c>
       <c r="R50" t="n">
-        <v>6448313</v>
+        <v>6448366</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,32 +5757,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081932</v>
+        <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>75064</v>
+        <v>30133</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1460</v>
+        <v>200985</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540159</v>
+        <v>540052</v>
       </c>
       <c r="R51" t="n">
-        <v>6448374</v>
+        <v>6448313</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7018,32 +7018,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127081952</v>
+        <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>95768</v>
+        <v>92532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>2075</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540073</v>
+        <v>540128</v>
       </c>
       <c r="R64" t="n">
-        <v>6448314</v>
+        <v>6448358</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081920</v>
+        <v>127081952</v>
       </c>
       <c r="B65" t="n">
         <v>95768</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540200</v>
+        <v>540073</v>
       </c>
       <c r="R65" t="n">
-        <v>6448453</v>
+        <v>6448314</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081967</v>
+        <v>127081920</v>
       </c>
       <c r="B66" t="n">
         <v>95768</v>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R66" t="n">
-        <v>6448358</v>
+        <v>6448453</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,32 +7309,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081960</v>
+        <v>127081967</v>
       </c>
       <c r="B67" t="n">
-        <v>92532</v>
+        <v>95768</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540128</v>
+        <v>540121</v>
       </c>
       <c r="R67" t="n">
         <v>6448358</v>
@@ -11832,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288022</v>
+        <v>127288016</v>
       </c>
       <c r="B113" t="n">
-        <v>91350</v>
+        <v>95783</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>2668</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540171</v>
+        <v>540187</v>
       </c>
       <c r="R113" t="n">
-        <v>6448436</v>
+        <v>6448494</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B114" t="n">
-        <v>95783</v>
+        <v>91350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R114" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>100536</v>
+        <v>95783</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R133" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>95783</v>
+        <v>100536</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R134" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B139" t="n">
-        <v>79398</v>
+        <v>100536</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>100536</v>
+        <v>79398</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288064</v>
+        <v>127288031</v>
       </c>
       <c r="B83" t="n">
-        <v>95779</v>
+        <v>100536</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540177</v>
+        <v>540180</v>
       </c>
       <c r="R83" t="n">
-        <v>6448499</v>
+        <v>6448493</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288089</v>
+        <v>127288064</v>
       </c>
       <c r="B84" t="n">
-        <v>95573</v>
+        <v>95779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540206</v>
+        <v>540177</v>
       </c>
       <c r="R84" t="n">
-        <v>6448439</v>
+        <v>6448499</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B85" t="n">
-        <v>95800</v>
+        <v>95573</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R85" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288040</v>
+        <v>127288035</v>
       </c>
       <c r="B86" t="n">
-        <v>105303</v>
+        <v>95800</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221101</v>
+        <v>2818</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540165</v>
+        <v>540222</v>
       </c>
       <c r="R86" t="n">
-        <v>6448488</v>
+        <v>6448525</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,7 +9253,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9272,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>100536</v>
+        <v>105303</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,16 +9282,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R87" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9351,6 +9350,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288037</v>
+        <v>127288039</v>
       </c>
       <c r="B115" t="n">
-        <v>95800</v>
+        <v>105303</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>221101</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540213</v>
+        <v>540178</v>
       </c>
       <c r="R115" t="n">
-        <v>6448463</v>
+        <v>6448431</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288059</v>
+        <v>127288037</v>
       </c>
       <c r="B116" t="n">
-        <v>95779</v>
+        <v>95800</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540182</v>
+        <v>540213</v>
       </c>
       <c r="R116" t="n">
-        <v>6448496</v>
+        <v>6448463</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288075</v>
+        <v>127288059</v>
       </c>
       <c r="B117" t="n">
-        <v>91892</v>
+        <v>95779</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540145</v>
+        <v>540182</v>
       </c>
       <c r="R117" t="n">
-        <v>6448348</v>
+        <v>6448496</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288084</v>
+        <v>127288075</v>
       </c>
       <c r="B118" t="n">
-        <v>95573</v>
+        <v>91892</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540075</v>
+        <v>540145</v>
       </c>
       <c r="R118" t="n">
-        <v>6448321</v>
+        <v>6448348</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288012</v>
+        <v>127288084</v>
       </c>
       <c r="B119" t="n">
-        <v>95783</v>
+        <v>95573</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540210</v>
+        <v>540075</v>
       </c>
       <c r="R119" t="n">
-        <v>6448417</v>
+        <v>6448321</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288039</v>
+        <v>127288012</v>
       </c>
       <c r="B120" t="n">
-        <v>105303</v>
+        <v>95783</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221101</v>
+        <v>2668</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540178</v>
+        <v>540210</v>
       </c>
       <c r="R120" t="n">
-        <v>6448431</v>
+        <v>6448417</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288026</v>
+        <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>100536</v>
+        <v>91892</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540319</v>
+        <v>540152</v>
       </c>
       <c r="R135" t="n">
-        <v>6448616</v>
+        <v>6448350</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288077</v>
+        <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>91892</v>
+        <v>95768</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540152</v>
+        <v>540174</v>
       </c>
       <c r="R136" t="n">
-        <v>6448350</v>
+        <v>6448493</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288107</v>
+        <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95768</v>
+        <v>95781</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540174</v>
+        <v>540169</v>
       </c>
       <c r="R137" t="n">
-        <v>6448493</v>
+        <v>6448494</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288092</v>
+        <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>95781</v>
+        <v>100536</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2666</v>
+        <v>222771</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540169</v>
+        <v>540319</v>
       </c>
       <c r="R138" t="n">
-        <v>6448494</v>
+        <v>6448616</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288034</v>
+        <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>100536</v>
+        <v>95573</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222771</v>
+        <v>2779</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R139" t="n">
-        <v>6448432</v>
+        <v>6448518</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288090</v>
+        <v>127288079</v>
       </c>
       <c r="B140" t="n">
-        <v>95573</v>
+        <v>91892</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540163</v>
+        <v>540310</v>
       </c>
       <c r="R140" t="n">
-        <v>6448518</v>
+        <v>6448579</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288079</v>
+        <v>127288104</v>
       </c>
       <c r="B141" t="n">
-        <v>91892</v>
+        <v>95768</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540310</v>
+        <v>540169</v>
       </c>
       <c r="R141" t="n">
-        <v>6448579</v>
+        <v>6448515</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288104</v>
+        <v>127288036</v>
       </c>
       <c r="B142" t="n">
-        <v>95768</v>
+        <v>95800</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>2818</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540169</v>
+        <v>540336</v>
       </c>
       <c r="R142" t="n">
-        <v>6448515</v>
+        <v>6448578</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288036</v>
+        <v>127288068</v>
       </c>
       <c r="B143" t="n">
-        <v>95800</v>
+        <v>79398</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2818</v>
+        <v>6431</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540336</v>
+        <v>540274</v>
       </c>
       <c r="R143" t="n">
-        <v>6448578</v>
+        <v>6448603</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>79398</v>
+        <v>100536</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>95896</v>
+        <v>79398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R43" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>79398</v>
+        <v>95896</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R44" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081921</v>
+        <v>127081932</v>
       </c>
       <c r="B47" t="n">
-        <v>95779</v>
+        <v>75064</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540200</v>
+        <v>540159</v>
       </c>
       <c r="R47" t="n">
-        <v>6448453</v>
+        <v>6448374</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081957</v>
+        <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>95573</v>
+        <v>95779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540098</v>
+        <v>540200</v>
       </c>
       <c r="R48" t="n">
-        <v>6448341</v>
+        <v>6448453</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,32 +5563,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081932</v>
+        <v>127081963</v>
       </c>
       <c r="B49" t="n">
-        <v>75064</v>
+        <v>95779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540159</v>
+        <v>540121</v>
       </c>
       <c r="R49" t="n">
-        <v>6448374</v>
+        <v>6448366</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081963</v>
+        <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>95779</v>
+        <v>95573</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540121</v>
+        <v>540098</v>
       </c>
       <c r="R50" t="n">
-        <v>6448366</v>
+        <v>6448341</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127081918</v>
+        <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540208</v>
+        <v>540074</v>
       </c>
       <c r="R52" t="n">
-        <v>6448378</v>
+        <v>6448313</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127081951</v>
+        <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95768</v>
+        <v>95779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540074</v>
+        <v>540208</v>
       </c>
       <c r="R54" t="n">
-        <v>6448313</v>
+        <v>6448378</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6342,7 +6342,7 @@
         <v>127081940</v>
       </c>
       <c r="B57" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127081942</v>
+        <v>127081954</v>
       </c>
       <c r="B62" t="n">
-        <v>91892</v>
+        <v>95779</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540102</v>
+        <v>540093</v>
       </c>
       <c r="R62" t="n">
-        <v>6448315</v>
+        <v>6448328</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127081954</v>
+        <v>127081942</v>
       </c>
       <c r="B63" t="n">
-        <v>95779</v>
+        <v>91892</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540093</v>
+        <v>540102</v>
       </c>
       <c r="R63" t="n">
-        <v>6448328</v>
+        <v>6448315</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081952</v>
+        <v>127081920</v>
       </c>
       <c r="B65" t="n">
         <v>95768</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540073</v>
+        <v>540200</v>
       </c>
       <c r="R65" t="n">
-        <v>6448314</v>
+        <v>6448453</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081920</v>
+        <v>127081967</v>
       </c>
       <c r="B66" t="n">
         <v>95768</v>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R66" t="n">
-        <v>6448453</v>
+        <v>6448358</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,7 +7309,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081967</v>
+        <v>127081952</v>
       </c>
       <c r="B67" t="n">
         <v>95768</v>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540121</v>
+        <v>540073</v>
       </c>
       <c r="R67" t="n">
-        <v>6448358</v>
+        <v>6448314</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081958</v>
+        <v>127081941</v>
       </c>
       <c r="B69" t="n">
         <v>91892</v>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540100</v>
+        <v>540160</v>
       </c>
       <c r="R69" t="n">
-        <v>6448331</v>
+        <v>6448357</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,7 +7600,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B70" t="n">
         <v>91892</v>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R70" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081974</v>
+        <v>127081971</v>
       </c>
       <c r="B71" t="n">
-        <v>95573</v>
+        <v>95768</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540097</v>
+        <v>540096</v>
       </c>
       <c r="R71" t="n">
-        <v>6448346</v>
+        <v>6448345</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081971</v>
+        <v>127081974</v>
       </c>
       <c r="B72" t="n">
-        <v>95768</v>
+        <v>95573</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540096</v>
+        <v>540097</v>
       </c>
       <c r="R72" t="n">
-        <v>6448345</v>
+        <v>6448346</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081945</v>
+        <v>127081928</v>
       </c>
       <c r="B74" t="n">
-        <v>91892</v>
+        <v>95779</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540092</v>
+        <v>540172</v>
       </c>
       <c r="R74" t="n">
-        <v>6448293</v>
+        <v>6448411</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081928</v>
+        <v>127081945</v>
       </c>
       <c r="B75" t="n">
-        <v>95779</v>
+        <v>91892</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540172</v>
+        <v>540092</v>
       </c>
       <c r="R75" t="n">
-        <v>6448411</v>
+        <v>6448293</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8495,7 +8495,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081925</v>
+        <v>127081976</v>
       </c>
       <c r="B79" t="n">
         <v>95768</v>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540175</v>
+        <v>540092</v>
       </c>
       <c r="R79" t="n">
-        <v>6448426</v>
+        <v>6448349</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081944</v>
+        <v>127081925</v>
       </c>
       <c r="B80" t="n">
-        <v>91892</v>
+        <v>95768</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8603,21 +8603,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540096</v>
+        <v>540175</v>
       </c>
       <c r="R80" t="n">
-        <v>6448303</v>
+        <v>6448426</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081976</v>
+        <v>127081944</v>
       </c>
       <c r="B82" t="n">
-        <v>95768</v>
+        <v>91892</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R82" t="n">
-        <v>6448349</v>
+        <v>6448303</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8886,7 +8886,7 @@
         <v>127288031</v>
       </c>
       <c r="B83" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288064</v>
+        <v>127288040</v>
       </c>
       <c r="B84" t="n">
-        <v>95779</v>
+        <v>105305</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>221101</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540177</v>
+        <v>540165</v>
       </c>
       <c r="R84" t="n">
-        <v>6448499</v>
+        <v>6448488</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9059,6 +9059,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9077,10 +9078,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288089</v>
+        <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95573</v>
+        <v>95800</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9089,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540206</v>
+        <v>540222</v>
       </c>
       <c r="R85" t="n">
-        <v>6448439</v>
+        <v>6448525</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9175,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B86" t="n">
-        <v>95800</v>
+        <v>95573</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9186,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9210,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R86" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288040</v>
+        <v>127288064</v>
       </c>
       <c r="B87" t="n">
-        <v>105303</v>
+        <v>95779</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,21 +9283,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221101</v>
+        <v>2667</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540165</v>
+        <v>540177</v>
       </c>
       <c r="R87" t="n">
-        <v>6448488</v>
+        <v>6448499</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9350,7 +9351,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288100</v>
+        <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>95768</v>
+        <v>100537</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540237</v>
       </c>
       <c r="R88" t="n">
-        <v>6448342</v>
+        <v>6448446</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288060</v>
+        <v>127288100</v>
       </c>
       <c r="B90" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540187</v>
+        <v>540195</v>
       </c>
       <c r="R90" t="n">
-        <v>6448488</v>
+        <v>6448342</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288023</v>
+        <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>100536</v>
+        <v>95779</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540237</v>
+        <v>540187</v>
       </c>
       <c r="R91" t="n">
-        <v>6448446</v>
+        <v>6448488</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127288082</v>
+        <v>127288025</v>
       </c>
       <c r="B93" t="n">
-        <v>91892</v>
+        <v>100537</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,21 +9865,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540219</v>
+        <v>540221</v>
       </c>
       <c r="R93" t="n">
-        <v>6448415</v>
+        <v>6448522</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127288025</v>
+        <v>127288082</v>
       </c>
       <c r="B94" t="n">
-        <v>100536</v>
+        <v>91892</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9962,21 +9962,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540221</v>
+        <v>540219</v>
       </c>
       <c r="R94" t="n">
-        <v>6448522</v>
+        <v>6448415</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10245,7 +10245,7 @@
         <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288013</v>
+        <v>127288027</v>
       </c>
       <c r="B98" t="n">
-        <v>95783</v>
+        <v>100537</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540189</v>
+        <v>540310</v>
       </c>
       <c r="R98" t="n">
-        <v>6448461</v>
+        <v>6448579</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B99" t="n">
-        <v>95779</v>
+        <v>91892</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R99" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288074</v>
+        <v>127288013</v>
       </c>
       <c r="B100" t="n">
-        <v>91892</v>
+        <v>95783</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540039</v>
+        <v>540189</v>
       </c>
       <c r="R100" t="n">
-        <v>6448303</v>
+        <v>6448461</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288057</v>
+        <v>127288065</v>
       </c>
       <c r="B101" t="n">
         <v>95779</v>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540076</v>
+        <v>540174</v>
       </c>
       <c r="R101" t="n">
-        <v>6448321</v>
+        <v>6448468</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288027</v>
+        <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>100536</v>
+        <v>95779</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540310</v>
+        <v>540076</v>
       </c>
       <c r="R102" t="n">
-        <v>6448579</v>
+        <v>6448321</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10830,7 +10830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288101</v>
+        <v>127288094</v>
       </c>
       <c r="B103" t="n">
         <v>95768</v>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R103" t="n">
-        <v>6448609</v>
+        <v>6448441</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10909,8 +10909,24 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -10927,10 +10943,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B104" t="n">
-        <v>95768</v>
+        <v>95779</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10938,21 +10954,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10962,10 +10978,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R104" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11040,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B105" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11051,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11075,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R105" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,7 +11137,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288094</v>
+        <v>127288101</v>
       </c>
       <c r="B106" t="n">
         <v>95768</v>
@@ -11156,10 +11172,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R106" t="n">
-        <v>6448441</v>
+        <v>6448609</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,24 +11216,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11237,7 +11237,7 @@
         <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288086</v>
+        <v>127288022</v>
       </c>
       <c r="B109" t="n">
-        <v>95573</v>
+        <v>91350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R109" t="n">
-        <v>6448609</v>
+        <v>6448436</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,7 +11525,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288087</v>
+        <v>127288086</v>
       </c>
       <c r="B110" t="n">
         <v>95573</v>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R110" t="n">
-        <v>6448608</v>
+        <v>6448609</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288022</v>
+        <v>127288087</v>
       </c>
       <c r="B114" t="n">
-        <v>91350</v>
+        <v>95573</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540171</v>
+        <v>540335</v>
       </c>
       <c r="R114" t="n">
-        <v>6448436</v>
+        <v>6448608</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288039</v>
+        <v>127288075</v>
       </c>
       <c r="B115" t="n">
-        <v>105303</v>
+        <v>91892</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221101</v>
+        <v>3884</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540178</v>
+        <v>540145</v>
       </c>
       <c r="R115" t="n">
-        <v>6448431</v>
+        <v>6448348</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288037</v>
+        <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95800</v>
+        <v>95779</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540213</v>
+        <v>540182</v>
       </c>
       <c r="R116" t="n">
-        <v>6448463</v>
+        <v>6448496</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288059</v>
+        <v>127288084</v>
       </c>
       <c r="B117" t="n">
-        <v>95779</v>
+        <v>95573</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540182</v>
+        <v>540075</v>
       </c>
       <c r="R117" t="n">
-        <v>6448496</v>
+        <v>6448321</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288075</v>
+        <v>127288012</v>
       </c>
       <c r="B118" t="n">
-        <v>91892</v>
+        <v>95783</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540145</v>
+        <v>540210</v>
       </c>
       <c r="R118" t="n">
-        <v>6448348</v>
+        <v>6448417</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288084</v>
+        <v>127288037</v>
       </c>
       <c r="B119" t="n">
-        <v>95573</v>
+        <v>95800</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540075</v>
+        <v>540213</v>
       </c>
       <c r="R119" t="n">
-        <v>6448321</v>
+        <v>6448463</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288012</v>
+        <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>95783</v>
+        <v>105305</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2668</v>
+        <v>221101</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540210</v>
+        <v>540178</v>
       </c>
       <c r="R120" t="n">
-        <v>6448417</v>
+        <v>6448431</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12705,7 +12705,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288088</v>
+        <v>127288091</v>
       </c>
       <c r="B122" t="n">
         <v>95573</v>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540338</v>
+        <v>540169</v>
       </c>
       <c r="R122" t="n">
-        <v>6448617</v>
+        <v>6448494</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288091</v>
+        <v>127288062</v>
       </c>
       <c r="B123" t="n">
-        <v>95573</v>
+        <v>95779</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12813,21 +12813,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540169</v>
+        <v>540177</v>
       </c>
       <c r="R123" t="n">
-        <v>6448494</v>
+        <v>6448495</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12899,10 +12899,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127288062</v>
+        <v>127288088</v>
       </c>
       <c r="B124" t="n">
-        <v>95779</v>
+        <v>95573</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12910,21 +12910,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12934,10 +12934,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540177</v>
+        <v>540338</v>
       </c>
       <c r="R124" t="n">
-        <v>6448495</v>
+        <v>6448617</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>79398</v>
+        <v>91290</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R125" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B126" t="n">
-        <v>91290</v>
+        <v>79398</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R126" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127288103</v>
+        <v>127288085</v>
       </c>
       <c r="B130" t="n">
-        <v>95768</v>
+        <v>95573</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540182</v>
+        <v>540251</v>
       </c>
       <c r="R130" t="n">
-        <v>6448495</v>
+        <v>6448599</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288085</v>
+        <v>127288103</v>
       </c>
       <c r="B131" t="n">
-        <v>95573</v>
+        <v>95768</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540251</v>
+        <v>540182</v>
       </c>
       <c r="R131" t="n">
-        <v>6448599</v>
+        <v>6448495</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13872,7 +13872,7 @@
         <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288077</v>
+        <v>127288026</v>
       </c>
       <c r="B135" t="n">
-        <v>91892</v>
+        <v>100537</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540152</v>
+        <v>540319</v>
       </c>
       <c r="R135" t="n">
-        <v>6448350</v>
+        <v>6448616</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288107</v>
+        <v>127288077</v>
       </c>
       <c r="B136" t="n">
-        <v>95768</v>
+        <v>91892</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540174</v>
+        <v>540152</v>
       </c>
       <c r="R136" t="n">
-        <v>6448493</v>
+        <v>6448350</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288026</v>
+        <v>127288107</v>
       </c>
       <c r="B138" t="n">
-        <v>100536</v>
+        <v>95768</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540319</v>
+        <v>540174</v>
       </c>
       <c r="R138" t="n">
-        <v>6448616</v>
+        <v>6448493</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288090</v>
+        <v>127288034</v>
       </c>
       <c r="B139" t="n">
-        <v>95573</v>
+        <v>100537</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448518</v>
+        <v>6448432</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288104</v>
+        <v>127288090</v>
       </c>
       <c r="B141" t="n">
-        <v>95768</v>
+        <v>95573</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R141" t="n">
-        <v>6448515</v>
+        <v>6448518</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288036</v>
+        <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448578</v>
+        <v>6448515</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288068</v>
+        <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>79398</v>
+        <v>95800</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6431</v>
+        <v>2818</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540274</v>
+        <v>540336</v>
       </c>
       <c r="R143" t="n">
-        <v>6448603</v>
+        <v>6448578</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>100536</v>
+        <v>79398</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B145" t="n">
-        <v>95783</v>
+        <v>91892</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R145" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288080</v>
+        <v>127288024</v>
       </c>
       <c r="B146" t="n">
-        <v>91892</v>
+        <v>100537</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540251</v>
+        <v>540221</v>
       </c>
       <c r="R146" t="n">
-        <v>6448423</v>
+        <v>6448466</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288015</v>
+        <v>127288032</v>
       </c>
       <c r="B147" t="n">
-        <v>95783</v>
+        <v>100537</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540180</v>
+        <v>540179</v>
       </c>
       <c r="R147" t="n">
-        <v>6448493</v>
+        <v>6448506</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,10 +15227,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288024</v>
+        <v>127288018</v>
       </c>
       <c r="B148" t="n">
-        <v>100536</v>
+        <v>95783</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15238,21 +15238,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540221</v>
+        <v>540167</v>
       </c>
       <c r="R148" t="n">
-        <v>6448466</v>
+        <v>6448513</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15324,10 +15324,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127288032</v>
+        <v>127288015</v>
       </c>
       <c r="B149" t="n">
-        <v>100536</v>
+        <v>95783</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>540179</v>
+        <v>540180</v>
       </c>
       <c r="R149" t="n">
-        <v>6448506</v>
+        <v>6448493</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288020</v>
+        <v>127288081</v>
       </c>
       <c r="B150" t="n">
-        <v>95783</v>
+        <v>91892</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540165</v>
+        <v>540243</v>
       </c>
       <c r="R150" t="n">
-        <v>6448511</v>
+        <v>6448421</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288081</v>
+        <v>127288020</v>
       </c>
       <c r="B152" t="n">
-        <v>91892</v>
+        <v>95783</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540243</v>
+        <v>540165</v>
       </c>
       <c r="R152" t="n">
-        <v>6448421</v>
+        <v>6448511</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081971</v>
+        <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>95768</v>
+        <v>91892</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R71" t="n">
-        <v>6448345</v>
+        <v>6448293</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081974</v>
+        <v>127081971</v>
       </c>
       <c r="B72" t="n">
-        <v>95573</v>
+        <v>95768</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540097</v>
+        <v>540096</v>
       </c>
       <c r="R72" t="n">
-        <v>6448346</v>
+        <v>6448345</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081923</v>
+        <v>127081974</v>
       </c>
       <c r="B73" t="n">
-        <v>95768</v>
+        <v>95573</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540198</v>
+        <v>540097</v>
       </c>
       <c r="R73" t="n">
-        <v>6448437</v>
+        <v>6448346</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081928</v>
+        <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540172</v>
+        <v>540198</v>
       </c>
       <c r="R74" t="n">
-        <v>6448411</v>
+        <v>6448437</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081945</v>
+        <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>91892</v>
+        <v>95779</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540092</v>
+        <v>540172</v>
       </c>
       <c r="R75" t="n">
-        <v>6448293</v>
+        <v>6448411</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081976</v>
+        <v>127081944</v>
       </c>
       <c r="B79" t="n">
-        <v>95768</v>
+        <v>91892</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R79" t="n">
-        <v>6448349</v>
+        <v>6448303</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081925</v>
+        <v>127081976</v>
       </c>
       <c r="B80" t="n">
         <v>95768</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540175</v>
+        <v>540092</v>
       </c>
       <c r="R80" t="n">
-        <v>6448426</v>
+        <v>6448349</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081924</v>
+        <v>127081925</v>
       </c>
       <c r="B81" t="n">
         <v>95768</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540180</v>
+        <v>540175</v>
       </c>
       <c r="R81" t="n">
-        <v>6448428</v>
+        <v>6448426</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081944</v>
+        <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>91892</v>
+        <v>95768</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540096</v>
+        <v>540180</v>
       </c>
       <c r="R82" t="n">
-        <v>6448303</v>
+        <v>6448428</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288094</v>
+        <v>127288028</v>
       </c>
       <c r="B103" t="n">
-        <v>95768</v>
+        <v>100537</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540171</v>
+        <v>540335</v>
       </c>
       <c r="R103" t="n">
-        <v>6448441</v>
+        <v>6448550</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10909,24 +10909,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11234,10 +11218,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288028</v>
+        <v>127288094</v>
       </c>
       <c r="B107" t="n">
-        <v>100537</v>
+        <v>95768</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11245,21 +11229,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11269,10 +11253,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540335</v>
+        <v>540171</v>
       </c>
       <c r="R107" t="n">
-        <v>6448550</v>
+        <v>6448441</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11313,8 +11297,24 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288078</v>
+        <v>127288017</v>
       </c>
       <c r="B128" t="n">
-        <v>91892</v>
+        <v>95783</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540193</v>
+        <v>540172</v>
       </c>
       <c r="R128" t="n">
-        <v>6448342</v>
+        <v>6448507</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288017</v>
+        <v>127288085</v>
       </c>
       <c r="B129" t="n">
-        <v>95783</v>
+        <v>95573</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540172</v>
+        <v>540251</v>
       </c>
       <c r="R129" t="n">
-        <v>6448507</v>
+        <v>6448599</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127288085</v>
+        <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95573</v>
+        <v>95768</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540251</v>
+        <v>540182</v>
       </c>
       <c r="R130" t="n">
-        <v>6448599</v>
+        <v>6448495</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288103</v>
+        <v>127288058</v>
       </c>
       <c r="B131" t="n">
-        <v>95768</v>
+        <v>95779</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13616,7 +13616,7 @@
         <v>540182</v>
       </c>
       <c r="R131" t="n">
-        <v>6448495</v>
+        <v>6448466</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127288058</v>
+        <v>127288078</v>
       </c>
       <c r="B132" t="n">
-        <v>95779</v>
+        <v>91892</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540182</v>
+        <v>540193</v>
       </c>
       <c r="R132" t="n">
-        <v>6448466</v>
+        <v>6448342</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B139" t="n">
-        <v>100537</v>
+        <v>79398</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R139" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>79398</v>
+        <v>100537</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288080</v>
+        <v>127288024</v>
       </c>
       <c r="B145" t="n">
-        <v>91892</v>
+        <v>100537</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540251</v>
+        <v>540221</v>
       </c>
       <c r="R145" t="n">
-        <v>6448423</v>
+        <v>6448466</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,7 +15033,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288024</v>
+        <v>127288032</v>
       </c>
       <c r="B146" t="n">
         <v>100537</v>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540221</v>
+        <v>540179</v>
       </c>
       <c r="R146" t="n">
-        <v>6448466</v>
+        <v>6448506</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288032</v>
+        <v>127288080</v>
       </c>
       <c r="B147" t="n">
-        <v>100537</v>
+        <v>91892</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540179</v>
+        <v>540251</v>
       </c>
       <c r="R147" t="n">
-        <v>6448506</v>
+        <v>6448423</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92532</v>
+        <v>92534</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127081948</v>
       </c>
       <c r="B39" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>127081927</v>
       </c>
       <c r="B40" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B43" t="n">
-        <v>79398</v>
+        <v>95898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R43" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B44" t="n">
-        <v>95896</v>
+        <v>79400</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R44" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>127081964</v>
       </c>
       <c r="B45" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081916</v>
       </c>
       <c r="B46" t="n">
-        <v>91892</v>
+        <v>91894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081932</v>
+        <v>127081949</v>
       </c>
       <c r="B47" t="n">
-        <v>75064</v>
+        <v>30135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1460</v>
+        <v>200985</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540159</v>
+        <v>540052</v>
       </c>
       <c r="R47" t="n">
-        <v>6448374</v>
+        <v>6448313</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081921</v>
+        <v>127081932</v>
       </c>
       <c r="B48" t="n">
-        <v>95779</v>
+        <v>75066</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540200</v>
+        <v>540159</v>
       </c>
       <c r="R48" t="n">
-        <v>6448453</v>
+        <v>6448374</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081963</v>
+        <v>127081921</v>
       </c>
       <c r="B49" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R49" t="n">
-        <v>6448366</v>
+        <v>6448453</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081957</v>
+        <v>127081963</v>
       </c>
       <c r="B50" t="n">
-        <v>95573</v>
+        <v>95781</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540098</v>
+        <v>540121</v>
       </c>
       <c r="R50" t="n">
-        <v>6448341</v>
+        <v>6448366</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081949</v>
+        <v>127081957</v>
       </c>
       <c r="B51" t="n">
-        <v>30133</v>
+        <v>95575</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>200985</v>
+        <v>2779</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540052</v>
+        <v>540098</v>
       </c>
       <c r="R51" t="n">
-        <v>6448313</v>
+        <v>6448341</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5857,7 +5857,7 @@
         <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>127081939</v>
       </c>
       <c r="B55" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>127081926</v>
       </c>
       <c r="B56" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>127081940</v>
       </c>
       <c r="B57" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127081954</v>
       </c>
       <c r="B62" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127081942</v>
       </c>
       <c r="B63" t="n">
-        <v>91892</v>
+        <v>91894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>92532</v>
+        <v>92534</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>127081968</v>
       </c>
       <c r="B68" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B69" t="n">
-        <v>91892</v>
+        <v>91894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R69" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081958</v>
+        <v>127081941</v>
       </c>
       <c r="B70" t="n">
-        <v>91892</v>
+        <v>91894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540100</v>
+        <v>540160</v>
       </c>
       <c r="R70" t="n">
-        <v>6448331</v>
+        <v>6448357</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081945</v>
+        <v>127081971</v>
       </c>
       <c r="B71" t="n">
-        <v>91892</v>
+        <v>95770</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R71" t="n">
-        <v>6448293</v>
+        <v>6448345</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081971</v>
+        <v>127081974</v>
       </c>
       <c r="B72" t="n">
-        <v>95768</v>
+        <v>95575</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540096</v>
+        <v>540097</v>
       </c>
       <c r="R72" t="n">
-        <v>6448345</v>
+        <v>6448346</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081974</v>
+        <v>127081923</v>
       </c>
       <c r="B73" t="n">
-        <v>95573</v>
+        <v>95770</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540097</v>
+        <v>540198</v>
       </c>
       <c r="R73" t="n">
-        <v>6448346</v>
+        <v>6448437</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081923</v>
+        <v>127081928</v>
       </c>
       <c r="B74" t="n">
-        <v>95768</v>
+        <v>95781</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540198</v>
+        <v>540172</v>
       </c>
       <c r="R74" t="n">
-        <v>6448437</v>
+        <v>6448411</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081928</v>
+        <v>127081945</v>
       </c>
       <c r="B75" t="n">
-        <v>95779</v>
+        <v>91894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540172</v>
+        <v>540092</v>
       </c>
       <c r="R75" t="n">
-        <v>6448411</v>
+        <v>6448293</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8185,7 +8185,7 @@
         <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92532</v>
+        <v>92534</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081944</v>
+        <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>91892</v>
+        <v>95770</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R79" t="n">
-        <v>6448303</v>
+        <v>6448349</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081976</v>
+        <v>127081925</v>
       </c>
       <c r="B80" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540092</v>
+        <v>540175</v>
       </c>
       <c r="R80" t="n">
-        <v>6448349</v>
+        <v>6448426</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081925</v>
+        <v>127081924</v>
       </c>
       <c r="B81" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540175</v>
+        <v>540180</v>
       </c>
       <c r="R81" t="n">
-        <v>6448426</v>
+        <v>6448428</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081924</v>
+        <v>127081944</v>
       </c>
       <c r="B82" t="n">
-        <v>95768</v>
+        <v>91894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540180</v>
+        <v>540096</v>
       </c>
       <c r="R82" t="n">
-        <v>6448428</v>
+        <v>6448303</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288031</v>
+        <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>100537</v>
+        <v>95781</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540180</v>
+        <v>540177</v>
       </c>
       <c r="R83" t="n">
-        <v>6448493</v>
+        <v>6448499</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288040</v>
+        <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>105305</v>
+        <v>95575</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221101</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540165</v>
+        <v>540206</v>
       </c>
       <c r="R84" t="n">
-        <v>6448488</v>
+        <v>6448439</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9059,7 +9059,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9081,7 +9080,7 @@
         <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95800</v>
+        <v>95802</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9175,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288089</v>
+        <v>127288031</v>
       </c>
       <c r="B86" t="n">
-        <v>95573</v>
+        <v>100539</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9186,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9210,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540206</v>
+        <v>540180</v>
       </c>
       <c r="R86" t="n">
-        <v>6448439</v>
+        <v>6448493</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9272,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288064</v>
+        <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>95779</v>
+        <v>105307</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,21 +9282,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2667</v>
+        <v>221101</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540177</v>
+        <v>540165</v>
       </c>
       <c r="R87" t="n">
-        <v>6448499</v>
+        <v>6448488</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9351,6 +9350,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288019</v>
+        <v>127288100</v>
       </c>
       <c r="B89" t="n">
-        <v>95783</v>
+        <v>95770</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540163</v>
+        <v>540195</v>
       </c>
       <c r="R89" t="n">
-        <v>6448517</v>
+        <v>6448342</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288100</v>
+        <v>127288019</v>
       </c>
       <c r="B90" t="n">
-        <v>95768</v>
+        <v>95785</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,16 +9574,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540195</v>
+        <v>540163</v>
       </c>
       <c r="R90" t="n">
-        <v>6448342</v>
+        <v>6448517</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9663,7 +9663,7 @@
         <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127288025</v>
+        <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>100537</v>
+        <v>91894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,21 +9865,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540221</v>
+        <v>540219</v>
       </c>
       <c r="R93" t="n">
-        <v>6448522</v>
+        <v>6448415</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127288082</v>
+        <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>91892</v>
+        <v>100539</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9962,21 +9962,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540219</v>
+        <v>540221</v>
       </c>
       <c r="R94" t="n">
-        <v>6448415</v>
+        <v>6448522</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10051,7 +10051,7 @@
         <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95783</v>
+        <v>95785</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>106046</v>
+        <v>106048</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>127288027</v>
       </c>
       <c r="B98" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288074</v>
+        <v>127288013</v>
       </c>
       <c r="B99" t="n">
-        <v>91892</v>
+        <v>95785</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540039</v>
+        <v>540189</v>
       </c>
       <c r="R99" t="n">
-        <v>6448303</v>
+        <v>6448461</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288013</v>
+        <v>127288065</v>
       </c>
       <c r="B100" t="n">
-        <v>95783</v>
+        <v>95781</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540189</v>
+        <v>540174</v>
       </c>
       <c r="R100" t="n">
-        <v>6448461</v>
+        <v>6448468</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B101" t="n">
-        <v>95779</v>
+        <v>91894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R101" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10736,7 +10736,7 @@
         <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288028</v>
+        <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>100537</v>
+        <v>95770</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R103" t="n">
-        <v>6448550</v>
+        <v>6448609</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10927,10 +10927,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95779</v>
+        <v>95770</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10938,21 +10938,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R104" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95768</v>
+        <v>95781</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R105" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288101</v>
+        <v>127288094</v>
       </c>
       <c r="B106" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R106" t="n">
-        <v>6448609</v>
+        <v>6448441</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,8 +11200,24 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11218,10 +11234,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288094</v>
+        <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>95768</v>
+        <v>100539</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11229,21 +11245,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11253,10 +11269,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540171</v>
+        <v>540335</v>
       </c>
       <c r="R107" t="n">
-        <v>6448441</v>
+        <v>6448550</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11297,24 +11313,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288022</v>
+        <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>91350</v>
+        <v>95575</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R109" t="n">
-        <v>6448436</v>
+        <v>6448609</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,10 +11525,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288086</v>
+        <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540333</v>
+        <v>540335</v>
       </c>
       <c r="R110" t="n">
-        <v>6448609</v>
+        <v>6448608</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11625,7 +11625,7 @@
         <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95783</v>
+        <v>95785</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11832,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>95783</v>
+        <v>91352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R113" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11929,10 +11929,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288087</v>
+        <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>95573</v>
+        <v>95785</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11940,21 +11940,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540335</v>
+        <v>540187</v>
       </c>
       <c r="R114" t="n">
-        <v>6448608</v>
+        <v>6448494</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288075</v>
+        <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>91892</v>
+        <v>95802</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3884</v>
+        <v>2818</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540145</v>
+        <v>540213</v>
       </c>
       <c r="R115" t="n">
-        <v>6448348</v>
+        <v>6448463</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12126,7 +12126,7 @@
         <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288084</v>
+        <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>95573</v>
+        <v>91894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540075</v>
+        <v>540145</v>
       </c>
       <c r="R117" t="n">
-        <v>6448321</v>
+        <v>6448348</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288012</v>
+        <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>95783</v>
+        <v>95575</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540210</v>
+        <v>540075</v>
       </c>
       <c r="R118" t="n">
-        <v>6448417</v>
+        <v>6448321</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288037</v>
+        <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>95800</v>
+        <v>95785</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2818</v>
+        <v>2668</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540213</v>
+        <v>540210</v>
       </c>
       <c r="R119" t="n">
-        <v>6448463</v>
+        <v>6448417</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12514,7 +12514,7 @@
         <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>105305</v>
+        <v>105307</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>91892</v>
+        <v>91894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288091</v>
+        <v>127288088</v>
       </c>
       <c r="B122" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540169</v>
+        <v>540338</v>
       </c>
       <c r="R122" t="n">
-        <v>6448494</v>
+        <v>6448617</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288062</v>
+        <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>95779</v>
+        <v>95575</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12813,21 +12813,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540177</v>
+        <v>540169</v>
       </c>
       <c r="R123" t="n">
-        <v>6448495</v>
+        <v>6448494</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12899,10 +12899,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127288088</v>
+        <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95573</v>
+        <v>95781</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12910,21 +12910,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12934,10 +12934,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540338</v>
+        <v>540177</v>
       </c>
       <c r="R124" t="n">
-        <v>6448617</v>
+        <v>6448495</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -12999,7 +12999,7 @@
         <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>91290</v>
+        <v>91292</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>127288069</v>
       </c>
       <c r="B126" t="n">
-        <v>79398</v>
+        <v>79400</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288017</v>
+        <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>95783</v>
+        <v>91894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540172</v>
+        <v>540193</v>
       </c>
       <c r="R128" t="n">
-        <v>6448507</v>
+        <v>6448342</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288085</v>
+        <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95573</v>
+        <v>95785</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540251</v>
+        <v>540172</v>
       </c>
       <c r="R129" t="n">
-        <v>6448599</v>
+        <v>6448507</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288058</v>
+        <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95779</v>
+        <v>95575</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540182</v>
+        <v>540251</v>
       </c>
       <c r="R131" t="n">
-        <v>6448466</v>
+        <v>6448599</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127288078</v>
+        <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>91892</v>
+        <v>95781</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540193</v>
+        <v>540182</v>
       </c>
       <c r="R132" t="n">
-        <v>6448342</v>
+        <v>6448466</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>95783</v>
+        <v>100539</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R133" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>100537</v>
+        <v>95785</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R134" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288026</v>
+        <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>100537</v>
+        <v>91894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540319</v>
+        <v>540152</v>
       </c>
       <c r="R135" t="n">
-        <v>6448616</v>
+        <v>6448350</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288077</v>
+        <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>91892</v>
+        <v>95770</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540152</v>
+        <v>540174</v>
       </c>
       <c r="R136" t="n">
-        <v>6448350</v>
+        <v>6448493</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14163,7 +14163,7 @@
         <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95781</v>
+        <v>95783</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288107</v>
+        <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>95768</v>
+        <v>100539</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540174</v>
+        <v>540319</v>
       </c>
       <c r="R138" t="n">
-        <v>6448493</v>
+        <v>6448616</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14357,7 +14357,7 @@
         <v>127288068</v>
       </c>
       <c r="B139" t="n">
-        <v>79398</v>
+        <v>79400</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288079</v>
+        <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>91892</v>
+        <v>95575</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540310</v>
+        <v>540163</v>
       </c>
       <c r="R140" t="n">
-        <v>6448579</v>
+        <v>6448518</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288090</v>
+        <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>95573</v>
+        <v>91894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540163</v>
+        <v>540310</v>
       </c>
       <c r="R141" t="n">
-        <v>6448518</v>
+        <v>6448579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14648,7 +14648,7 @@
         <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>95800</v>
+        <v>95802</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288024</v>
+        <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>100537</v>
+        <v>95785</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540221</v>
+        <v>540167</v>
       </c>
       <c r="R145" t="n">
-        <v>6448466</v>
+        <v>6448513</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288032</v>
+        <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>100537</v>
+        <v>91894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540179</v>
+        <v>540251</v>
       </c>
       <c r="R146" t="n">
-        <v>6448506</v>
+        <v>6448423</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288080</v>
+        <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>91892</v>
+        <v>95785</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540251</v>
+        <v>540180</v>
       </c>
       <c r="R147" t="n">
-        <v>6448423</v>
+        <v>6448493</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,10 +15227,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288018</v>
+        <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>95783</v>
+        <v>100539</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15238,21 +15238,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540167</v>
+        <v>540221</v>
       </c>
       <c r="R148" t="n">
-        <v>6448513</v>
+        <v>6448466</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15324,10 +15324,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127288015</v>
+        <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>95783</v>
+        <v>100539</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>540180</v>
+        <v>540179</v>
       </c>
       <c r="R149" t="n">
-        <v>6448493</v>
+        <v>6448506</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288081</v>
+        <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>91892</v>
+        <v>95785</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540243</v>
+        <v>540165</v>
       </c>
       <c r="R150" t="n">
-        <v>6448421</v>
+        <v>6448511</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15521,7 +15521,7 @@
         <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288020</v>
+        <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>95783</v>
+        <v>91894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540165</v>
+        <v>540243</v>
       </c>
       <c r="R152" t="n">
-        <v>6448511</v>
+        <v>6448421</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081949</v>
+        <v>127081932</v>
       </c>
       <c r="B47" t="n">
-        <v>30135</v>
+        <v>75066</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>200985</v>
+        <v>1460</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540052</v>
+        <v>540159</v>
       </c>
       <c r="R47" t="n">
-        <v>6448313</v>
+        <v>6448374</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>75066</v>
+        <v>95781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R48" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081921</v>
+        <v>127081963</v>
       </c>
       <c r="B49" t="n">
         <v>95781</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R49" t="n">
-        <v>6448453</v>
+        <v>6448366</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081963</v>
+        <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>95781</v>
+        <v>95575</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540121</v>
+        <v>540098</v>
       </c>
       <c r="R50" t="n">
-        <v>6448366</v>
+        <v>6448341</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081957</v>
+        <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>95575</v>
+        <v>30135</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2779</v>
+        <v>200985</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540098</v>
+        <v>540052</v>
       </c>
       <c r="R51" t="n">
-        <v>6448341</v>
+        <v>6448313</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7018,32 +7018,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127081960</v>
+        <v>127081920</v>
       </c>
       <c r="B64" t="n">
-        <v>92534</v>
+        <v>95770</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2075</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540128</v>
+        <v>540200</v>
       </c>
       <c r="R64" t="n">
-        <v>6448358</v>
+        <v>6448453</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081920</v>
+        <v>127081967</v>
       </c>
       <c r="B65" t="n">
         <v>95770</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R65" t="n">
-        <v>6448453</v>
+        <v>6448358</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081967</v>
+        <v>127081952</v>
       </c>
       <c r="B66" t="n">
         <v>95770</v>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540121</v>
+        <v>540073</v>
       </c>
       <c r="R66" t="n">
-        <v>6448358</v>
+        <v>6448314</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,32 +7309,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081952</v>
+        <v>127081960</v>
       </c>
       <c r="B67" t="n">
-        <v>95770</v>
+        <v>92534</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>2075</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540073</v>
+        <v>540128</v>
       </c>
       <c r="R67" t="n">
-        <v>6448314</v>
+        <v>6448358</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081968</v>
+        <v>127081958</v>
       </c>
       <c r="B68" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540109</v>
+        <v>540100</v>
       </c>
       <c r="R68" t="n">
-        <v>6448358</v>
+        <v>6448331</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B69" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R69" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081923</v>
+        <v>127081945</v>
       </c>
       <c r="B73" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540198</v>
+        <v>540092</v>
       </c>
       <c r="R73" t="n">
-        <v>6448437</v>
+        <v>6448293</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081928</v>
+        <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95781</v>
+        <v>95770</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540172</v>
+        <v>540198</v>
       </c>
       <c r="R74" t="n">
-        <v>6448411</v>
+        <v>6448437</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081945</v>
+        <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>91894</v>
+        <v>95781</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540092</v>
+        <v>540172</v>
       </c>
       <c r="R75" t="n">
-        <v>6448293</v>
+        <v>6448411</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B76" t="n">
-        <v>95781</v>
+        <v>9401</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,34 +8193,55 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R76" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8261,6 +8282,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8279,10 +8301,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B77" t="n">
-        <v>9401</v>
+        <v>95781</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8290,55 +8312,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R77" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8379,7 +8380,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B86" t="n">
-        <v>100539</v>
+        <v>105307</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,16 +9185,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R86" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,6 +9253,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288040</v>
+        <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>105307</v>
+        <v>100539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,16 +9283,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540165</v>
+        <v>540180</v>
       </c>
       <c r="R87" t="n">
-        <v>6448488</v>
+        <v>6448493</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9350,7 +9351,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288023</v>
+        <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>100539</v>
+        <v>95770</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540237</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>6448446</v>
+        <v>6448342</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288100</v>
+        <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95770</v>
+        <v>95785</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540195</v>
+        <v>540163</v>
       </c>
       <c r="R89" t="n">
-        <v>6448342</v>
+        <v>6448517</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288019</v>
+        <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95785</v>
+        <v>95781</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540163</v>
+        <v>540187</v>
       </c>
       <c r="R90" t="n">
-        <v>6448517</v>
+        <v>6448488</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288060</v>
+        <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>95781</v>
+        <v>100539</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540187</v>
+        <v>540237</v>
       </c>
       <c r="R91" t="n">
-        <v>6448488</v>
+        <v>6448446</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288027</v>
+        <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>100539</v>
+        <v>95785</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540310</v>
+        <v>540189</v>
       </c>
       <c r="R98" t="n">
-        <v>6448579</v>
+        <v>6448461</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288013</v>
+        <v>127288065</v>
       </c>
       <c r="B99" t="n">
-        <v>95785</v>
+        <v>95781</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540189</v>
+        <v>540174</v>
       </c>
       <c r="R99" t="n">
-        <v>6448461</v>
+        <v>6448468</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>95781</v>
+        <v>91894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R100" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288074</v>
+        <v>127288057</v>
       </c>
       <c r="B101" t="n">
-        <v>91894</v>
+        <v>95781</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540039</v>
+        <v>540076</v>
       </c>
       <c r="R101" t="n">
-        <v>6448303</v>
+        <v>6448321</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288057</v>
+        <v>127288027</v>
       </c>
       <c r="B102" t="n">
-        <v>95781</v>
+        <v>100539</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540076</v>
+        <v>540310</v>
       </c>
       <c r="R102" t="n">
-        <v>6448321</v>
+        <v>6448579</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11832,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288022</v>
+        <v>127288016</v>
       </c>
       <c r="B113" t="n">
-        <v>91352</v>
+        <v>95785</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>2668</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540171</v>
+        <v>540187</v>
       </c>
       <c r="R113" t="n">
-        <v>6448436</v>
+        <v>6448494</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B114" t="n">
-        <v>95785</v>
+        <v>91352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R114" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288068</v>
+        <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>79400</v>
+        <v>95575</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R139" t="n">
-        <v>6448603</v>
+        <v>6448518</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288090</v>
+        <v>127288079</v>
       </c>
       <c r="B140" t="n">
-        <v>95575</v>
+        <v>91894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540163</v>
+        <v>540310</v>
       </c>
       <c r="R140" t="n">
-        <v>6448518</v>
+        <v>6448579</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288079</v>
+        <v>127288104</v>
       </c>
       <c r="B141" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540310</v>
+        <v>540169</v>
       </c>
       <c r="R141" t="n">
-        <v>6448579</v>
+        <v>6448515</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288104</v>
+        <v>127288036</v>
       </c>
       <c r="B142" t="n">
-        <v>95770</v>
+        <v>95802</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>2818</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540169</v>
+        <v>540336</v>
       </c>
       <c r="R142" t="n">
-        <v>6448515</v>
+        <v>6448578</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288036</v>
+        <v>127288068</v>
       </c>
       <c r="B143" t="n">
-        <v>95802</v>
+        <v>79400</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2818</v>
+        <v>6431</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540336</v>
+        <v>540274</v>
       </c>
       <c r="R143" t="n">
-        <v>6448578</v>
+        <v>6448603</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081932</v>
+        <v>127081949</v>
       </c>
       <c r="B47" t="n">
-        <v>75066</v>
+        <v>30135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1460</v>
+        <v>200985</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540159</v>
+        <v>540052</v>
       </c>
       <c r="R47" t="n">
-        <v>6448374</v>
+        <v>6448313</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081921</v>
+        <v>127081932</v>
       </c>
       <c r="B48" t="n">
-        <v>95781</v>
+        <v>75066</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2667</v>
+        <v>1460</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540200</v>
+        <v>540159</v>
       </c>
       <c r="R48" t="n">
-        <v>6448453</v>
+        <v>6448374</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081963</v>
+        <v>127081921</v>
       </c>
       <c r="B49" t="n">
         <v>95781</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R49" t="n">
-        <v>6448366</v>
+        <v>6448453</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081957</v>
+        <v>127081963</v>
       </c>
       <c r="B50" t="n">
-        <v>95575</v>
+        <v>95781</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540098</v>
+        <v>540121</v>
       </c>
       <c r="R50" t="n">
-        <v>6448341</v>
+        <v>6448366</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081949</v>
+        <v>127081957</v>
       </c>
       <c r="B51" t="n">
-        <v>30135</v>
+        <v>95575</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>200985</v>
+        <v>2779</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540052</v>
+        <v>540098</v>
       </c>
       <c r="R51" t="n">
-        <v>6448313</v>
+        <v>6448341</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081939</v>
+        <v>127081926</v>
       </c>
       <c r="B55" t="n">
-        <v>95770</v>
+        <v>91352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540134</v>
+        <v>540175</v>
       </c>
       <c r="R55" t="n">
-        <v>6448373</v>
+        <v>6448412</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127081926</v>
+        <v>127081939</v>
       </c>
       <c r="B56" t="n">
-        <v>91352</v>
+        <v>95770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540175</v>
+        <v>540134</v>
       </c>
       <c r="R56" t="n">
-        <v>6448412</v>
+        <v>6448373</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081958</v>
+        <v>127081968</v>
       </c>
       <c r="B68" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540100</v>
+        <v>540109</v>
       </c>
       <c r="R68" t="n">
-        <v>6448331</v>
+        <v>6448358</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081968</v>
+        <v>127081941</v>
       </c>
       <c r="B69" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540109</v>
+        <v>540160</v>
       </c>
       <c r="R69" t="n">
-        <v>6448358</v>
+        <v>6448357</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,7 +7600,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B70" t="n">
         <v>91894</v>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R70" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081976</v>
+        <v>127081944</v>
       </c>
       <c r="B79" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R79" t="n">
-        <v>6448349</v>
+        <v>6448303</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081925</v>
+        <v>127081976</v>
       </c>
       <c r="B80" t="n">
         <v>95770</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540175</v>
+        <v>540092</v>
       </c>
       <c r="R80" t="n">
-        <v>6448426</v>
+        <v>6448349</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081924</v>
+        <v>127081925</v>
       </c>
       <c r="B81" t="n">
         <v>95770</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540180</v>
+        <v>540175</v>
       </c>
       <c r="R81" t="n">
-        <v>6448428</v>
+        <v>6448426</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081944</v>
+        <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540096</v>
+        <v>540180</v>
       </c>
       <c r="R82" t="n">
-        <v>6448303</v>
+        <v>6448428</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288064</v>
+        <v>127288031</v>
       </c>
       <c r="B83" t="n">
-        <v>95781</v>
+        <v>100539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540177</v>
+        <v>540180</v>
       </c>
       <c r="R83" t="n">
-        <v>6448499</v>
+        <v>6448493</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288089</v>
+        <v>127288064</v>
       </c>
       <c r="B84" t="n">
-        <v>95575</v>
+        <v>95781</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540206</v>
+        <v>540177</v>
       </c>
       <c r="R84" t="n">
-        <v>6448439</v>
+        <v>6448499</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B85" t="n">
-        <v>95802</v>
+        <v>95575</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R85" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288040</v>
+        <v>127288035</v>
       </c>
       <c r="B86" t="n">
-        <v>105307</v>
+        <v>95802</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221101</v>
+        <v>2818</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540165</v>
+        <v>540222</v>
       </c>
       <c r="R86" t="n">
-        <v>6448488</v>
+        <v>6448525</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,7 +9253,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9272,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>100539</v>
+        <v>105307</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,16 +9282,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R87" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9351,6 +9350,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288100</v>
+        <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>95770</v>
+        <v>100539</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540237</v>
       </c>
       <c r="R88" t="n">
-        <v>6448342</v>
+        <v>6448446</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288019</v>
+        <v>127288100</v>
       </c>
       <c r="B89" t="n">
-        <v>95785</v>
+        <v>95770</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540163</v>
+        <v>540195</v>
       </c>
       <c r="R89" t="n">
-        <v>6448517</v>
+        <v>6448342</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288060</v>
+        <v>127288019</v>
       </c>
       <c r="B90" t="n">
-        <v>95781</v>
+        <v>95785</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540187</v>
+        <v>540163</v>
       </c>
       <c r="R90" t="n">
-        <v>6448488</v>
+        <v>6448517</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288023</v>
+        <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>100539</v>
+        <v>95781</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540237</v>
+        <v>540187</v>
       </c>
       <c r="R91" t="n">
-        <v>6448446</v>
+        <v>6448488</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288108</v>
+        <v>127288038</v>
       </c>
       <c r="B95" t="n">
-        <v>95770</v>
+        <v>106048</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2671</v>
+        <v>220785</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540163</v>
+        <v>540274</v>
       </c>
       <c r="R95" t="n">
-        <v>6448463</v>
+        <v>6448610</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,12 +10121,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10145,10 +10151,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288011</v>
+        <v>127288108</v>
       </c>
       <c r="B96" t="n">
-        <v>95785</v>
+        <v>95770</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10156,16 +10162,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10180,10 +10186,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540224</v>
+        <v>540163</v>
       </c>
       <c r="R96" t="n">
-        <v>6448404</v>
+        <v>6448463</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10242,32 +10248,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288038</v>
+        <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>106048</v>
+        <v>95785</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10277,10 +10283,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540274</v>
+        <v>540224</v>
       </c>
       <c r="R97" t="n">
-        <v>6448610</v>
+        <v>6448404</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10315,18 +10321,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288037</v>
+        <v>127288039</v>
       </c>
       <c r="B115" t="n">
-        <v>95802</v>
+        <v>105307</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>221101</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540213</v>
+        <v>540178</v>
       </c>
       <c r="R115" t="n">
-        <v>6448463</v>
+        <v>6448431</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288039</v>
+        <v>127288037</v>
       </c>
       <c r="B120" t="n">
-        <v>105307</v>
+        <v>95802</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221101</v>
+        <v>2818</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540178</v>
+        <v>540213</v>
       </c>
       <c r="R120" t="n">
-        <v>6448431</v>
+        <v>6448463</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>100539</v>
+        <v>95785</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R133" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>95785</v>
+        <v>100539</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R134" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288077</v>
+        <v>127288026</v>
       </c>
       <c r="B135" t="n">
-        <v>91894</v>
+        <v>100539</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540152</v>
+        <v>540319</v>
       </c>
       <c r="R135" t="n">
-        <v>6448350</v>
+        <v>6448616</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288107</v>
+        <v>127288077</v>
       </c>
       <c r="B136" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540174</v>
+        <v>540152</v>
       </c>
       <c r="R136" t="n">
-        <v>6448493</v>
+        <v>6448350</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288092</v>
+        <v>127288107</v>
       </c>
       <c r="B137" t="n">
-        <v>95783</v>
+        <v>95770</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2666</v>
+        <v>2671</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540169</v>
+        <v>540174</v>
       </c>
       <c r="R137" t="n">
-        <v>6448494</v>
+        <v>6448493</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288026</v>
+        <v>127288092</v>
       </c>
       <c r="B138" t="n">
-        <v>100539</v>
+        <v>95783</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222771</v>
+        <v>2666</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540319</v>
+        <v>540169</v>
       </c>
       <c r="R138" t="n">
-        <v>6448616</v>
+        <v>6448494</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288090</v>
+        <v>127288034</v>
       </c>
       <c r="B139" t="n">
-        <v>95575</v>
+        <v>100539</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448518</v>
+        <v>6448432</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288079</v>
+        <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>91894</v>
+        <v>95575</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540310</v>
+        <v>540163</v>
       </c>
       <c r="R140" t="n">
-        <v>6448579</v>
+        <v>6448518</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288104</v>
+        <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540169</v>
+        <v>540310</v>
       </c>
       <c r="R141" t="n">
-        <v>6448515</v>
+        <v>6448579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288036</v>
+        <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95802</v>
+        <v>95770</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448578</v>
+        <v>6448515</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288068</v>
+        <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>79400</v>
+        <v>95802</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6431</v>
+        <v>2818</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540274</v>
+        <v>540336</v>
       </c>
       <c r="R143" t="n">
-        <v>6448603</v>
+        <v>6448578</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>100539</v>
+        <v>79400</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081949</v>
+        <v>127081932</v>
       </c>
       <c r="B47" t="n">
-        <v>30135</v>
+        <v>75066</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>200985</v>
+        <v>1460</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540052</v>
+        <v>540159</v>
       </c>
       <c r="R47" t="n">
-        <v>6448313</v>
+        <v>6448374</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>75066</v>
+        <v>95781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R48" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081921</v>
+        <v>127081963</v>
       </c>
       <c r="B49" t="n">
         <v>95781</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R49" t="n">
-        <v>6448453</v>
+        <v>6448366</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081963</v>
+        <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>95781</v>
+        <v>95575</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540121</v>
+        <v>540098</v>
       </c>
       <c r="R50" t="n">
-        <v>6448366</v>
+        <v>6448341</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127081957</v>
+        <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>95575</v>
+        <v>30135</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2779</v>
+        <v>200985</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540098</v>
+        <v>540052</v>
       </c>
       <c r="R51" t="n">
-        <v>6448341</v>
+        <v>6448313</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6145,32 +6145,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081926</v>
+        <v>127081940</v>
       </c>
       <c r="B55" t="n">
-        <v>91352</v>
+        <v>100539</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>222771</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540175</v>
+        <v>540164</v>
       </c>
       <c r="R55" t="n">
-        <v>6448412</v>
+        <v>6448364</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6339,32 +6339,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127081940</v>
+        <v>127081926</v>
       </c>
       <c r="B57" t="n">
-        <v>100539</v>
+        <v>91352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222771</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540164</v>
+        <v>540175</v>
       </c>
       <c r="R57" t="n">
-        <v>6448364</v>
+        <v>6448412</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6824,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127081954</v>
+        <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>95781</v>
+        <v>91894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540093</v>
+        <v>540102</v>
       </c>
       <c r="R62" t="n">
-        <v>6448328</v>
+        <v>6448315</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127081942</v>
+        <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>91894</v>
+        <v>95781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540102</v>
+        <v>540093</v>
       </c>
       <c r="R63" t="n">
-        <v>6448315</v>
+        <v>6448328</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7018,32 +7018,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127081920</v>
+        <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>95770</v>
+        <v>92534</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>2075</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540200</v>
+        <v>540128</v>
       </c>
       <c r="R64" t="n">
-        <v>6448453</v>
+        <v>6448358</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127081967</v>
+        <v>127081920</v>
       </c>
       <c r="B65" t="n">
         <v>95770</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540121</v>
+        <v>540200</v>
       </c>
       <c r="R65" t="n">
-        <v>6448358</v>
+        <v>6448453</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127081952</v>
+        <v>127081967</v>
       </c>
       <c r="B66" t="n">
         <v>95770</v>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540073</v>
+        <v>540121</v>
       </c>
       <c r="R66" t="n">
-        <v>6448314</v>
+        <v>6448358</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7309,32 +7309,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127081960</v>
+        <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>92534</v>
+        <v>95770</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540128</v>
+        <v>540073</v>
       </c>
       <c r="R67" t="n">
-        <v>6448358</v>
+        <v>6448314</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B69" t="n">
         <v>91894</v>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R69" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,7 +7600,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081958</v>
+        <v>127081941</v>
       </c>
       <c r="B70" t="n">
         <v>91894</v>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540100</v>
+        <v>540160</v>
       </c>
       <c r="R70" t="n">
-        <v>6448331</v>
+        <v>6448357</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081945</v>
+        <v>127081923</v>
       </c>
       <c r="B73" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540092</v>
+        <v>540198</v>
       </c>
       <c r="R73" t="n">
-        <v>6448293</v>
+        <v>6448437</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081923</v>
+        <v>127081928</v>
       </c>
       <c r="B74" t="n">
-        <v>95770</v>
+        <v>95781</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540198</v>
+        <v>540172</v>
       </c>
       <c r="R74" t="n">
-        <v>6448437</v>
+        <v>6448411</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081928</v>
+        <v>127081945</v>
       </c>
       <c r="B75" t="n">
-        <v>95781</v>
+        <v>91894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540172</v>
+        <v>540092</v>
       </c>
       <c r="R75" t="n">
-        <v>6448411</v>
+        <v>6448293</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>9401</v>
+        <v>95781</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,55 +8193,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R76" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8282,7 +8261,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8301,10 +8279,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B77" t="n">
-        <v>95781</v>
+        <v>9401</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8312,34 +8290,55 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R77" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8380,6 +8379,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081944</v>
+        <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R79" t="n">
-        <v>6448303</v>
+        <v>6448349</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081976</v>
+        <v>127081925</v>
       </c>
       <c r="B80" t="n">
         <v>95770</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540092</v>
+        <v>540175</v>
       </c>
       <c r="R80" t="n">
-        <v>6448349</v>
+        <v>6448426</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081925</v>
+        <v>127081924</v>
       </c>
       <c r="B81" t="n">
         <v>95770</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540175</v>
+        <v>540180</v>
       </c>
       <c r="R81" t="n">
-        <v>6448426</v>
+        <v>6448428</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081924</v>
+        <v>127081944</v>
       </c>
       <c r="B82" t="n">
-        <v>95770</v>
+        <v>91894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540180</v>
+        <v>540096</v>
       </c>
       <c r="R82" t="n">
-        <v>6448428</v>
+        <v>6448303</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288031</v>
+        <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>100539</v>
+        <v>95781</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540180</v>
+        <v>540177</v>
       </c>
       <c r="R83" t="n">
-        <v>6448493</v>
+        <v>6448499</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288064</v>
+        <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95781</v>
+        <v>95575</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540177</v>
+        <v>540206</v>
       </c>
       <c r="R84" t="n">
-        <v>6448499</v>
+        <v>6448439</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288089</v>
+        <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95575</v>
+        <v>95802</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540206</v>
+        <v>540222</v>
       </c>
       <c r="R85" t="n">
-        <v>6448439</v>
+        <v>6448525</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288035</v>
+        <v>127288040</v>
       </c>
       <c r="B86" t="n">
-        <v>95802</v>
+        <v>105307</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2818</v>
+        <v>221101</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540222</v>
+        <v>540165</v>
       </c>
       <c r="R86" t="n">
-        <v>6448525</v>
+        <v>6448488</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,6 +9253,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288040</v>
+        <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>105307</v>
+        <v>100539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,16 +9283,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540165</v>
+        <v>540180</v>
       </c>
       <c r="R87" t="n">
-        <v>6448488</v>
+        <v>6448493</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9350,7 +9351,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288023</v>
+        <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>100539</v>
+        <v>95770</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540237</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>6448446</v>
+        <v>6448342</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288100</v>
+        <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95770</v>
+        <v>95785</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540195</v>
+        <v>540163</v>
       </c>
       <c r="R89" t="n">
-        <v>6448342</v>
+        <v>6448517</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288019</v>
+        <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95785</v>
+        <v>95781</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540163</v>
+        <v>540187</v>
       </c>
       <c r="R90" t="n">
-        <v>6448517</v>
+        <v>6448488</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288060</v>
+        <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>95781</v>
+        <v>100539</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540187</v>
+        <v>540237</v>
       </c>
       <c r="R91" t="n">
-        <v>6448488</v>
+        <v>6448446</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288038</v>
+        <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>106048</v>
+        <v>95770</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R95" t="n">
-        <v>6448610</v>
+        <v>6448463</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,18 +10121,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10151,10 +10145,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288108</v>
+        <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95770</v>
+        <v>95785</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10162,16 +10156,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10186,10 +10180,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540163</v>
+        <v>540224</v>
       </c>
       <c r="R96" t="n">
-        <v>6448463</v>
+        <v>6448404</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10248,32 +10242,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288011</v>
+        <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>95785</v>
+        <v>106048</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2668</v>
+        <v>220785</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10283,10 +10277,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540224</v>
+        <v>540274</v>
       </c>
       <c r="R97" t="n">
-        <v>6448404</v>
+        <v>6448610</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10321,12 +10315,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288086</v>
+        <v>127288022</v>
       </c>
       <c r="B109" t="n">
-        <v>95575</v>
+        <v>91352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R109" t="n">
-        <v>6448609</v>
+        <v>6448436</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,7 +11525,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288087</v>
+        <v>127288086</v>
       </c>
       <c r="B110" t="n">
         <v>95575</v>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540335</v>
+        <v>540333</v>
       </c>
       <c r="R110" t="n">
-        <v>6448608</v>
+        <v>6448609</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288014</v>
+        <v>127288087</v>
       </c>
       <c r="B111" t="n">
-        <v>95785</v>
+        <v>95575</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540187</v>
+        <v>540335</v>
       </c>
       <c r="R111" t="n">
-        <v>6448463</v>
+        <v>6448608</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288093</v>
+        <v>127288014</v>
       </c>
       <c r="B112" t="n">
-        <v>95770</v>
+        <v>95785</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540165</v>
+        <v>540187</v>
       </c>
       <c r="R112" t="n">
-        <v>6448484</v>
+        <v>6448463</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,24 +11798,8 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11832,10 +11816,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288016</v>
+        <v>127288093</v>
       </c>
       <c r="B113" t="n">
-        <v>95785</v>
+        <v>95770</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11843,16 +11827,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11867,10 +11851,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540187</v>
+        <v>540165</v>
       </c>
       <c r="R113" t="n">
-        <v>6448494</v>
+        <v>6448484</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11911,8 +11895,24 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288022</v>
+        <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>91352</v>
+        <v>95785</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>2668</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540171</v>
+        <v>540187</v>
       </c>
       <c r="R114" t="n">
-        <v>6448436</v>
+        <v>6448494</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288059</v>
+        <v>127288037</v>
       </c>
       <c r="B116" t="n">
-        <v>95781</v>
+        <v>95802</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540182</v>
+        <v>540213</v>
       </c>
       <c r="R116" t="n">
-        <v>6448496</v>
+        <v>6448463</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288075</v>
+        <v>127288059</v>
       </c>
       <c r="B117" t="n">
-        <v>91894</v>
+        <v>95781</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540145</v>
+        <v>540182</v>
       </c>
       <c r="R117" t="n">
-        <v>6448348</v>
+        <v>6448496</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288084</v>
+        <v>127288075</v>
       </c>
       <c r="B118" t="n">
-        <v>95575</v>
+        <v>91894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540075</v>
+        <v>540145</v>
       </c>
       <c r="R118" t="n">
-        <v>6448321</v>
+        <v>6448348</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288012</v>
+        <v>127288084</v>
       </c>
       <c r="B119" t="n">
-        <v>95785</v>
+        <v>95575</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540210</v>
+        <v>540075</v>
       </c>
       <c r="R119" t="n">
-        <v>6448417</v>
+        <v>6448321</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288037</v>
+        <v>127288012</v>
       </c>
       <c r="B120" t="n">
-        <v>95802</v>
+        <v>95785</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2818</v>
+        <v>2668</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540213</v>
+        <v>540210</v>
       </c>
       <c r="R120" t="n">
-        <v>6448463</v>
+        <v>6448417</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>95785</v>
+        <v>100539</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R133" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>100539</v>
+        <v>95785</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R134" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288026</v>
+        <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>100539</v>
+        <v>91894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540319</v>
+        <v>540152</v>
       </c>
       <c r="R135" t="n">
-        <v>6448616</v>
+        <v>6448350</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288077</v>
+        <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>91894</v>
+        <v>95770</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540152</v>
+        <v>540174</v>
       </c>
       <c r="R136" t="n">
-        <v>6448350</v>
+        <v>6448493</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288107</v>
+        <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95770</v>
+        <v>95783</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540174</v>
+        <v>540169</v>
       </c>
       <c r="R137" t="n">
-        <v>6448493</v>
+        <v>6448494</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288092</v>
+        <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>95783</v>
+        <v>100539</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2666</v>
+        <v>222771</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540169</v>
+        <v>540319</v>
       </c>
       <c r="R138" t="n">
-        <v>6448494</v>
+        <v>6448616</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B139" t="n">
-        <v>100539</v>
+        <v>79400</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R139" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>79400</v>
+        <v>100539</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92534</v>
+        <v>92540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127081948</v>
+        <v>127081927</v>
       </c>
       <c r="B39" t="n">
-        <v>95781</v>
+        <v>91358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540060</v>
+        <v>540175</v>
       </c>
       <c r="R39" t="n">
-        <v>6448311</v>
+        <v>6448411</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4690,32 +4690,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127081927</v>
+        <v>127081948</v>
       </c>
       <c r="B40" t="n">
-        <v>91352</v>
+        <v>95787</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540175</v>
+        <v>540060</v>
       </c>
       <c r="R40" t="n">
-        <v>6448411</v>
+        <v>6448311</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>95898</v>
+        <v>79400</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R43" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>79400</v>
+        <v>95904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R44" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127081964</v>
+        <v>127081916</v>
       </c>
       <c r="B45" t="n">
-        <v>95575</v>
+        <v>91900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,21 +5186,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540121</v>
+        <v>540227</v>
       </c>
       <c r="R45" t="n">
-        <v>6448366</v>
+        <v>6448359</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5272,10 +5272,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127081916</v>
+        <v>127081964</v>
       </c>
       <c r="B46" t="n">
-        <v>91894</v>
+        <v>95581</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5283,21 +5283,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540227</v>
+        <v>540121</v>
       </c>
       <c r="R46" t="n">
-        <v>6448359</v>
+        <v>6448366</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5469,7 +5469,7 @@
         <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>127081963</v>
       </c>
       <c r="B49" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081940</v>
+        <v>127081939</v>
       </c>
       <c r="B55" t="n">
-        <v>100539</v>
+        <v>95776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540164</v>
+        <v>540134</v>
       </c>
       <c r="R55" t="n">
-        <v>6448364</v>
+        <v>6448373</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127081939</v>
+        <v>127081926</v>
       </c>
       <c r="B56" t="n">
-        <v>95770</v>
+        <v>91358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540134</v>
+        <v>540175</v>
       </c>
       <c r="R56" t="n">
-        <v>6448373</v>
+        <v>6448412</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6339,32 +6339,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127081926</v>
+        <v>127081940</v>
       </c>
       <c r="B57" t="n">
-        <v>91352</v>
+        <v>100545</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>222771</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540175</v>
+        <v>540164</v>
       </c>
       <c r="R57" t="n">
-        <v>6448412</v>
+        <v>6448364</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127081942</v>
+        <v>127081954</v>
       </c>
       <c r="B62" t="n">
-        <v>91894</v>
+        <v>95787</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540102</v>
+        <v>540093</v>
       </c>
       <c r="R62" t="n">
-        <v>6448315</v>
+        <v>6448328</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127081954</v>
+        <v>127081942</v>
       </c>
       <c r="B63" t="n">
-        <v>95781</v>
+        <v>91900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540093</v>
+        <v>540102</v>
       </c>
       <c r="R63" t="n">
-        <v>6448328</v>
+        <v>6448315</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7021,7 +7021,7 @@
         <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>92534</v>
+        <v>92540</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>127081968</v>
       </c>
       <c r="B68" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081958</v>
+        <v>127081941</v>
       </c>
       <c r="B69" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540100</v>
+        <v>540160</v>
       </c>
       <c r="R69" t="n">
-        <v>6448331</v>
+        <v>6448357</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127081941</v>
+        <v>127081958</v>
       </c>
       <c r="B70" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540160</v>
+        <v>540100</v>
       </c>
       <c r="R70" t="n">
-        <v>6448357</v>
+        <v>6448331</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081971</v>
+        <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>95770</v>
+        <v>91900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R71" t="n">
-        <v>6448345</v>
+        <v>6448293</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081974</v>
+        <v>127081971</v>
       </c>
       <c r="B72" t="n">
-        <v>95575</v>
+        <v>95776</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540097</v>
+        <v>540096</v>
       </c>
       <c r="R72" t="n">
-        <v>6448346</v>
+        <v>6448345</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081923</v>
+        <v>127081974</v>
       </c>
       <c r="B73" t="n">
-        <v>95770</v>
+        <v>95581</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540198</v>
+        <v>540097</v>
       </c>
       <c r="R73" t="n">
-        <v>6448437</v>
+        <v>6448346</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081928</v>
+        <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95781</v>
+        <v>95776</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540172</v>
+        <v>540198</v>
       </c>
       <c r="R74" t="n">
-        <v>6448411</v>
+        <v>6448437</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081945</v>
+        <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>91894</v>
+        <v>95787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540092</v>
+        <v>540172</v>
       </c>
       <c r="R75" t="n">
-        <v>6448293</v>
+        <v>6448411</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8185,7 +8185,7 @@
         <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92534</v>
+        <v>92540</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081976</v>
+        <v>127081944</v>
       </c>
       <c r="B79" t="n">
-        <v>95770</v>
+        <v>91900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R79" t="n">
-        <v>6448349</v>
+        <v>6448303</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081925</v>
+        <v>127081976</v>
       </c>
       <c r="B80" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540175</v>
+        <v>540092</v>
       </c>
       <c r="R80" t="n">
-        <v>6448426</v>
+        <v>6448349</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081924</v>
+        <v>127081925</v>
       </c>
       <c r="B81" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540180</v>
+        <v>540175</v>
       </c>
       <c r="R81" t="n">
-        <v>6448428</v>
+        <v>6448426</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8786,10 +8786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127081944</v>
+        <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>91894</v>
+        <v>95776</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8797,21 +8797,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540096</v>
+        <v>540180</v>
       </c>
       <c r="R82" t="n">
-        <v>6448303</v>
+        <v>6448428</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288064</v>
+        <v>127288035</v>
       </c>
       <c r="B83" t="n">
-        <v>95781</v>
+        <v>95808</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R83" t="n">
-        <v>6448499</v>
+        <v>6448525</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288035</v>
+        <v>127288064</v>
       </c>
       <c r="B85" t="n">
-        <v>95802</v>
+        <v>95787</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540222</v>
+        <v>540177</v>
       </c>
       <c r="R85" t="n">
-        <v>6448525</v>
+        <v>6448499</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9177,7 +9177,7 @@
         <v>127288040</v>
       </c>
       <c r="B86" t="n">
-        <v>105307</v>
+        <v>105313</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288100</v>
+        <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>95770</v>
+        <v>100545</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540237</v>
       </c>
       <c r="R88" t="n">
-        <v>6448342</v>
+        <v>6448446</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9469,7 +9469,7 @@
         <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95785</v>
+        <v>95791</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288060</v>
+        <v>127288100</v>
       </c>
       <c r="B90" t="n">
-        <v>95781</v>
+        <v>95776</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540187</v>
+        <v>540195</v>
       </c>
       <c r="R90" t="n">
-        <v>6448488</v>
+        <v>6448342</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288023</v>
+        <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>100539</v>
+        <v>95787</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540237</v>
+        <v>540187</v>
       </c>
       <c r="R91" t="n">
-        <v>6448446</v>
+        <v>6448488</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288108</v>
+        <v>127288038</v>
       </c>
       <c r="B95" t="n">
-        <v>95770</v>
+        <v>106054</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2671</v>
+        <v>220785</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540163</v>
+        <v>540274</v>
       </c>
       <c r="R95" t="n">
-        <v>6448463</v>
+        <v>6448610</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,12 +10121,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10145,10 +10151,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288011</v>
+        <v>127288108</v>
       </c>
       <c r="B96" t="n">
-        <v>95785</v>
+        <v>95776</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10156,16 +10162,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10180,10 +10186,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540224</v>
+        <v>540163</v>
       </c>
       <c r="R96" t="n">
-        <v>6448404</v>
+        <v>6448463</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10242,32 +10248,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288038</v>
+        <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>106048</v>
+        <v>95791</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10277,10 +10283,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540274</v>
+        <v>540224</v>
       </c>
       <c r="R97" t="n">
-        <v>6448610</v>
+        <v>6448404</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10315,18 +10321,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288013</v>
+        <v>127288027</v>
       </c>
       <c r="B98" t="n">
-        <v>95785</v>
+        <v>100545</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540189</v>
+        <v>540310</v>
       </c>
       <c r="R98" t="n">
-        <v>6448461</v>
+        <v>6448579</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288065</v>
+        <v>127288013</v>
       </c>
       <c r="B99" t="n">
-        <v>95781</v>
+        <v>95791</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540174</v>
+        <v>540189</v>
       </c>
       <c r="R99" t="n">
-        <v>6448468</v>
+        <v>6448461</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10542,7 +10542,7 @@
         <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288057</v>
+        <v>127288065</v>
       </c>
       <c r="B101" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540076</v>
+        <v>540174</v>
       </c>
       <c r="R101" t="n">
-        <v>6448321</v>
+        <v>6448468</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288027</v>
+        <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>100539</v>
+        <v>95787</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540310</v>
+        <v>540076</v>
       </c>
       <c r="R102" t="n">
-        <v>6448579</v>
+        <v>6448321</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288101</v>
+        <v>127288094</v>
       </c>
       <c r="B103" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R103" t="n">
-        <v>6448609</v>
+        <v>6448441</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10909,8 +10909,24 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -10927,10 +10943,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B104" t="n">
-        <v>95770</v>
+        <v>95787</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10938,21 +10954,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10962,10 +10978,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R104" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11040,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B105" t="n">
-        <v>95781</v>
+        <v>95776</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11051,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11075,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R105" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11137,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288094</v>
+        <v>127288101</v>
       </c>
       <c r="B106" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11156,10 +11172,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R106" t="n">
-        <v>6448441</v>
+        <v>6448609</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,24 +11216,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11237,7 +11237,7 @@
         <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11428,32 +11428,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127288022</v>
+        <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>91352</v>
+        <v>95581</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R109" t="n">
-        <v>6448436</v>
+        <v>6448609</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11525,10 +11525,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288086</v>
+        <v>127288014</v>
       </c>
       <c r="B110" t="n">
-        <v>95575</v>
+        <v>95791</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11536,21 +11536,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540333</v>
+        <v>540187</v>
       </c>
       <c r="R110" t="n">
-        <v>6448609</v>
+        <v>6448463</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288087</v>
+        <v>127288093</v>
       </c>
       <c r="B111" t="n">
-        <v>95575</v>
+        <v>95776</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540335</v>
+        <v>540165</v>
       </c>
       <c r="R111" t="n">
-        <v>6448608</v>
+        <v>6448484</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11701,8 +11701,24 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -11719,10 +11735,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288014</v>
+        <v>127288016</v>
       </c>
       <c r="B112" t="n">
-        <v>95785</v>
+        <v>95791</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11757,7 +11773,7 @@
         <v>540187</v>
       </c>
       <c r="R112" t="n">
-        <v>6448463</v>
+        <v>6448494</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11816,10 +11832,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288093</v>
+        <v>127288087</v>
       </c>
       <c r="B113" t="n">
-        <v>95770</v>
+        <v>95581</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11827,21 +11843,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11851,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540165</v>
+        <v>540335</v>
       </c>
       <c r="R113" t="n">
-        <v>6448484</v>
+        <v>6448608</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11895,24 +11911,8 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B114" t="n">
-        <v>95785</v>
+        <v>91358</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R114" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288039</v>
+        <v>127288059</v>
       </c>
       <c r="B115" t="n">
-        <v>105307</v>
+        <v>95787</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221101</v>
+        <v>2667</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540178</v>
+        <v>540182</v>
       </c>
       <c r="R115" t="n">
-        <v>6448431</v>
+        <v>6448496</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288037</v>
+        <v>127288084</v>
       </c>
       <c r="B116" t="n">
-        <v>95802</v>
+        <v>95581</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540213</v>
+        <v>540075</v>
       </c>
       <c r="R116" t="n">
-        <v>6448463</v>
+        <v>6448321</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288059</v>
+        <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>95781</v>
+        <v>91900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540182</v>
+        <v>540145</v>
       </c>
       <c r="R117" t="n">
-        <v>6448496</v>
+        <v>6448348</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288075</v>
+        <v>127288012</v>
       </c>
       <c r="B118" t="n">
-        <v>91894</v>
+        <v>95791</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540145</v>
+        <v>540210</v>
       </c>
       <c r="R118" t="n">
-        <v>6448348</v>
+        <v>6448417</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288084</v>
+        <v>127288037</v>
       </c>
       <c r="B119" t="n">
-        <v>95575</v>
+        <v>95808</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540075</v>
+        <v>540213</v>
       </c>
       <c r="R119" t="n">
-        <v>6448321</v>
+        <v>6448463</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288012</v>
+        <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>95785</v>
+        <v>105313</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2668</v>
+        <v>221101</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540210</v>
+        <v>540178</v>
       </c>
       <c r="R120" t="n">
-        <v>6448417</v>
+        <v>6448431</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127288076</v>
+        <v>127288091</v>
       </c>
       <c r="B121" t="n">
-        <v>91894</v>
+        <v>95581</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12619,21 +12619,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540155</v>
+        <v>540169</v>
       </c>
       <c r="R121" t="n">
-        <v>6448348</v>
+        <v>6448494</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288088</v>
+        <v>127288076</v>
       </c>
       <c r="B122" t="n">
-        <v>95575</v>
+        <v>91900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12716,21 +12716,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540338</v>
+        <v>540155</v>
       </c>
       <c r="R122" t="n">
-        <v>6448617</v>
+        <v>6448348</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288091</v>
+        <v>127288062</v>
       </c>
       <c r="B123" t="n">
-        <v>95575</v>
+        <v>95787</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12813,21 +12813,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540169</v>
+        <v>540177</v>
       </c>
       <c r="R123" t="n">
-        <v>6448494</v>
+        <v>6448495</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12899,10 +12899,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127288062</v>
+        <v>127288088</v>
       </c>
       <c r="B124" t="n">
-        <v>95781</v>
+        <v>95581</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12910,21 +12910,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12934,10 +12934,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540177</v>
+        <v>540338</v>
       </c>
       <c r="R124" t="n">
-        <v>6448495</v>
+        <v>6448617</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -12999,7 +12999,7 @@
         <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>91292</v>
+        <v>91298</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288078</v>
+        <v>127288017</v>
       </c>
       <c r="B128" t="n">
-        <v>91894</v>
+        <v>95791</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540193</v>
+        <v>540172</v>
       </c>
       <c r="R128" t="n">
-        <v>6448342</v>
+        <v>6448507</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288017</v>
+        <v>127288085</v>
       </c>
       <c r="B129" t="n">
-        <v>95785</v>
+        <v>95581</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540172</v>
+        <v>540251</v>
       </c>
       <c r="R129" t="n">
-        <v>6448507</v>
+        <v>6448599</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288085</v>
+        <v>127288058</v>
       </c>
       <c r="B131" t="n">
-        <v>95575</v>
+        <v>95787</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540251</v>
+        <v>540182</v>
       </c>
       <c r="R131" t="n">
-        <v>6448599</v>
+        <v>6448466</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127288058</v>
+        <v>127288078</v>
       </c>
       <c r="B132" t="n">
-        <v>95781</v>
+        <v>91900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540182</v>
+        <v>540193</v>
       </c>
       <c r="R132" t="n">
-        <v>6448466</v>
+        <v>6448342</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>100539</v>
+        <v>95791</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R133" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>95785</v>
+        <v>100545</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R134" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288077</v>
+        <v>127288092</v>
       </c>
       <c r="B135" t="n">
-        <v>91894</v>
+        <v>95789</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3884</v>
+        <v>2666</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540152</v>
+        <v>540169</v>
       </c>
       <c r="R135" t="n">
-        <v>6448350</v>
+        <v>6448494</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288107</v>
+        <v>127288077</v>
       </c>
       <c r="B136" t="n">
-        <v>95770</v>
+        <v>91900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540174</v>
+        <v>540152</v>
       </c>
       <c r="R136" t="n">
-        <v>6448493</v>
+        <v>6448350</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288092</v>
+        <v>127288107</v>
       </c>
       <c r="B137" t="n">
-        <v>95783</v>
+        <v>95776</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2666</v>
+        <v>2671</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540169</v>
+        <v>540174</v>
       </c>
       <c r="R137" t="n">
-        <v>6448494</v>
+        <v>6448493</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14260,7 +14260,7 @@
         <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288068</v>
+        <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>79400</v>
+        <v>95581</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R139" t="n">
-        <v>6448603</v>
+        <v>6448518</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288090</v>
+        <v>127288104</v>
       </c>
       <c r="B140" t="n">
-        <v>95575</v>
+        <v>95776</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R140" t="n">
-        <v>6448518</v>
+        <v>6448515</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288104</v>
+        <v>127288036</v>
       </c>
       <c r="B142" t="n">
-        <v>95770</v>
+        <v>95808</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>2818</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540169</v>
+        <v>540336</v>
       </c>
       <c r="R142" t="n">
-        <v>6448515</v>
+        <v>6448578</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288036</v>
+        <v>127288068</v>
       </c>
       <c r="B143" t="n">
-        <v>95802</v>
+        <v>79400</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2818</v>
+        <v>6431</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540336</v>
+        <v>540274</v>
       </c>
       <c r="R143" t="n">
-        <v>6448578</v>
+        <v>6448603</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14842,7 +14842,7 @@
         <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>95785</v>
+        <v>95791</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>95785</v>
+        <v>95791</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288020</v>
+        <v>127288102</v>
       </c>
       <c r="B150" t="n">
-        <v>95785</v>
+        <v>95776</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,16 +15432,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540165</v>
+        <v>540208</v>
       </c>
       <c r="R150" t="n">
-        <v>6448511</v>
+        <v>6448415</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288102</v>
+        <v>127288081</v>
       </c>
       <c r="B151" t="n">
-        <v>95770</v>
+        <v>91900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,21 +15529,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540208</v>
+        <v>540243</v>
       </c>
       <c r="R151" t="n">
-        <v>6448415</v>
+        <v>6448421</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288081</v>
+        <v>127288020</v>
       </c>
       <c r="B152" t="n">
-        <v>91894</v>
+        <v>95791</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540243</v>
+        <v>540165</v>
       </c>
       <c r="R152" t="n">
-        <v>6448421</v>
+        <v>6448511</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127081927</v>
       </c>
       <c r="B39" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>127081948</v>
       </c>
       <c r="B40" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B43" t="n">
-        <v>79400</v>
+        <v>95907</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R43" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B44" t="n">
-        <v>95904</v>
+        <v>79403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R44" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>127081916</v>
       </c>
       <c r="B45" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081964</v>
       </c>
       <c r="B46" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>127081932</v>
       </c>
       <c r="B47" t="n">
-        <v>75066</v>
+        <v>75069</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>127081921</v>
       </c>
       <c r="B48" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>127081963</v>
       </c>
       <c r="B49" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>127081957</v>
       </c>
       <c r="B50" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>30135</v>
+        <v>30136</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127081939</v>
+        <v>127081940</v>
       </c>
       <c r="B55" t="n">
-        <v>95776</v>
+        <v>100548</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540134</v>
+        <v>540164</v>
       </c>
       <c r="R55" t="n">
-        <v>6448373</v>
+        <v>6448364</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6242,32 +6242,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127081926</v>
+        <v>127081939</v>
       </c>
       <c r="B56" t="n">
-        <v>91358</v>
+        <v>95779</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540175</v>
+        <v>540134</v>
       </c>
       <c r="R56" t="n">
-        <v>6448412</v>
+        <v>6448373</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6339,32 +6339,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127081940</v>
+        <v>127081926</v>
       </c>
       <c r="B57" t="n">
-        <v>100545</v>
+        <v>91361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222771</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540164</v>
+        <v>540175</v>
       </c>
       <c r="R57" t="n">
-        <v>6448364</v>
+        <v>6448412</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127081954</v>
+        <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>95787</v>
+        <v>91903</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540093</v>
+        <v>540102</v>
       </c>
       <c r="R62" t="n">
-        <v>6448328</v>
+        <v>6448315</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127081942</v>
+        <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>91900</v>
+        <v>95790</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540102</v>
+        <v>540093</v>
       </c>
       <c r="R63" t="n">
-        <v>6448315</v>
+        <v>6448328</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7021,7 +7021,7 @@
         <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127081968</v>
+        <v>127081941</v>
       </c>
       <c r="B68" t="n">
-        <v>95776</v>
+        <v>91903</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540109</v>
+        <v>540160</v>
       </c>
       <c r="R68" t="n">
-        <v>6448358</v>
+        <v>6448357</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127081941</v>
+        <v>127081968</v>
       </c>
       <c r="B69" t="n">
-        <v>91900</v>
+        <v>95779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540160</v>
+        <v>540109</v>
       </c>
       <c r="R69" t="n">
-        <v>6448357</v>
+        <v>6448358</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7603,7 +7603,7 @@
         <v>127081958</v>
       </c>
       <c r="B70" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081945</v>
+        <v>127081971</v>
       </c>
       <c r="B71" t="n">
-        <v>91900</v>
+        <v>95779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540092</v>
+        <v>540096</v>
       </c>
       <c r="R71" t="n">
-        <v>6448293</v>
+        <v>6448345</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081971</v>
+        <v>127081945</v>
       </c>
       <c r="B72" t="n">
-        <v>95776</v>
+        <v>91903</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R72" t="n">
-        <v>6448345</v>
+        <v>6448293</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7894,7 +7894,7 @@
         <v>127081974</v>
       </c>
       <c r="B73" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>127081923</v>
       </c>
       <c r="B74" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>127081928</v>
       </c>
       <c r="B75" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B76" t="n">
-        <v>95787</v>
+        <v>9401</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,34 +8193,55 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R76" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8261,6 +8282,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8279,10 +8301,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B77" t="n">
-        <v>9401</v>
+        <v>95790</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8290,55 +8312,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R77" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8379,7 +8380,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127081944</v>
+        <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>91900</v>
+        <v>95779</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R79" t="n">
-        <v>6448303</v>
+        <v>6448349</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127081976</v>
+        <v>127081925</v>
       </c>
       <c r="B80" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540092</v>
+        <v>540175</v>
       </c>
       <c r="R80" t="n">
-        <v>6448349</v>
+        <v>6448426</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127081925</v>
+        <v>127081944</v>
       </c>
       <c r="B81" t="n">
-        <v>95776</v>
+        <v>91903</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540175</v>
+        <v>540096</v>
       </c>
       <c r="R81" t="n">
-        <v>6448426</v>
+        <v>6448303</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8789,7 +8789,7 @@
         <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>127288035</v>
       </c>
       <c r="B83" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288089</v>
+        <v>127288040</v>
       </c>
       <c r="B84" t="n">
-        <v>95581</v>
+        <v>105316</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>221101</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540206</v>
+        <v>540165</v>
       </c>
       <c r="R84" t="n">
-        <v>6448439</v>
+        <v>6448488</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9059,6 +9059,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9080,7 +9081,7 @@
         <v>127288064</v>
       </c>
       <c r="B85" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9174,10 +9175,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288040</v>
+        <v>127288089</v>
       </c>
       <c r="B86" t="n">
-        <v>105313</v>
+        <v>95584</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9186,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221101</v>
+        <v>2779</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9210,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540165</v>
+        <v>540206</v>
       </c>
       <c r="R86" t="n">
-        <v>6448488</v>
+        <v>6448439</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,7 +9254,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288023</v>
+        <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>100545</v>
+        <v>95779</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540237</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>6448446</v>
+        <v>6448342</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9469,7 +9469,7 @@
         <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95791</v>
+        <v>95794</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288100</v>
+        <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95776</v>
+        <v>95790</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540195</v>
+        <v>540187</v>
       </c>
       <c r="R90" t="n">
-        <v>6448342</v>
+        <v>6448488</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288060</v>
+        <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>95787</v>
+        <v>100548</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540187</v>
+        <v>540237</v>
       </c>
       <c r="R91" t="n">
-        <v>6448488</v>
+        <v>6448446</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>127288038</v>
       </c>
       <c r="B95" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>127288108</v>
       </c>
       <c r="B96" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>95791</v>
+        <v>95794</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>127288027</v>
       </c>
       <c r="B98" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>127288013</v>
       </c>
       <c r="B99" t="n">
-        <v>95791</v>
+        <v>95794</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288074</v>
+        <v>127288065</v>
       </c>
       <c r="B100" t="n">
-        <v>91900</v>
+        <v>95790</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540039</v>
+        <v>540174</v>
       </c>
       <c r="R100" t="n">
-        <v>6448303</v>
+        <v>6448468</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B101" t="n">
-        <v>95787</v>
+        <v>91903</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R101" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10736,7 +10736,7 @@
         <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288094</v>
+        <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R103" t="n">
-        <v>6448441</v>
+        <v>6448609</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10909,24 +10909,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -10943,10 +10927,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95787</v>
+        <v>95779</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10954,21 +10938,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10978,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R104" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11040,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95776</v>
+        <v>95790</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11051,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11075,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R105" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11137,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288101</v>
+        <v>127288094</v>
       </c>
       <c r="B106" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11172,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R106" t="n">
-        <v>6448609</v>
+        <v>6448441</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11216,8 +11200,24 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11237,7 +11237,7 @@
         <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11525,10 +11525,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127288014</v>
+        <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95791</v>
+        <v>95584</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11536,21 +11536,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540187</v>
+        <v>540335</v>
       </c>
       <c r="R110" t="n">
-        <v>6448463</v>
+        <v>6448608</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11622,10 +11622,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288093</v>
+        <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95776</v>
+        <v>95794</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11633,16 +11633,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540165</v>
+        <v>540187</v>
       </c>
       <c r="R111" t="n">
-        <v>6448484</v>
+        <v>6448463</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11701,24 +11701,8 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -11735,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288016</v>
+        <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95791</v>
+        <v>95779</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11746,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11770,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540187</v>
+        <v>540165</v>
       </c>
       <c r="R112" t="n">
-        <v>6448494</v>
+        <v>6448484</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11814,8 +11798,24 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11832,10 +11832,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288087</v>
+        <v>127288016</v>
       </c>
       <c r="B113" t="n">
-        <v>95581</v>
+        <v>95794</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11843,21 +11843,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540335</v>
+        <v>540187</v>
       </c>
       <c r="R113" t="n">
-        <v>6448608</v>
+        <v>6448494</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11932,7 +11932,7 @@
         <v>127288022</v>
       </c>
       <c r="B114" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288059</v>
+        <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>95787</v>
+        <v>95811</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540182</v>
+        <v>540213</v>
       </c>
       <c r="R115" t="n">
-        <v>6448496</v>
+        <v>6448463</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288084</v>
+        <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95581</v>
+        <v>95790</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540075</v>
+        <v>540182</v>
       </c>
       <c r="R116" t="n">
-        <v>6448321</v>
+        <v>6448496</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12223,7 +12223,7 @@
         <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288012</v>
+        <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>95791</v>
+        <v>95584</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540210</v>
+        <v>540075</v>
       </c>
       <c r="R118" t="n">
-        <v>6448417</v>
+        <v>6448321</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288037</v>
+        <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>95808</v>
+        <v>95794</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2818</v>
+        <v>2668</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540213</v>
+        <v>540210</v>
       </c>
       <c r="R119" t="n">
-        <v>6448463</v>
+        <v>6448417</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12514,7 +12514,7 @@
         <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>105313</v>
+        <v>105316</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127288091</v>
+        <v>127288088</v>
       </c>
       <c r="B121" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540169</v>
+        <v>540338</v>
       </c>
       <c r="R121" t="n">
-        <v>6448494</v>
+        <v>6448617</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288076</v>
+        <v>127288091</v>
       </c>
       <c r="B122" t="n">
-        <v>91900</v>
+        <v>95584</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12716,21 +12716,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540155</v>
+        <v>540169</v>
       </c>
       <c r="R122" t="n">
-        <v>6448348</v>
+        <v>6448494</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288062</v>
+        <v>127288076</v>
       </c>
       <c r="B123" t="n">
-        <v>95787</v>
+        <v>91903</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12813,21 +12813,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540177</v>
+        <v>540155</v>
       </c>
       <c r="R123" t="n">
-        <v>6448495</v>
+        <v>6448348</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12899,10 +12899,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127288088</v>
+        <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95581</v>
+        <v>95790</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12910,21 +12910,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12934,10 +12934,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540338</v>
+        <v>540177</v>
       </c>
       <c r="R124" t="n">
-        <v>6448617</v>
+        <v>6448495</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B125" t="n">
-        <v>91298</v>
+        <v>79403</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R125" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B126" t="n">
-        <v>79400</v>
+        <v>91301</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R126" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288017</v>
+        <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>95791</v>
+        <v>91903</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540172</v>
+        <v>540193</v>
       </c>
       <c r="R128" t="n">
-        <v>6448507</v>
+        <v>6448342</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288085</v>
+        <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95581</v>
+        <v>95794</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540251</v>
+        <v>540172</v>
       </c>
       <c r="R129" t="n">
-        <v>6448599</v>
+        <v>6448507</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288058</v>
+        <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95787</v>
+        <v>95584</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540182</v>
+        <v>540251</v>
       </c>
       <c r="R131" t="n">
-        <v>6448466</v>
+        <v>6448599</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13675,10 +13675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127288078</v>
+        <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>91900</v>
+        <v>95790</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540193</v>
+        <v>540182</v>
       </c>
       <c r="R132" t="n">
-        <v>6448342</v>
+        <v>6448466</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -13775,7 +13775,7 @@
         <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>95791</v>
+        <v>95794</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288092</v>
+        <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>95789</v>
+        <v>91903</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2666</v>
+        <v>3884</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540169</v>
+        <v>540152</v>
       </c>
       <c r="R135" t="n">
-        <v>6448494</v>
+        <v>6448350</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288077</v>
+        <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>91900</v>
+        <v>95779</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540152</v>
+        <v>540174</v>
       </c>
       <c r="R136" t="n">
-        <v>6448350</v>
+        <v>6448493</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288107</v>
+        <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95776</v>
+        <v>95792</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540174</v>
+        <v>540169</v>
       </c>
       <c r="R137" t="n">
-        <v>6448493</v>
+        <v>6448494</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14260,7 +14260,7 @@
         <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288090</v>
+        <v>127288034</v>
       </c>
       <c r="B139" t="n">
-        <v>95581</v>
+        <v>100548</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448518</v>
+        <v>6448432</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288104</v>
+        <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>95776</v>
+        <v>95584</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R140" t="n">
-        <v>6448515</v>
+        <v>6448518</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288036</v>
+        <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95808</v>
+        <v>95779</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448578</v>
+        <v>6448515</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288068</v>
+        <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>79400</v>
+        <v>95811</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6431</v>
+        <v>2818</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540274</v>
+        <v>540336</v>
       </c>
       <c r="R143" t="n">
-        <v>6448603</v>
+        <v>6448578</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>100545</v>
+        <v>79403</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14939,7 +14939,7 @@
         <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>95791</v>
+        <v>95794</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>95791</v>
+        <v>95794</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288102</v>
+        <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>95776</v>
+        <v>95794</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,16 +15432,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540208</v>
+        <v>540165</v>
       </c>
       <c r="R150" t="n">
-        <v>6448415</v>
+        <v>6448511</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288081</v>
+        <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>91900</v>
+        <v>95779</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,21 +15529,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540243</v>
+        <v>540208</v>
       </c>
       <c r="R151" t="n">
-        <v>6448421</v>
+        <v>6448415</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288020</v>
+        <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>95791</v>
+        <v>91903</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540165</v>
+        <v>540243</v>
       </c>
       <c r="R152" t="n">
-        <v>6448511</v>
+        <v>6448421</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288035</v>
+        <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>95811</v>
+        <v>95798</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540222</v>
+        <v>540177</v>
       </c>
       <c r="R83" t="n">
-        <v>6448525</v>
+        <v>6448499</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288040</v>
+        <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>105316</v>
+        <v>95592</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221101</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540165</v>
+        <v>540206</v>
       </c>
       <c r="R84" t="n">
-        <v>6448488</v>
+        <v>6448439</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9059,7 +9059,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9078,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288064</v>
+        <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95790</v>
+        <v>95819</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9089,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9113,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R85" t="n">
-        <v>6448499</v>
+        <v>6448525</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9175,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288089</v>
+        <v>127288040</v>
       </c>
       <c r="B86" t="n">
-        <v>95584</v>
+        <v>105324</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9186,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2779</v>
+        <v>221101</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9210,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540206</v>
+        <v>540165</v>
       </c>
       <c r="R86" t="n">
-        <v>6448439</v>
+        <v>6448488</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9254,6 +9253,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>127288031</v>
       </c>
       <c r="B87" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>127288038</v>
       </c>
       <c r="B95" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>127288108</v>
       </c>
       <c r="B96" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288027</v>
+        <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>100548</v>
+        <v>95802</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540310</v>
+        <v>540189</v>
       </c>
       <c r="R98" t="n">
-        <v>6448579</v>
+        <v>6448461</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288013</v>
+        <v>127288065</v>
       </c>
       <c r="B99" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540189</v>
+        <v>540174</v>
       </c>
       <c r="R99" t="n">
-        <v>6448461</v>
+        <v>6448468</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>95790</v>
+        <v>91911</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R100" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288074</v>
+        <v>127288057</v>
       </c>
       <c r="B101" t="n">
-        <v>91903</v>
+        <v>95798</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540039</v>
+        <v>540076</v>
       </c>
       <c r="R101" t="n">
-        <v>6448303</v>
+        <v>6448321</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288057</v>
+        <v>127288027</v>
       </c>
       <c r="B102" t="n">
-        <v>95790</v>
+        <v>100556</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540076</v>
+        <v>540310</v>
       </c>
       <c r="R102" t="n">
-        <v>6448321</v>
+        <v>6448579</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288101</v>
+        <v>127288028</v>
       </c>
       <c r="B103" t="n">
-        <v>95779</v>
+        <v>100556</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540333</v>
+        <v>540335</v>
       </c>
       <c r="R103" t="n">
-        <v>6448609</v>
+        <v>6448550</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10927,10 +10927,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288105</v>
+        <v>127288101</v>
       </c>
       <c r="B104" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R104" t="n">
-        <v>6448504</v>
+        <v>6448609</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B105" t="n">
-        <v>95790</v>
+        <v>95787</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R105" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288094</v>
+        <v>127288061</v>
       </c>
       <c r="B106" t="n">
-        <v>95779</v>
+        <v>95798</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R106" t="n">
-        <v>6448441</v>
+        <v>6448493</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,24 +11200,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11234,10 +11218,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288028</v>
+        <v>127288094</v>
       </c>
       <c r="B107" t="n">
-        <v>100548</v>
+        <v>95787</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11245,21 +11229,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11269,10 +11253,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540335</v>
+        <v>540171</v>
       </c>
       <c r="R107" t="n">
-        <v>6448550</v>
+        <v>6448441</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11313,8 +11297,24 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11832,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288016</v>
+        <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>95794</v>
+        <v>91369</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R113" t="n">
-        <v>6448494</v>
+        <v>6448436</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11929,32 +11929,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127288022</v>
+        <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>91361</v>
+        <v>95802</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>2668</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540171</v>
+        <v>540187</v>
       </c>
       <c r="R114" t="n">
-        <v>6448436</v>
+        <v>6448494</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12029,7 +12029,7 @@
         <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>105316</v>
+        <v>105324</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127288088</v>
+        <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>95584</v>
+        <v>91911</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12619,21 +12619,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540338</v>
+        <v>540155</v>
       </c>
       <c r="R121" t="n">
-        <v>6448617</v>
+        <v>6448348</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288091</v>
+        <v>127288088</v>
       </c>
       <c r="B122" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540169</v>
+        <v>540338</v>
       </c>
       <c r="R122" t="n">
-        <v>6448494</v>
+        <v>6448617</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288076</v>
+        <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>91903</v>
+        <v>95592</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12813,21 +12813,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540155</v>
+        <v>540169</v>
       </c>
       <c r="R123" t="n">
-        <v>6448348</v>
+        <v>6448494</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>127288069</v>
       </c>
       <c r="B125" t="n">
-        <v>79403</v>
+        <v>79409</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>127288110</v>
       </c>
       <c r="B126" t="n">
-        <v>91301</v>
+        <v>91309</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95792</v>
+        <v>95800</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288034</v>
+        <v>127288068</v>
       </c>
       <c r="B139" t="n">
-        <v>100548</v>
+        <v>79409</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222771</v>
+        <v>6431</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R139" t="n">
-        <v>6448432</v>
+        <v>6448603</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14454,7 +14454,7 @@
         <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288068</v>
+        <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>79403</v>
+        <v>100556</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>222771</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448603</v>
+        <v>6448432</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14939,7 +14939,7 @@
         <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>95794</v>
+        <v>95802</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288064</v>
+        <v>127288089</v>
       </c>
       <c r="B83" t="n">
-        <v>95798</v>
+        <v>95593</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540177</v>
+        <v>540206</v>
       </c>
       <c r="R83" t="n">
-        <v>6448499</v>
+        <v>6448439</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288089</v>
+        <v>127288035</v>
       </c>
       <c r="B84" t="n">
-        <v>95592</v>
+        <v>95820</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540206</v>
+        <v>540222</v>
       </c>
       <c r="R84" t="n">
-        <v>6448439</v>
+        <v>6448525</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288035</v>
+        <v>127288064</v>
       </c>
       <c r="B85" t="n">
-        <v>95819</v>
+        <v>95799</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540222</v>
+        <v>540177</v>
       </c>
       <c r="R85" t="n">
-        <v>6448525</v>
+        <v>6448499</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288040</v>
+        <v>127288031</v>
       </c>
       <c r="B86" t="n">
-        <v>105324</v>
+        <v>100557</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,16 +9185,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540165</v>
+        <v>540180</v>
       </c>
       <c r="R86" t="n">
-        <v>6448488</v>
+        <v>6448493</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9253,7 +9253,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9272,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>100556</v>
+        <v>105325</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9283,16 +9282,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R87" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9351,6 +9350,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288100</v>
+        <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>95787</v>
+        <v>100557</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540237</v>
       </c>
       <c r="R88" t="n">
-        <v>6448342</v>
+        <v>6448446</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9469,7 +9469,7 @@
         <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95802</v>
+        <v>95803</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288060</v>
+        <v>127288100</v>
       </c>
       <c r="B90" t="n">
-        <v>95798</v>
+        <v>95788</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540187</v>
+        <v>540195</v>
       </c>
       <c r="R90" t="n">
-        <v>6448488</v>
+        <v>6448342</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288023</v>
+        <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>100556</v>
+        <v>95799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540237</v>
+        <v>540187</v>
       </c>
       <c r="R91" t="n">
-        <v>6448446</v>
+        <v>6448488</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>91911</v>
+        <v>91912</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10048,32 +10048,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127288038</v>
+        <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>106065</v>
+        <v>95788</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540274</v>
+        <v>540163</v>
       </c>
       <c r="R95" t="n">
-        <v>6448610</v>
+        <v>6448463</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10121,18 +10121,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10151,10 +10145,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288108</v>
+        <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95787</v>
+        <v>95803</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10162,16 +10156,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10186,10 +10180,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540163</v>
+        <v>540224</v>
       </c>
       <c r="R96" t="n">
-        <v>6448463</v>
+        <v>6448404</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10248,32 +10242,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288011</v>
+        <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>95802</v>
+        <v>106066</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2668</v>
+        <v>220785</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10283,10 +10277,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540224</v>
+        <v>540274</v>
       </c>
       <c r="R97" t="n">
-        <v>6448404</v>
+        <v>6448610</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10321,12 +10315,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>95802</v>
+        <v>95803</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>127288065</v>
       </c>
       <c r="B99" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>91911</v>
+        <v>91912</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288057</v>
+        <v>127288027</v>
       </c>
       <c r="B101" t="n">
-        <v>95798</v>
+        <v>100557</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540076</v>
+        <v>540310</v>
       </c>
       <c r="R101" t="n">
-        <v>6448321</v>
+        <v>6448579</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288027</v>
+        <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>100556</v>
+        <v>95799</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540310</v>
+        <v>540076</v>
       </c>
       <c r="R102" t="n">
-        <v>6448579</v>
+        <v>6448321</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10830,10 +10830,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288028</v>
+        <v>127288094</v>
       </c>
       <c r="B103" t="n">
-        <v>100556</v>
+        <v>95788</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10841,21 +10841,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540335</v>
+        <v>540171</v>
       </c>
       <c r="R103" t="n">
-        <v>6448550</v>
+        <v>6448441</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10909,8 +10909,24 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -10927,10 +10943,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288101</v>
+        <v>127288061</v>
       </c>
       <c r="B104" t="n">
-        <v>95787</v>
+        <v>95799</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10938,21 +10954,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10962,10 +10978,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540333</v>
+        <v>540180</v>
       </c>
       <c r="R104" t="n">
-        <v>6448609</v>
+        <v>6448493</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11027,7 +11043,7 @@
         <v>127288105</v>
       </c>
       <c r="B105" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11121,10 +11137,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288061</v>
+        <v>127288101</v>
       </c>
       <c r="B106" t="n">
-        <v>95798</v>
+        <v>95788</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11148,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11172,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540180</v>
+        <v>540333</v>
       </c>
       <c r="R106" t="n">
-        <v>6448493</v>
+        <v>6448609</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11218,10 +11234,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288094</v>
+        <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>95787</v>
+        <v>100557</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11229,21 +11245,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11253,10 +11269,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540171</v>
+        <v>540335</v>
       </c>
       <c r="R107" t="n">
-        <v>6448441</v>
+        <v>6448550</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11297,24 +11313,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>95592</v>
+        <v>95593</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95592</v>
+        <v>95593</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11622,32 +11622,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288014</v>
+        <v>127288022</v>
       </c>
       <c r="B111" t="n">
-        <v>95802</v>
+        <v>91370</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2668</v>
+        <v>5442</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540187</v>
+        <v>540171</v>
       </c>
       <c r="R111" t="n">
-        <v>6448463</v>
+        <v>6448436</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288093</v>
+        <v>127288014</v>
       </c>
       <c r="B112" t="n">
-        <v>95787</v>
+        <v>95803</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540165</v>
+        <v>540187</v>
       </c>
       <c r="R112" t="n">
-        <v>6448484</v>
+        <v>6448463</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,24 +11798,8 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11832,32 +11816,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288022</v>
+        <v>127288093</v>
       </c>
       <c r="B113" t="n">
-        <v>91369</v>
+        <v>95788</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11867,10 +11851,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540171</v>
+        <v>540165</v>
       </c>
       <c r="R113" t="n">
-        <v>6448436</v>
+        <v>6448484</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11911,8 +11895,24 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11932,7 +11932,7 @@
         <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>95802</v>
+        <v>95803</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288037</v>
+        <v>127288059</v>
       </c>
       <c r="B115" t="n">
-        <v>95819</v>
+        <v>95799</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540213</v>
+        <v>540182</v>
       </c>
       <c r="R115" t="n">
-        <v>6448463</v>
+        <v>6448496</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288059</v>
+        <v>127288012</v>
       </c>
       <c r="B116" t="n">
-        <v>95798</v>
+        <v>95803</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540182</v>
+        <v>540210</v>
       </c>
       <c r="R116" t="n">
-        <v>6448496</v>
+        <v>6448417</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288075</v>
+        <v>127288039</v>
       </c>
       <c r="B117" t="n">
-        <v>91911</v>
+        <v>105325</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3884</v>
+        <v>221101</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540145</v>
+        <v>540178</v>
       </c>
       <c r="R117" t="n">
-        <v>6448348</v>
+        <v>6448431</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288084</v>
+        <v>127288037</v>
       </c>
       <c r="B118" t="n">
-        <v>95592</v>
+        <v>95820</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540075</v>
+        <v>540213</v>
       </c>
       <c r="R118" t="n">
-        <v>6448321</v>
+        <v>6448463</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288012</v>
+        <v>127288075</v>
       </c>
       <c r="B119" t="n">
-        <v>95802</v>
+        <v>91912</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540210</v>
+        <v>540145</v>
       </c>
       <c r="R119" t="n">
-        <v>6448417</v>
+        <v>6448348</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288039</v>
+        <v>127288084</v>
       </c>
       <c r="B120" t="n">
-        <v>105324</v>
+        <v>95593</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221101</v>
+        <v>2779</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540178</v>
+        <v>540075</v>
       </c>
       <c r="R120" t="n">
-        <v>6448431</v>
+        <v>6448321</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12611,7 +12611,7 @@
         <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>91911</v>
+        <v>91912</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>127288088</v>
       </c>
       <c r="B122" t="n">
-        <v>95592</v>
+        <v>95593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>95592</v>
+        <v>95593</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>79409</v>
+        <v>91310</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R125" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B126" t="n">
-        <v>91309</v>
+        <v>79409</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R126" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288078</v>
+        <v>127288103</v>
       </c>
       <c r="B128" t="n">
-        <v>91911</v>
+        <v>95788</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540193</v>
+        <v>540182</v>
       </c>
       <c r="R128" t="n">
-        <v>6448342</v>
+        <v>6448495</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288017</v>
+        <v>127288078</v>
       </c>
       <c r="B129" t="n">
-        <v>95802</v>
+        <v>91912</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540172</v>
+        <v>540193</v>
       </c>
       <c r="R129" t="n">
-        <v>6448507</v>
+        <v>6448342</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127288103</v>
+        <v>127288085</v>
       </c>
       <c r="B130" t="n">
-        <v>95787</v>
+        <v>95593</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540182</v>
+        <v>540251</v>
       </c>
       <c r="R130" t="n">
-        <v>6448495</v>
+        <v>6448599</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288085</v>
+        <v>127288017</v>
       </c>
       <c r="B131" t="n">
-        <v>95592</v>
+        <v>95803</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540251</v>
+        <v>540172</v>
       </c>
       <c r="R131" t="n">
-        <v>6448599</v>
+        <v>6448507</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>95802</v>
+        <v>100557</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R133" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>100556</v>
+        <v>95803</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R134" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -13969,7 +13969,7 @@
         <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>91911</v>
+        <v>91912</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288107</v>
+        <v>127288026</v>
       </c>
       <c r="B136" t="n">
-        <v>95787</v>
+        <v>100557</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540174</v>
+        <v>540319</v>
       </c>
       <c r="R136" t="n">
-        <v>6448493</v>
+        <v>6448616</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14163,7 +14163,7 @@
         <v>127288092</v>
       </c>
       <c r="B137" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288026</v>
+        <v>127288107</v>
       </c>
       <c r="B138" t="n">
-        <v>100556</v>
+        <v>95788</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540319</v>
+        <v>540174</v>
       </c>
       <c r="R138" t="n">
-        <v>6448616</v>
+        <v>6448493</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288068</v>
+        <v>127288104</v>
       </c>
       <c r="B139" t="n">
-        <v>79409</v>
+        <v>95788</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6431</v>
+        <v>2671</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540274</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448603</v>
+        <v>6448515</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288090</v>
+        <v>127288068</v>
       </c>
       <c r="B140" t="n">
-        <v>95592</v>
+        <v>79409</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540163</v>
+        <v>540274</v>
       </c>
       <c r="R140" t="n">
-        <v>6448518</v>
+        <v>6448603</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288079</v>
+        <v>127288090</v>
       </c>
       <c r="B141" t="n">
-        <v>91911</v>
+        <v>95593</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540310</v>
+        <v>540163</v>
       </c>
       <c r="R141" t="n">
-        <v>6448579</v>
+        <v>6448518</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288104</v>
+        <v>127288079</v>
       </c>
       <c r="B142" t="n">
-        <v>95787</v>
+        <v>91912</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540169</v>
+        <v>540310</v>
       </c>
       <c r="R142" t="n">
-        <v>6448515</v>
+        <v>6448579</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14745,7 +14745,7 @@
         <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>127288034</v>
       </c>
       <c r="B144" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B145" t="n">
-        <v>95802</v>
+        <v>91912</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R145" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288080</v>
+        <v>127288018</v>
       </c>
       <c r="B146" t="n">
-        <v>91911</v>
+        <v>95803</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540251</v>
+        <v>540167</v>
       </c>
       <c r="R146" t="n">
-        <v>6448423</v>
+        <v>6448513</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15133,7 +15133,7 @@
         <v>127288015</v>
       </c>
       <c r="B147" t="n">
-        <v>95802</v>
+        <v>95803</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>127288024</v>
       </c>
       <c r="B148" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288020</v>
+        <v>127288102</v>
       </c>
       <c r="B150" t="n">
-        <v>95802</v>
+        <v>95788</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,16 +15432,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540165</v>
+        <v>540208</v>
       </c>
       <c r="R150" t="n">
-        <v>6448511</v>
+        <v>6448415</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288102</v>
+        <v>127288020</v>
       </c>
       <c r="B151" t="n">
-        <v>95787</v>
+        <v>95803</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,16 +15529,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540208</v>
+        <v>540165</v>
       </c>
       <c r="R151" t="n">
-        <v>6448415</v>
+        <v>6448511</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15618,7 +15618,7 @@
         <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>91911</v>
+        <v>91912</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288089</v>
+        <v>127288064</v>
       </c>
       <c r="B83" t="n">
-        <v>95593</v>
+        <v>95799</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540206</v>
+        <v>540177</v>
       </c>
       <c r="R83" t="n">
-        <v>6448439</v>
+        <v>6448499</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B84" t="n">
-        <v>95820</v>
+        <v>95593</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R84" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288064</v>
+        <v>127288035</v>
       </c>
       <c r="B85" t="n">
-        <v>95799</v>
+        <v>95820</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540177</v>
+        <v>540222</v>
       </c>
       <c r="R85" t="n">
-        <v>6448499</v>
+        <v>6448525</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288023</v>
+        <v>127288100</v>
       </c>
       <c r="B88" t="n">
-        <v>100557</v>
+        <v>95788</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540237</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>6448446</v>
+        <v>6448342</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288100</v>
+        <v>127288060</v>
       </c>
       <c r="B90" t="n">
-        <v>95788</v>
+        <v>95799</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540195</v>
+        <v>540187</v>
       </c>
       <c r="R90" t="n">
-        <v>6448342</v>
+        <v>6448488</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288060</v>
+        <v>127288023</v>
       </c>
       <c r="B91" t="n">
-        <v>95799</v>
+        <v>100557</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540187</v>
+        <v>540237</v>
       </c>
       <c r="R91" t="n">
-        <v>6448488</v>
+        <v>6448446</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288013</v>
+        <v>127288027</v>
       </c>
       <c r="B98" t="n">
-        <v>95803</v>
+        <v>100557</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540189</v>
+        <v>540310</v>
       </c>
       <c r="R98" t="n">
-        <v>6448461</v>
+        <v>6448579</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288065</v>
+        <v>127288013</v>
       </c>
       <c r="B99" t="n">
-        <v>95799</v>
+        <v>95803</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540174</v>
+        <v>540189</v>
       </c>
       <c r="R99" t="n">
-        <v>6448468</v>
+        <v>6448461</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288074</v>
+        <v>127288065</v>
       </c>
       <c r="B100" t="n">
-        <v>91912</v>
+        <v>95799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540039</v>
+        <v>540174</v>
       </c>
       <c r="R100" t="n">
-        <v>6448303</v>
+        <v>6448468</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288027</v>
+        <v>127288074</v>
       </c>
       <c r="B101" t="n">
-        <v>100557</v>
+        <v>91912</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540310</v>
+        <v>540039</v>
       </c>
       <c r="R101" t="n">
-        <v>6448579</v>
+        <v>6448303</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10830,7 +10830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127288094</v>
+        <v>127288101</v>
       </c>
       <c r="B103" t="n">
         <v>95788</v>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540171</v>
+        <v>540333</v>
       </c>
       <c r="R103" t="n">
-        <v>6448441</v>
+        <v>6448609</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -10909,24 +10909,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -10943,10 +10927,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127288061</v>
+        <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95799</v>
+        <v>95788</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10954,21 +10938,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10978,10 +10962,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540180</v>
+        <v>540171</v>
       </c>
       <c r="R104" t="n">
-        <v>6448493</v>
+        <v>6448504</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11040,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288105</v>
+        <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95788</v>
+        <v>95799</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11051,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11075,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R105" t="n">
-        <v>6448504</v>
+        <v>6448493</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11137,7 +11121,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288101</v>
+        <v>127288094</v>
       </c>
       <c r="B106" t="n">
         <v>95788</v>
@@ -11172,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540333</v>
+        <v>540171</v>
       </c>
       <c r="R106" t="n">
-        <v>6448609</v>
+        <v>6448441</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11216,8 +11200,24 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11622,32 +11622,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127288022</v>
+        <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>91370</v>
+        <v>95803</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5442</v>
+        <v>2668</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540171</v>
+        <v>540187</v>
       </c>
       <c r="R111" t="n">
-        <v>6448436</v>
+        <v>6448463</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127288014</v>
+        <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95803</v>
+        <v>95788</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540187</v>
+        <v>540165</v>
       </c>
       <c r="R112" t="n">
-        <v>6448463</v>
+        <v>6448484</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -11798,8 +11798,24 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -11816,32 +11832,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127288093</v>
+        <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>95788</v>
+        <v>91370</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11851,10 +11867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540165</v>
+        <v>540171</v>
       </c>
       <c r="R113" t="n">
-        <v>6448484</v>
+        <v>6448436</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11895,24 +11911,8 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288059</v>
+        <v>127288037</v>
       </c>
       <c r="B115" t="n">
-        <v>95799</v>
+        <v>95820</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540182</v>
+        <v>540213</v>
       </c>
       <c r="R115" t="n">
-        <v>6448496</v>
+        <v>6448463</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288012</v>
+        <v>127288059</v>
       </c>
       <c r="B116" t="n">
-        <v>95803</v>
+        <v>95799</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540210</v>
+        <v>540182</v>
       </c>
       <c r="R116" t="n">
-        <v>6448417</v>
+        <v>6448496</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288039</v>
+        <v>127288075</v>
       </c>
       <c r="B117" t="n">
-        <v>105325</v>
+        <v>91912</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221101</v>
+        <v>3884</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540178</v>
+        <v>540145</v>
       </c>
       <c r="R117" t="n">
-        <v>6448431</v>
+        <v>6448348</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288037</v>
+        <v>127288084</v>
       </c>
       <c r="B118" t="n">
-        <v>95820</v>
+        <v>95593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540213</v>
+        <v>540075</v>
       </c>
       <c r="R118" t="n">
-        <v>6448463</v>
+        <v>6448321</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288075</v>
+        <v>127288012</v>
       </c>
       <c r="B119" t="n">
-        <v>91912</v>
+        <v>95803</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540145</v>
+        <v>540210</v>
       </c>
       <c r="R119" t="n">
-        <v>6448348</v>
+        <v>6448417</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288084</v>
+        <v>127288039</v>
       </c>
       <c r="B120" t="n">
-        <v>95593</v>
+        <v>105325</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2779</v>
+        <v>221101</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540075</v>
+        <v>540178</v>
       </c>
       <c r="R120" t="n">
-        <v>6448321</v>
+        <v>6448431</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127288103</v>
+        <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>95788</v>
+        <v>91912</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540182</v>
+        <v>540193</v>
       </c>
       <c r="R128" t="n">
-        <v>6448495</v>
+        <v>6448342</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127288078</v>
+        <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>91912</v>
+        <v>95803</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540193</v>
+        <v>540172</v>
       </c>
       <c r="R129" t="n">
-        <v>6448342</v>
+        <v>6448507</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127288085</v>
+        <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95593</v>
+        <v>95788</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540251</v>
+        <v>540182</v>
       </c>
       <c r="R130" t="n">
-        <v>6448599</v>
+        <v>6448495</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127288017</v>
+        <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95803</v>
+        <v>95593</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540172</v>
+        <v>540251</v>
       </c>
       <c r="R131" t="n">
-        <v>6448507</v>
+        <v>6448599</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>100557</v>
+        <v>95803</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R133" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>95803</v>
+        <v>100557</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R134" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288026</v>
+        <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>100557</v>
+        <v>95788</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540319</v>
+        <v>540174</v>
       </c>
       <c r="R136" t="n">
-        <v>6448616</v>
+        <v>6448493</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288107</v>
+        <v>127288026</v>
       </c>
       <c r="B138" t="n">
-        <v>95788</v>
+        <v>100557</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540174</v>
+        <v>540319</v>
       </c>
       <c r="R138" t="n">
-        <v>6448493</v>
+        <v>6448616</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288104</v>
+        <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>95788</v>
+        <v>95593</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540169</v>
+        <v>540163</v>
       </c>
       <c r="R139" t="n">
-        <v>6448515</v>
+        <v>6448518</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288068</v>
+        <v>127288079</v>
       </c>
       <c r="B140" t="n">
-        <v>79409</v>
+        <v>91912</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540274</v>
+        <v>540310</v>
       </c>
       <c r="R140" t="n">
-        <v>6448603</v>
+        <v>6448579</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288090</v>
+        <v>127288104</v>
       </c>
       <c r="B141" t="n">
-        <v>95593</v>
+        <v>95788</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R141" t="n">
-        <v>6448518</v>
+        <v>6448515</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288079</v>
+        <v>127288036</v>
       </c>
       <c r="B142" t="n">
-        <v>91912</v>
+        <v>95820</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3884</v>
+        <v>2818</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540310</v>
+        <v>540336</v>
       </c>
       <c r="R142" t="n">
-        <v>6448579</v>
+        <v>6448578</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288036</v>
+        <v>127288068</v>
       </c>
       <c r="B143" t="n">
-        <v>95820</v>
+        <v>79409</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2818</v>
+        <v>6431</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540336</v>
+        <v>540274</v>
       </c>
       <c r="R143" t="n">
-        <v>6448578</v>
+        <v>6448603</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14936,10 +14936,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127288080</v>
+        <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>91912</v>
+        <v>95803</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14947,21 +14947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3884</v>
+        <v>2668</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>540251</v>
+        <v>540167</v>
       </c>
       <c r="R145" t="n">
-        <v>6448423</v>
+        <v>6448513</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288018</v>
+        <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>95803</v>
+        <v>91912</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540167</v>
+        <v>540251</v>
       </c>
       <c r="R146" t="n">
-        <v>6448513</v>
+        <v>6448423</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288102</v>
+        <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>95788</v>
+        <v>95803</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,16 +15432,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540208</v>
+        <v>540165</v>
       </c>
       <c r="R150" t="n">
-        <v>6448415</v>
+        <v>6448511</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288020</v>
+        <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95803</v>
+        <v>95788</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,16 +15529,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540165</v>
+        <v>540208</v>
       </c>
       <c r="R151" t="n">
-        <v>6448511</v>
+        <v>6448415</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288064</v>
+        <v>127288031</v>
       </c>
       <c r="B83" t="n">
-        <v>95799</v>
+        <v>100558</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,21 +8894,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540177</v>
+        <v>540180</v>
       </c>
       <c r="R83" t="n">
-        <v>6448499</v>
+        <v>6448493</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127288089</v>
+        <v>127288064</v>
       </c>
       <c r="B84" t="n">
-        <v>95593</v>
+        <v>95800</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540206</v>
+        <v>540177</v>
       </c>
       <c r="R84" t="n">
-        <v>6448439</v>
+        <v>6448499</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B85" t="n">
-        <v>95820</v>
+        <v>95594</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R85" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288031</v>
+        <v>127288035</v>
       </c>
       <c r="B86" t="n">
-        <v>100557</v>
+        <v>95821</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9185,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540180</v>
+        <v>540222</v>
       </c>
       <c r="R86" t="n">
-        <v>6448493</v>
+        <v>6448525</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9274,7 +9274,7 @@
         <v>127288040</v>
       </c>
       <c r="B87" t="n">
-        <v>105325</v>
+        <v>105326</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127288100</v>
+        <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>95788</v>
+        <v>100558</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9380,21 +9380,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540237</v>
       </c>
       <c r="R88" t="n">
-        <v>6448342</v>
+        <v>6448446</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9469,7 +9469,7 @@
         <v>127288019</v>
       </c>
       <c r="B89" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288060</v>
+        <v>127288100</v>
       </c>
       <c r="B90" t="n">
-        <v>95799</v>
+        <v>95789</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,21 +9574,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540187</v>
+        <v>540195</v>
       </c>
       <c r="R90" t="n">
-        <v>6448488</v>
+        <v>6448342</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127288023</v>
+        <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>100557</v>
+        <v>95800</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9671,21 +9671,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540237</v>
+        <v>540187</v>
       </c>
       <c r="R91" t="n">
-        <v>6448446</v>
+        <v>6448488</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>127288082</v>
       </c>
       <c r="B93" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>127288025</v>
       </c>
       <c r="B94" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>127288011</v>
       </c>
       <c r="B96" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>127288038</v>
       </c>
       <c r="B97" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127288027</v>
+        <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>100557</v>
+        <v>95804</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10356,21 +10356,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540310</v>
+        <v>540189</v>
       </c>
       <c r="R98" t="n">
-        <v>6448579</v>
+        <v>6448461</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288013</v>
+        <v>127288065</v>
       </c>
       <c r="B99" t="n">
-        <v>95803</v>
+        <v>95800</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540189</v>
+        <v>540174</v>
       </c>
       <c r="R99" t="n">
-        <v>6448461</v>
+        <v>6448468</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288065</v>
+        <v>127288074</v>
       </c>
       <c r="B100" t="n">
-        <v>95799</v>
+        <v>91913</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540174</v>
+        <v>540039</v>
       </c>
       <c r="R100" t="n">
-        <v>6448468</v>
+        <v>6448303</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288074</v>
+        <v>127288057</v>
       </c>
       <c r="B101" t="n">
-        <v>91912</v>
+        <v>95800</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540039</v>
+        <v>540076</v>
       </c>
       <c r="R101" t="n">
-        <v>6448303</v>
+        <v>6448321</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288057</v>
+        <v>127288027</v>
       </c>
       <c r="B102" t="n">
-        <v>95799</v>
+        <v>100558</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540076</v>
+        <v>540310</v>
       </c>
       <c r="R102" t="n">
-        <v>6448321</v>
+        <v>6448579</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10833,7 +10833,7 @@
         <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>127288061</v>
       </c>
       <c r="B105" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>127288094</v>
       </c>
       <c r="B106" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>127288028</v>
       </c>
       <c r="B107" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>95593</v>
+        <v>95594</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95593</v>
+        <v>95594</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12026,10 +12026,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127288037</v>
+        <v>127288039</v>
       </c>
       <c r="B115" t="n">
-        <v>95820</v>
+        <v>105326</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,21 +12037,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>221101</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540213</v>
+        <v>540178</v>
       </c>
       <c r="R115" t="n">
-        <v>6448463</v>
+        <v>6448431</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12123,10 +12123,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127288059</v>
+        <v>127288037</v>
       </c>
       <c r="B116" t="n">
-        <v>95799</v>
+        <v>95821</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540182</v>
+        <v>540213</v>
       </c>
       <c r="R116" t="n">
-        <v>6448496</v>
+        <v>6448463</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127288075</v>
+        <v>127288059</v>
       </c>
       <c r="B117" t="n">
-        <v>91912</v>
+        <v>95800</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540145</v>
+        <v>540182</v>
       </c>
       <c r="R117" t="n">
-        <v>6448348</v>
+        <v>6448496</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127288084</v>
+        <v>127288075</v>
       </c>
       <c r="B118" t="n">
-        <v>95593</v>
+        <v>91913</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12328,21 +12328,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540075</v>
+        <v>540145</v>
       </c>
       <c r="R118" t="n">
-        <v>6448321</v>
+        <v>6448348</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127288012</v>
+        <v>127288084</v>
       </c>
       <c r="B119" t="n">
-        <v>95803</v>
+        <v>95594</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12425,21 +12425,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540210</v>
+        <v>540075</v>
       </c>
       <c r="R119" t="n">
-        <v>6448417</v>
+        <v>6448321</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127288039</v>
+        <v>127288012</v>
       </c>
       <c r="B120" t="n">
-        <v>105325</v>
+        <v>95804</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221101</v>
+        <v>2668</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540178</v>
+        <v>540210</v>
       </c>
       <c r="R120" t="n">
-        <v>6448431</v>
+        <v>6448417</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127288076</v>
+        <v>127288088</v>
       </c>
       <c r="B121" t="n">
-        <v>91912</v>
+        <v>95594</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12619,21 +12619,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540155</v>
+        <v>540338</v>
       </c>
       <c r="R121" t="n">
-        <v>6448348</v>
+        <v>6448617</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288088</v>
+        <v>127288076</v>
       </c>
       <c r="B122" t="n">
-        <v>95593</v>
+        <v>91913</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12716,21 +12716,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540338</v>
+        <v>540155</v>
       </c>
       <c r="R122" t="n">
-        <v>6448617</v>
+        <v>6448348</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12805,7 +12805,7 @@
         <v>127288091</v>
       </c>
       <c r="B123" t="n">
-        <v>95593</v>
+        <v>95594</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B125" t="n">
-        <v>91310</v>
+        <v>79409</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R125" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B126" t="n">
-        <v>79409</v>
+        <v>91311</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R126" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95593</v>
+        <v>95594</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>127288021</v>
       </c>
       <c r="B133" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>127288029</v>
       </c>
       <c r="B134" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288077</v>
+        <v>127288026</v>
       </c>
       <c r="B135" t="n">
-        <v>91912</v>
+        <v>100558</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540152</v>
+        <v>540319</v>
       </c>
       <c r="R135" t="n">
-        <v>6448350</v>
+        <v>6448616</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288107</v>
+        <v>127288077</v>
       </c>
       <c r="B136" t="n">
-        <v>95788</v>
+        <v>91913</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540174</v>
+        <v>540152</v>
       </c>
       <c r="R136" t="n">
-        <v>6448493</v>
+        <v>6448350</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288092</v>
+        <v>127288107</v>
       </c>
       <c r="B137" t="n">
-        <v>95801</v>
+        <v>95789</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2666</v>
+        <v>2671</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540169</v>
+        <v>540174</v>
       </c>
       <c r="R137" t="n">
-        <v>6448494</v>
+        <v>6448493</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14257,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127288026</v>
+        <v>127288092</v>
       </c>
       <c r="B138" t="n">
-        <v>100557</v>
+        <v>95802</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222771</v>
+        <v>2666</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540319</v>
+        <v>540169</v>
       </c>
       <c r="R138" t="n">
-        <v>6448616</v>
+        <v>6448494</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14357,7 +14357,7 @@
         <v>127288090</v>
       </c>
       <c r="B139" t="n">
-        <v>95593</v>
+        <v>95594</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>127288079</v>
       </c>
       <c r="B140" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288104</v>
+        <v>127288036</v>
       </c>
       <c r="B141" t="n">
-        <v>95788</v>
+        <v>95821</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2671</v>
+        <v>2818</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540169</v>
+        <v>540336</v>
       </c>
       <c r="R141" t="n">
-        <v>6448515</v>
+        <v>6448578</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288036</v>
+        <v>127288034</v>
       </c>
       <c r="B142" t="n">
-        <v>95820</v>
+        <v>100558</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2818</v>
+        <v>222771</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540336</v>
+        <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448578</v>
+        <v>6448432</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288034</v>
+        <v>127288104</v>
       </c>
       <c r="B144" t="n">
-        <v>100557</v>
+        <v>95789</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14877,7 +14877,7 @@
         <v>540169</v>
       </c>
       <c r="R144" t="n">
-        <v>6448432</v>
+        <v>6448515</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14939,7 +14939,7 @@
         <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>127288080</v>
       </c>
       <c r="B146" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288015</v>
+        <v>127288024</v>
       </c>
       <c r="B147" t="n">
-        <v>95803</v>
+        <v>100558</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540180</v>
+        <v>540221</v>
       </c>
       <c r="R147" t="n">
-        <v>6448493</v>
+        <v>6448466</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,10 +15227,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288024</v>
+        <v>127288032</v>
       </c>
       <c r="B148" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540221</v>
+        <v>540179</v>
       </c>
       <c r="R148" t="n">
-        <v>6448466</v>
+        <v>6448506</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15324,10 +15324,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127288032</v>
+        <v>127288015</v>
       </c>
       <c r="B149" t="n">
-        <v>100557</v>
+        <v>95804</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>540179</v>
+        <v>540180</v>
       </c>
       <c r="R149" t="n">
-        <v>6448506</v>
+        <v>6448493</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15424,7 +15424,7 @@
         <v>127288020</v>
       </c>
       <c r="B150" t="n">
-        <v>95803</v>
+        <v>95804</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>127288102</v>
       </c>
       <c r="B151" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>127288081</v>
       </c>
       <c r="B152" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY152"/>
+  <dimension ref="A1:AY153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15710,6 +15710,123 @@
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>129376443</v>
+      </c>
+      <c r="B153" t="n">
+        <v>92311</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>366</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Ekhamra, Ög</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>540229</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6448400</v>
+      </c>
+      <c r="S153" t="n">
+        <v>20</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92311</v>
+        <v>92324</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92324</v>
+        <v>92325</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92330</v>
+        <v>92334</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92335</v>
+        <v>92338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92338</v>
+        <v>92366</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92366</v>
+        <v>92372</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15715,7 +15715,7 @@
         <v>129376443</v>
       </c>
       <c r="B153" t="n">
-        <v>92373</v>
+        <v>92378</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -4499,7 +4499,7 @@
         <v>127081966</v>
       </c>
       <c r="B38" t="n">
-        <v>92543</v>
+        <v>92521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127081927</v>
+        <v>127081948</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>95768</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540175</v>
+        <v>540060</v>
       </c>
       <c r="R39" t="n">
-        <v>6448411</v>
+        <v>6448311</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4690,32 +4690,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127081948</v>
+        <v>127081927</v>
       </c>
       <c r="B40" t="n">
-        <v>95790</v>
+        <v>91339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540060</v>
+        <v>540175</v>
       </c>
       <c r="R40" t="n">
-        <v>6448311</v>
+        <v>6448411</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4790,7 +4790,7 @@
         <v>127081956</v>
       </c>
       <c r="B41" t="n">
-        <v>95790</v>
+        <v>95768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>127081969</v>
       </c>
       <c r="B42" t="n">
-        <v>95584</v>
+        <v>95562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127081929</v>
+        <v>127081953</v>
       </c>
       <c r="B43" t="n">
-        <v>95907</v>
+        <v>79391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540163</v>
+        <v>540080</v>
       </c>
       <c r="R43" t="n">
-        <v>6448407</v>
+        <v>6448328</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127081953</v>
+        <v>127081929</v>
       </c>
       <c r="B44" t="n">
-        <v>79403</v>
+        <v>95885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540080</v>
+        <v>540163</v>
       </c>
       <c r="R44" t="n">
-        <v>6448328</v>
+        <v>6448407</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>127081916</v>
       </c>
       <c r="B45" t="n">
-        <v>91903</v>
+        <v>91881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>127081964</v>
       </c>
       <c r="B46" t="n">
-        <v>95584</v>
+        <v>95562</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,32 +5369,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127081932</v>
+        <v>127081921</v>
       </c>
       <c r="B47" t="n">
-        <v>75069</v>
+        <v>95768</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1460</v>
+        <v>2667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540159</v>
+        <v>540200</v>
       </c>
       <c r="R47" t="n">
-        <v>6448374</v>
+        <v>6448453</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127081921</v>
+        <v>127081963</v>
       </c>
       <c r="B48" t="n">
-        <v>95790</v>
+        <v>95768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540200</v>
+        <v>540121</v>
       </c>
       <c r="R48" t="n">
-        <v>6448453</v>
+        <v>6448366</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127081963</v>
+        <v>127081957</v>
       </c>
       <c r="B49" t="n">
-        <v>95790</v>
+        <v>95562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540121</v>
+        <v>540098</v>
       </c>
       <c r="R49" t="n">
-        <v>6448366</v>
+        <v>6448341</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5660,32 +5660,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127081957</v>
+        <v>127081932</v>
       </c>
       <c r="B50" t="n">
-        <v>95584</v>
+        <v>75057</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2779</v>
+        <v>1460</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540098</v>
+        <v>540159</v>
       </c>
       <c r="R50" t="n">
-        <v>6448341</v>
+        <v>6448374</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5760,7 +5760,7 @@
         <v>127081949</v>
       </c>
       <c r="B51" t="n">
-        <v>30136</v>
+        <v>30129</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>127081951</v>
       </c>
       <c r="B52" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>127081959</v>
       </c>
       <c r="B53" t="n">
-        <v>95584</v>
+        <v>95562</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>127081918</v>
       </c>
       <c r="B54" t="n">
-        <v>95790</v>
+        <v>95768</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>127081940</v>
       </c>
       <c r="B55" t="n">
-        <v>100548</v>
+        <v>100525</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>127081939</v>
       </c>
       <c r="B56" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>127081926</v>
       </c>
       <c r="B57" t="n">
-        <v>91361</v>
+        <v>91339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>127081946</v>
       </c>
       <c r="B58" t="n">
-        <v>95584</v>
+        <v>95562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>127081975</v>
       </c>
       <c r="B59" t="n">
-        <v>95584</v>
+        <v>95562</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127081950</v>
       </c>
       <c r="B60" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>127081955</v>
       </c>
       <c r="B61" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>127081942</v>
       </c>
       <c r="B62" t="n">
-        <v>91903</v>
+        <v>91881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>127081954</v>
       </c>
       <c r="B63" t="n">
-        <v>95790</v>
+        <v>95768</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>127081960</v>
       </c>
       <c r="B64" t="n">
-        <v>92543</v>
+        <v>92521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>127081920</v>
       </c>
       <c r="B65" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>127081967</v>
       </c>
       <c r="B66" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>127081952</v>
       </c>
       <c r="B67" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>127081941</v>
       </c>
       <c r="B68" t="n">
-        <v>91903</v>
+        <v>91881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>127081968</v>
       </c>
       <c r="B69" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>127081958</v>
       </c>
       <c r="B70" t="n">
-        <v>91903</v>
+        <v>91881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127081971</v>
+        <v>127081945</v>
       </c>
       <c r="B71" t="n">
-        <v>95779</v>
+        <v>91881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540096</v>
+        <v>540092</v>
       </c>
       <c r="R71" t="n">
-        <v>6448345</v>
+        <v>6448293</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127081945</v>
+        <v>127081974</v>
       </c>
       <c r="B72" t="n">
-        <v>91903</v>
+        <v>95562</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540092</v>
+        <v>540097</v>
       </c>
       <c r="R72" t="n">
-        <v>6448293</v>
+        <v>6448346</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127081974</v>
+        <v>127081923</v>
       </c>
       <c r="B73" t="n">
-        <v>95584</v>
+        <v>95757</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540097</v>
+        <v>540198</v>
       </c>
       <c r="R73" t="n">
-        <v>6448346</v>
+        <v>6448437</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127081923</v>
+        <v>127081928</v>
       </c>
       <c r="B74" t="n">
-        <v>95779</v>
+        <v>95768</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540198</v>
+        <v>540172</v>
       </c>
       <c r="R74" t="n">
-        <v>6448437</v>
+        <v>6448411</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127081928</v>
+        <v>127081971</v>
       </c>
       <c r="B75" t="n">
-        <v>95790</v>
+        <v>95757</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8096,21 +8096,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540172</v>
+        <v>540096</v>
       </c>
       <c r="R75" t="n">
-        <v>6448411</v>
+        <v>6448345</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127081919</v>
+        <v>127081935</v>
       </c>
       <c r="B76" t="n">
-        <v>9401</v>
+        <v>95768</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8193,55 +8193,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>101246</v>
+        <v>2667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540210</v>
+        <v>540133</v>
       </c>
       <c r="R76" t="n">
-        <v>6448425</v>
+        <v>6448375</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8282,7 +8261,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8301,10 +8279,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127081935</v>
+        <v>127081919</v>
       </c>
       <c r="B77" t="n">
-        <v>95790</v>
+        <v>9398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8312,34 +8290,55 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>101246</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hamra Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540133</v>
+        <v>540210</v>
       </c>
       <c r="R77" t="n">
-        <v>6448375</v>
+        <v>6448425</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8380,6 +8379,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>127081962</v>
       </c>
       <c r="B78" t="n">
-        <v>92543</v>
+        <v>92521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>127081976</v>
       </c>
       <c r="B79" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>127081925</v>
       </c>
       <c r="B80" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127081944</v>
       </c>
       <c r="B81" t="n">
-        <v>91903</v>
+        <v>91881</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>127081924</v>
       </c>
       <c r="B82" t="n">
-        <v>95779</v>
+        <v>95757</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127288031</v>
+        <v>127288040</v>
       </c>
       <c r="B83" t="n">
-        <v>100558</v>
+        <v>105290</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8894,16 +8894,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540180</v>
+        <v>540165</v>
       </c>
       <c r="R83" t="n">
-        <v>6448493</v>
+        <v>6448488</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8962,6 +8962,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8983,7 +8984,7 @@
         <v>127288064</v>
       </c>
       <c r="B84" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9077,10 +9078,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127288089</v>
+        <v>127288031</v>
       </c>
       <c r="B85" t="n">
-        <v>95594</v>
+        <v>100525</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9088,21 +9089,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9112,10 +9113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540206</v>
+        <v>540180</v>
       </c>
       <c r="R85" t="n">
-        <v>6448439</v>
+        <v>6448493</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9174,10 +9175,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127288035</v>
+        <v>127288089</v>
       </c>
       <c r="B86" t="n">
-        <v>95821</v>
+        <v>95562</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,21 +9186,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9209,10 +9210,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540222</v>
+        <v>540206</v>
       </c>
       <c r="R86" t="n">
-        <v>6448525</v>
+        <v>6448439</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127288040</v>
+        <v>127288035</v>
       </c>
       <c r="B87" t="n">
-        <v>105326</v>
+        <v>95789</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,21 +9283,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221101</v>
+        <v>2818</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540165</v>
+        <v>540222</v>
       </c>
       <c r="R87" t="n">
-        <v>6448488</v>
+        <v>6448525</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9350,7 +9351,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>127288023</v>
       </c>
       <c r="B88" t="n">
-        <v>100558</v>
+        <v>100525</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127288019</v>
+        <v>127288100</v>
       </c>
       <c r="B89" t="n">
-        <v>95804</v>
+        <v>95757</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540163</v>
+        <v>540195</v>
       </c>
       <c r="R89" t="n">
-        <v>6448517</v>
+        <v>6448342</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127288100</v>
+        <v>127288019</v>
       </c>
       <c r="B90" t="n">
-        <v>95789</v>
+        <v>95772</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9574,16 +9574,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540195</v>
+        <v>540163</v>
       </c>
       <c r="R90" t="n">
-        <v>6448342</v>
+        <v>6448517</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9663,7 +9663,7 @@
         <v>127288060</v>
       </c>
       <c r="B91" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>127288063</v>
       </c>
       <c r="B92" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127288082</v>
+        <v>127288025</v>
       </c>
       <c r="B93" t="n">
-        <v>91913</v>
+        <v>100525</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,21 +9865,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540219</v>
+        <v>540221</v>
       </c>
       <c r="R93" t="n">
-        <v>6448415</v>
+        <v>6448522</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127288025</v>
+        <v>127288082</v>
       </c>
       <c r="B94" t="n">
-        <v>100558</v>
+        <v>91881</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9962,21 +9962,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540221</v>
+        <v>540219</v>
       </c>
       <c r="R94" t="n">
-        <v>6448522</v>
+        <v>6448415</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10051,7 +10051,7 @@
         <v>127288108</v>
       </c>
       <c r="B95" t="n">
-        <v>95789</v>
+        <v>95757</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10145,32 +10145,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127288011</v>
+        <v>127288038</v>
       </c>
       <c r="B96" t="n">
-        <v>95804</v>
+        <v>106031</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2668</v>
+        <v>220785</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10180,10 +10180,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540224</v>
+        <v>540274</v>
       </c>
       <c r="R96" t="n">
-        <v>6448404</v>
+        <v>6448610</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10218,12 +10218,18 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10242,32 +10248,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127288038</v>
+        <v>127288011</v>
       </c>
       <c r="B97" t="n">
-        <v>106067</v>
+        <v>95772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10277,10 +10283,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540274</v>
+        <v>540224</v>
       </c>
       <c r="R97" t="n">
-        <v>6448610</v>
+        <v>6448404</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10315,18 +10321,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Stor och till synes frisk ask.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>127288013</v>
       </c>
       <c r="B98" t="n">
-        <v>95804</v>
+        <v>95772</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127288065</v>
+        <v>127288027</v>
       </c>
       <c r="B99" t="n">
-        <v>95800</v>
+        <v>100525</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10453,21 +10453,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540174</v>
+        <v>540310</v>
       </c>
       <c r="R99" t="n">
-        <v>6448468</v>
+        <v>6448579</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127288074</v>
+        <v>127288065</v>
       </c>
       <c r="B100" t="n">
-        <v>91913</v>
+        <v>95768</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540039</v>
+        <v>540174</v>
       </c>
       <c r="R100" t="n">
-        <v>6448303</v>
+        <v>6448468</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127288057</v>
+        <v>127288074</v>
       </c>
       <c r="B101" t="n">
-        <v>95800</v>
+        <v>91881</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,21 +10647,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540076</v>
+        <v>540039</v>
       </c>
       <c r="R101" t="n">
-        <v>6448321</v>
+        <v>6448303</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127288027</v>
+        <v>127288057</v>
       </c>
       <c r="B102" t="n">
-        <v>100558</v>
+        <v>95768</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540310</v>
+        <v>540076</v>
       </c>
       <c r="R102" t="n">
-        <v>6448579</v>
+        <v>6448321</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10833,7 +10833,7 @@
         <v>127288101</v>
       </c>
       <c r="B103" t="n">
-        <v>95789</v>
+        <v>95757</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>127288105</v>
       </c>
       <c r="B104" t="n">
-        <v>95789</v>
+        <v>95757</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11024,10 +11024,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127288061</v>
+        <v>127288028</v>
       </c>
       <c r="B105" t="n">
-        <v>95800</v>
+        <v>100525</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>222771</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540180</v>
+        <v>540335</v>
       </c>
       <c r="R105" t="n">
-        <v>6448493</v>
+        <v>6448550</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127288094</v>
+        <v>127288061</v>
       </c>
       <c r="B106" t="n">
-        <v>95789</v>
+        <v>95768</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540171</v>
+        <v>540180</v>
       </c>
       <c r="R106" t="n">
-        <v>6448441</v>
+        <v>6448493</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11200,24 +11200,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>oxel</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Sorbus intermedia</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11234,10 +11218,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127288028</v>
+        <v>127288094</v>
       </c>
       <c r="B107" t="n">
-        <v>100558</v>
+        <v>95757</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11245,21 +11229,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11269,10 +11253,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540335</v>
+        <v>540171</v>
       </c>
       <c r="R107" t="n">
-        <v>6448550</v>
+        <v>6448441</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11313,8 +11297,24 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>oxel</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Sorbus intermedia</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11334,7 +11334,7 @@
         <v>127288030</v>
       </c>
       <c r="B108" t="n">
-        <v>100558</v>
+        <v>100525</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>127288086</v>
       </c>
       <c r="B109" t="n">
-        <v>95594</v>
+        <v>95562</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>127288087</v>
       </c>
       <c r="B110" t="n">
-        <v>95594</v>
+        <v>95562</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>127288014</v>
       </c>
       <c r="B111" t="n">
-        <v>95804</v>
+        <v>95772</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>127288093</v>
       </c>
       <c r="B112" t="n">
-        <v>95789</v>
+        <v>95757</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>127288022</v>
       </c>
       <c r="B113" t="n">
-        <v>91371</v>
+        <v>91339</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>127288016</v>
       </c>
       <c r="B114" t="n">
-        <v>95804</v>
+        <v>95772</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>127288039</v>
       </c>
       <c r="B115" t="n">
-        <v>105326</v>
+        <v>105290</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>127288037</v>
       </c>
       <c r="B116" t="n">
-        <v>95821</v>
+        <v>95789</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>127288059</v>
       </c>
       <c r="B117" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127288075</v>
       </c>
       <c r="B118" t="n">
-        <v>91913</v>
+        <v>91881</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>127288084</v>
       </c>
       <c r="B119" t="n">
-        <v>95594</v>
+        <v>95562</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>127288012</v>
       </c>
       <c r="B120" t="n">
-        <v>95804</v>
+        <v>95772</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127288088</v>
+        <v>127288076</v>
       </c>
       <c r="B121" t="n">
-        <v>95594</v>
+        <v>91881</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12619,21 +12619,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540338</v>
+        <v>540155</v>
       </c>
       <c r="R121" t="n">
-        <v>6448617</v>
+        <v>6448348</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -12705,10 +12705,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127288076</v>
+        <v>127288091</v>
       </c>
       <c r="B122" t="n">
-        <v>91913</v>
+        <v>95562</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12716,21 +12716,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540155</v>
+        <v>540169</v>
       </c>
       <c r="R122" t="n">
-        <v>6448348</v>
+        <v>6448494</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127288091</v>
+        <v>127288088</v>
       </c>
       <c r="B123" t="n">
-        <v>95594</v>
+        <v>95562</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540169</v>
+        <v>540338</v>
       </c>
       <c r="R123" t="n">
-        <v>6448494</v>
+        <v>6448617</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -12902,7 +12902,7 @@
         <v>127288062</v>
       </c>
       <c r="B124" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12996,32 +12996,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127288069</v>
+        <v>127288110</v>
       </c>
       <c r="B125" t="n">
-        <v>79409</v>
+        <v>91279</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540332</v>
+        <v>540237</v>
       </c>
       <c r="R125" t="n">
-        <v>6448609</v>
+        <v>6448446</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13093,32 +13093,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127288110</v>
+        <v>127288069</v>
       </c>
       <c r="B126" t="n">
-        <v>91311</v>
+        <v>79391</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540237</v>
+        <v>540332</v>
       </c>
       <c r="R126" t="n">
-        <v>6448446</v>
+        <v>6448609</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13193,7 +13193,7 @@
         <v>127288033</v>
       </c>
       <c r="B127" t="n">
-        <v>100558</v>
+        <v>100525</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>127288078</v>
       </c>
       <c r="B128" t="n">
-        <v>91913</v>
+        <v>91881</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>127288017</v>
       </c>
       <c r="B129" t="n">
-        <v>95804</v>
+        <v>95772</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>127288103</v>
       </c>
       <c r="B130" t="n">
-        <v>95789</v>
+        <v>95757</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>127288085</v>
       </c>
       <c r="B131" t="n">
-        <v>95594</v>
+        <v>95562</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>127288058</v>
       </c>
       <c r="B132" t="n">
-        <v>95800</v>
+        <v>95768</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127288021</v>
+        <v>127288029</v>
       </c>
       <c r="B133" t="n">
-        <v>95804</v>
+        <v>100525</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13783,21 +13783,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13807,10 +13807,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540167</v>
+        <v>540217</v>
       </c>
       <c r="R133" t="n">
-        <v>6448497</v>
+        <v>6448454</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127288029</v>
+        <v>127288021</v>
       </c>
       <c r="B134" t="n">
-        <v>100558</v>
+        <v>95772</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13880,21 +13880,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540217</v>
+        <v>540167</v>
       </c>
       <c r="R134" t="n">
-        <v>6448454</v>
+        <v>6448497</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -13966,10 +13966,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127288026</v>
+        <v>127288077</v>
       </c>
       <c r="B135" t="n">
-        <v>100558</v>
+        <v>91881</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540319</v>
+        <v>540152</v>
       </c>
       <c r="R135" t="n">
-        <v>6448616</v>
+        <v>6448350</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14063,10 +14063,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127288077</v>
+        <v>127288107</v>
       </c>
       <c r="B136" t="n">
-        <v>91913</v>
+        <v>95757</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540152</v>
+        <v>540174</v>
       </c>
       <c r="R136" t="n">
-        <v>6448350</v>
+        <v>6448493</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14160,10 +14160,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127288107</v>
+        <v>127288026</v>
       </c>
       <c r="B137" t="n">
-        <v>95789</v>
+        <v>100525</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14171,21 +14171,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540174</v>
+        <v>540319</v>
       </c>
       <c r="R137" t="n">
-        <v>6448493</v>
+        <v>6448616</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14260,7 +14260,7 @@
         <v>127288092</v>
       </c>
       <c r="B138" t="n">
-        <v>95802</v>
+        <v>95770</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127288090</v>
+        <v>127288034</v>
       </c>
       <c r="B139" t="n">
-        <v>95594</v>
+        <v>100525</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14365,21 +14365,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2779</v>
+        <v>222771</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540163</v>
+        <v>540169</v>
       </c>
       <c r="R139" t="n">
-        <v>6448518</v>
+        <v>6448432</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14451,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127288079</v>
+        <v>127288090</v>
       </c>
       <c r="B140" t="n">
-        <v>91913</v>
+        <v>95562</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540310</v>
+        <v>540163</v>
       </c>
       <c r="R140" t="n">
-        <v>6448579</v>
+        <v>6448518</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -14548,10 +14548,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127288036</v>
+        <v>127288079</v>
       </c>
       <c r="B141" t="n">
-        <v>95821</v>
+        <v>91881</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2818</v>
+        <v>3884</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540336</v>
+        <v>540310</v>
       </c>
       <c r="R141" t="n">
-        <v>6448578</v>
+        <v>6448579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14645,10 +14645,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127288034</v>
+        <v>127288104</v>
       </c>
       <c r="B142" t="n">
-        <v>100558</v>
+        <v>95757</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14656,21 +14656,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14683,7 +14683,7 @@
         <v>540169</v>
       </c>
       <c r="R142" t="n">
-        <v>6448432</v>
+        <v>6448515</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14742,10 +14742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127288068</v>
+        <v>127288036</v>
       </c>
       <c r="B143" t="n">
-        <v>79409</v>
+        <v>95789</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14753,21 +14753,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6431</v>
+        <v>2818</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540274</v>
+        <v>540336</v>
       </c>
       <c r="R143" t="n">
-        <v>6448603</v>
+        <v>6448578</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127288104</v>
+        <v>127288068</v>
       </c>
       <c r="B144" t="n">
-        <v>95789</v>
+        <v>79391</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14850,21 +14850,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2671</v>
+        <v>6431</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540169</v>
+        <v>540274</v>
       </c>
       <c r="R144" t="n">
-        <v>6448515</v>
+        <v>6448603</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -14939,7 +14939,7 @@
         <v>127288018</v>
       </c>
       <c r="B145" t="n">
-        <v>95804</v>
+        <v>95772</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127288080</v>
+        <v>127288024</v>
       </c>
       <c r="B146" t="n">
-        <v>91913</v>
+        <v>100525</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>540251</v>
+        <v>540221</v>
       </c>
       <c r="R146" t="n">
-        <v>6448423</v>
+        <v>6448466</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15130,10 +15130,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127288024</v>
+        <v>127288080</v>
       </c>
       <c r="B147" t="n">
-        <v>100558</v>
+        <v>91881</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>540221</v>
+        <v>540251</v>
       </c>
       <c r="R147" t="n">
-        <v>6448466</v>
+        <v>6448423</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15227,10 +15227,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127288032</v>
+        <v>127288015</v>
       </c>
       <c r="B148" t="n">
-        <v>100558</v>
+        <v>95772</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15238,21 +15238,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>540179</v>
+        <v>540180</v>
       </c>
       <c r="R148" t="n">
-        <v>6448506</v>
+        <v>6448493</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15324,10 +15324,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127288015</v>
+        <v>127288032</v>
       </c>
       <c r="B149" t="n">
-        <v>95804</v>
+        <v>100525</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2668</v>
+        <v>222771</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>540180</v>
+        <v>540179</v>
       </c>
       <c r="R149" t="n">
-        <v>6448493</v>
+        <v>6448506</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127288020</v>
+        <v>127288081</v>
       </c>
       <c r="B150" t="n">
-        <v>95804</v>
+        <v>91881</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2668</v>
+        <v>3884</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>540165</v>
+        <v>540243</v>
       </c>
       <c r="R150" t="n">
-        <v>6448511</v>
+        <v>6448421</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127288102</v>
+        <v>127288020</v>
       </c>
       <c r="B151" t="n">
-        <v>95789</v>
+        <v>95772</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15529,16 +15529,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>540208</v>
+        <v>540165</v>
       </c>
       <c r="R151" t="n">
-        <v>6448415</v>
+        <v>6448511</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15615,10 +15615,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127288081</v>
+        <v>127288102</v>
       </c>
       <c r="B152" t="n">
-        <v>91913</v>
+        <v>95757</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15626,21 +15626,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>540243</v>
+        <v>540208</v>
       </c>
       <c r="R152" t="n">
-        <v>6448421</v>
+        <v>6448415</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -15938,10 +15938,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132522294</v>
+        <v>132522328</v>
       </c>
       <c r="B155" t="n">
-        <v>106170</v>
+        <v>78691</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15949,53 +15949,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221141</v>
+        <v>6443</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Hamra, Hackelboö, Ög</t>
+          <t>Solbacken, Solbacken, Ög</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>540344</v>
+        <v>540163</v>
       </c>
       <c r="R155" t="n">
-        <v>6448518</v>
+        <v>6448369</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16022,50 +16006,39 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>08:22</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>08:22</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Tilde Tängerstad</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Tilde Tängerstad</t>
+          <t>Emil Ideskär, Tilde Tängerstad, William Rosén</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132522328</v>
+        <v>132522294</v>
       </c>
       <c r="B156" t="n">
-        <v>78691</v>
+        <v>106170</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16073,37 +16046,53 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6443</v>
+        <v>221141</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Solbacken, Solbacken, Ög</t>
+          <t>Hamra, Hackelboö, Ög</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>540163</v>
+        <v>540344</v>
       </c>
       <c r="R156" t="n">
-        <v>6448369</v>
+        <v>6448518</v>
       </c>
       <c r="S156" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16130,29 +16119,40 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Tilde Tängerstad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Tilde Tängerstad, William Rosén</t>
+          <t>Tilde Tängerstad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>

--- a/artfynd/A 17271-2025 artfynd.xlsx
+++ b/artfynd/A 17271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY171"/>
+  <dimension ref="A1:AZ171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15936161</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129376443</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081932</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288045</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Äldre fynd i Östergötlands flora x</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/423994</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/424762</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/424769</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
           <t>Kärlväxtinventering E-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/428912</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15939508</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53729208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1947,6 +2007,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081960</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081962</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081966</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2238,6 +2313,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124971516</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2335,6 +2415,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288092</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2432,6 +2517,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124971034</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2529,6 +2619,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124971310</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2631,6 +2726,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125148013</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125366296</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081918</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2932,6 +3042,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081921</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3029,6 +3144,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081928</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3126,6 +3246,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081933</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3223,6 +3348,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081935</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3320,6 +3450,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081948</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3417,6 +3552,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081954</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3514,6 +3654,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081956</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3611,6 +3756,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081963</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3708,6 +3858,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081970</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3805,6 +3960,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288057</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3902,6 +4062,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288058</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3999,6 +4164,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288059</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4096,6 +4266,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288060</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4193,6 +4368,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288061</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4290,6 +4470,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288062</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4387,6 +4572,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288063</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4484,6 +4674,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288064</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4581,6 +4776,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288065</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4688,6 +4888,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125366314</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4785,6 +4990,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288011</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4882,6 +5092,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288012</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4979,6 +5194,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288013</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5076,6 +5296,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288014</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5173,6 +5398,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288015</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5270,6 +5500,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288016</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5367,6 +5602,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288017</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5464,6 +5704,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288018</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5561,6 +5806,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288019</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5658,6 +5908,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288020</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5755,6 +6010,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288021</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5852,6 +6112,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124972268</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5954,6 +6219,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125148042</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6061,6 +6331,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125364204</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6158,6 +6433,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081920</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6255,6 +6535,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081923</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6352,6 +6637,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081924</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6449,6 +6739,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081925</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6546,6 +6841,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081939</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6643,6 +6943,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081950</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6740,6 +7045,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081951</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6837,6 +7147,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081952</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6934,6 +7249,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081955</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7031,6 +7351,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081967</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7128,6 +7453,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081968</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7225,6 +7555,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081971</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7322,6 +7657,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081976</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7419,6 +7759,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081977</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7516,6 +7861,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081978</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7613,6 +7963,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081979</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7710,6 +8065,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081980</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7807,6 +8167,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081981</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7920,6 +8285,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288093</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8033,6 +8403,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288094</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8130,6 +8505,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288100</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8227,6 +8607,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288101</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8324,6 +8709,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288102</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8421,6 +8811,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288103</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8518,6 +8913,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288104</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8615,6 +9015,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288105</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8712,6 +9117,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288107</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8809,6 +9219,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288108</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8906,6 +9321,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288109</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9008,6 +9428,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125148007</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9105,6 +9530,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081937</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9202,6 +9632,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081946</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9299,6 +9734,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081957</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9396,6 +9836,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081959</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9493,6 +9938,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081964</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9590,6 +10040,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081969</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9687,6 +10142,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081974</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9784,6 +10244,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081975</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9881,6 +10346,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288084</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9978,6 +10448,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288085</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10075,6 +10550,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288086</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10172,6 +10652,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288087</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10269,6 +10754,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288088</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10366,6 +10856,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288089</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10463,6 +10958,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288090</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10560,6 +11060,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288091</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10657,6 +11162,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288035</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10754,6 +11264,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288036</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10851,6 +11366,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288037</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10948,6 +11468,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081916</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11045,6 +11570,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081941</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11142,6 +11672,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081942</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11239,6 +11774,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081944</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11336,6 +11876,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081945</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11433,6 +11978,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081958</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11530,6 +12080,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081982</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11627,6 +12182,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288074</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11724,6 +12284,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288075</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11821,6 +12386,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288076</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11918,6 +12488,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288077</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12015,6 +12590,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288078</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12112,6 +12692,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288079</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12209,6 +12794,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288080</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12306,6 +12896,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288081</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12403,6 +12998,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288082</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12500,6 +13100,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124978294</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12597,6 +13202,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081926</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12694,6 +13304,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081927</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12791,6 +13406,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288022</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12888,6 +13508,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288110</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12985,6 +13610,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081953</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13082,6 +13712,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288068</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13179,6 +13814,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288069</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13276,6 +13916,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132522328</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13385,6 +14030,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532265</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13482,6 +14132,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125009086</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13586,6 +14241,11 @@
       <c r="AY132" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1939987</t>
         </is>
       </c>
     </row>
@@ -13694,6 +14354,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125147960</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13791,6 +14456,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124979217</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13910,6 +14580,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081919</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14007,6 +14682,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125499677</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14104,6 +14784,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124976354</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14211,6 +14896,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125366562</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14308,6 +14998,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124972164</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14405,6 +15100,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081949</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14519,6 +15219,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132575217</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14626,6 +15331,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15936156</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14729,6 +15439,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288038</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14831,6 +15546,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15936159</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14946,6 +15666,11 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119337931</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15043,6 +15768,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288039</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15141,6 +15871,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288040</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15238,6 +15973,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124968982</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15335,6 +16075,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124976998</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15437,6 +16182,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124977940</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15561,6 +16311,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132522294</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15663,6 +16418,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125148071</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15770,6 +16530,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15936158</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15867,6 +16632,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124972706</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15969,6 +16739,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125147970</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16080,6 +16855,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125364467</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16187,6 +16967,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125366402</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16294,6 +17079,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125366597</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16391,6 +17181,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081940</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16488,6 +17283,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288023</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16585,6 +17385,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288024</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16682,6 +17487,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288025</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16779,6 +17589,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288026</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16876,6 +17691,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288027</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16973,6 +17793,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288028</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17070,6 +17895,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288029</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17167,6 +17997,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288030</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17264,6 +18099,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288031</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17361,6 +18201,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288032</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17458,6 +18303,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288033</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17555,8 +18405,185 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>